--- a/review-results/河北实时运行及市场出清数据-20260906.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260906.xlsx
@@ -1400,10 +1400,18 @@
       <s:c r="C2" s="11" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D2" s="12"/>
-      <s:c r="E2" s="13"/>
-      <s:c r="F2" s="14"/>
-      <s:c r="G2" s="15"/>
+      <s:c r="D2" s="12" t="n">
+        <s:v>30828.2</s:v>
+      </s:c>
+      <s:c r="E2" s="13" t="n">
+        <s:v>8378.66</s:v>
+      </s:c>
+      <s:c r="F2" s="14" t="n">
+        <s:v>1045.3</s:v>
+      </s:c>
+      <s:c r="G2" s="15" t="n">
+        <s:v>6385.96</s:v>
+      </s:c>
       <s:c r="J2"/>
       <s:c r="K2"/>
       <s:c r="L2"/>
@@ -1420,10 +1428,18 @@
       <s:c r="C3" s="11" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D3" s="12"/>
-      <s:c r="E3" s="13"/>
-      <s:c r="F3" s="14"/>
-      <s:c r="G3" s="15"/>
+      <s:c r="D3" s="12" t="n">
+        <s:v>30590.9</s:v>
+      </s:c>
+      <s:c r="E3" s="13" t="n">
+        <s:v>8374.08</s:v>
+      </s:c>
+      <s:c r="F3" s="14" t="n">
+        <s:v>986.9</s:v>
+      </s:c>
+      <s:c r="G3" s="15" t="n">
+        <s:v>6216.35</s:v>
+      </s:c>
       <s:c r="J3"/>
       <s:c r="K3"/>
       <s:c r="L3"/>
@@ -1440,10 +1456,18 @@
       <s:c r="C4" s="11" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D4" s="12"/>
-      <s:c r="E4" s="13"/>
-      <s:c r="F4" s="14"/>
-      <s:c r="G4" s="15"/>
+      <s:c r="D4" s="12" t="n">
+        <s:v>30334.9</s:v>
+      </s:c>
+      <s:c r="E4" s="13" t="n">
+        <s:v>8369.47</s:v>
+      </s:c>
+      <s:c r="F4" s="14" t="n">
+        <s:v>909.6</s:v>
+      </s:c>
+      <s:c r="G4" s="15" t="n">
+        <s:v>6436.4</s:v>
+      </s:c>
       <s:c r="J4"/>
       <s:c r="K4"/>
       <s:c r="L4"/>
@@ -1460,10 +1484,18 @@
       <s:c r="C5" s="11" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D5" s="12"/>
-      <s:c r="E5" s="13"/>
-      <s:c r="F5" s="14"/>
-      <s:c r="G5" s="15"/>
+      <s:c r="D5" s="12" t="n">
+        <s:v>29933.5</s:v>
+      </s:c>
+      <s:c r="E5" s="13" t="n">
+        <s:v>8362.62</s:v>
+      </s:c>
+      <s:c r="F5" s="14" t="n">
+        <s:v>879.9</s:v>
+      </s:c>
+      <s:c r="G5" s="15" t="n">
+        <s:v>6188.57</s:v>
+      </s:c>
       <s:c r="J5"/>
       <s:c r="K5"/>
       <s:c r="L5"/>
@@ -1480,10 +1512,18 @@
       <s:c r="C6" s="11" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D6" s="12"/>
-      <s:c r="E6" s="13"/>
-      <s:c r="F6" s="14"/>
-      <s:c r="G6" s="15"/>
+      <s:c r="D6" s="12" t="n">
+        <s:v>29695.1</s:v>
+      </s:c>
+      <s:c r="E6" s="13" t="n">
+        <s:v>8356.38</s:v>
+      </s:c>
+      <s:c r="F6" s="14" t="n">
+        <s:v>856.6</s:v>
+      </s:c>
+      <s:c r="G6" s="15" t="n">
+        <s:v>5756.9</s:v>
+      </s:c>
       <s:c r="J6"/>
       <s:c r="K6"/>
       <s:c r="L6"/>
@@ -1500,10 +1540,18 @@
       <s:c r="C7" s="11" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D7" s="12"/>
-      <s:c r="E7" s="13"/>
-      <s:c r="F7" s="14"/>
-      <s:c r="G7" s="15"/>
+      <s:c r="D7" s="12" t="n">
+        <s:v>29449.9</s:v>
+      </s:c>
+      <s:c r="E7" s="13" t="n">
+        <s:v>8352.63</s:v>
+      </s:c>
+      <s:c r="F7" s="14" t="n">
+        <s:v>776.3</s:v>
+      </s:c>
+      <s:c r="G7" s="15" t="n">
+        <s:v>6053.2</s:v>
+      </s:c>
       <s:c r="J7"/>
       <s:c r="K7"/>
       <s:c r="L7"/>
@@ -1520,10 +1568,18 @@
       <s:c r="C8" s="11" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D8" s="12"/>
-      <s:c r="E8" s="13"/>
-      <s:c r="F8" s="14"/>
-      <s:c r="G8" s="15"/>
+      <s:c r="D8" s="12" t="n">
+        <s:v>29519.2</s:v>
+      </s:c>
+      <s:c r="E8" s="13" t="n">
+        <s:v>8347.17</s:v>
+      </s:c>
+      <s:c r="F8" s="14" t="n">
+        <s:v>677.9</s:v>
+      </s:c>
+      <s:c r="G8" s="15" t="n">
+        <s:v>6303.84</s:v>
+      </s:c>
       <s:c r="J8"/>
       <s:c r="K8"/>
       <s:c r="L8"/>
@@ -1540,10 +1596,18 @@
       <s:c r="C9" s="11" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D9" s="12"/>
-      <s:c r="E9" s="13"/>
-      <s:c r="F9" s="14"/>
-      <s:c r="G9" s="15"/>
+      <s:c r="D9" s="12" t="n">
+        <s:v>29529.2</s:v>
+      </s:c>
+      <s:c r="E9" s="13" t="n">
+        <s:v>8345.58</s:v>
+      </s:c>
+      <s:c r="F9" s="14" t="n">
+        <s:v>609.6</s:v>
+      </s:c>
+      <s:c r="G9" s="15" t="n">
+        <s:v>5359.14</s:v>
+      </s:c>
       <s:c r="J9"/>
       <s:c r="K9"/>
       <s:c r="L9"/>
@@ -1560,10 +1624,18 @@
       <s:c r="C10" s="11" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D10" s="12"/>
-      <s:c r="E10" s="13"/>
-      <s:c r="F10" s="14"/>
-      <s:c r="G10" s="15"/>
+      <s:c r="D10" s="12" t="n">
+        <s:v>32691</s:v>
+      </s:c>
+      <s:c r="E10" s="13" t="n">
+        <s:v>8339.01</s:v>
+      </s:c>
+      <s:c r="F10" s="14" t="n">
+        <s:v>585.2</s:v>
+      </s:c>
+      <s:c r="G10" s="15" t="n">
+        <s:v>6721.05</s:v>
+      </s:c>
       <s:c r="J10"/>
       <s:c r="K10"/>
       <s:c r="L10"/>
@@ -1580,10 +1652,18 @@
       <s:c r="C11" s="11" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D11" s="12"/>
-      <s:c r="E11" s="13"/>
-      <s:c r="F11" s="14"/>
-      <s:c r="G11" s="15"/>
+      <s:c r="D11" s="12" t="n">
+        <s:v>32066.4</s:v>
+      </s:c>
+      <s:c r="E11" s="13" t="n">
+        <s:v>8333.02</s:v>
+      </s:c>
+      <s:c r="F11" s="14" t="n">
+        <s:v>548.8</s:v>
+      </s:c>
+      <s:c r="G11" s="15" t="n">
+        <s:v>6837.02</s:v>
+      </s:c>
       <s:c r="J11"/>
       <s:c r="K11"/>
       <s:c r="L11"/>
@@ -1600,10 +1680,18 @@
       <s:c r="C12" s="11" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D12" s="12"/>
-      <s:c r="E12" s="13"/>
-      <s:c r="F12" s="14"/>
-      <s:c r="G12" s="15"/>
+      <s:c r="D12" s="12" t="n">
+        <s:v>31685.6</s:v>
+      </s:c>
+      <s:c r="E12" s="13" t="n">
+        <s:v>8327.15</s:v>
+      </s:c>
+      <s:c r="F12" s="14" t="n">
+        <s:v>493.1</s:v>
+      </s:c>
+      <s:c r="G12" s="15" t="n">
+        <s:v>6874.01</s:v>
+      </s:c>
       <s:c r="J12"/>
       <s:c r="K12"/>
       <s:c r="L12"/>
@@ -1620,10 +1708,18 @@
       <s:c r="C13" s="11" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D13" s="12"/>
-      <s:c r="E13" s="13"/>
-      <s:c r="F13" s="14"/>
-      <s:c r="G13" s="15"/>
+      <s:c r="D13" s="12" t="n">
+        <s:v>30842.4</s:v>
+      </s:c>
+      <s:c r="E13" s="13" t="n">
+        <s:v>8323.75</s:v>
+      </s:c>
+      <s:c r="F13" s="14" t="n">
+        <s:v>434.7</s:v>
+      </s:c>
+      <s:c r="G13" s="15" t="n">
+        <s:v>6949.48</s:v>
+      </s:c>
       <s:c r="J13"/>
       <s:c r="K13"/>
       <s:c r="L13"/>
@@ -1640,10 +1736,18 @@
       <s:c r="C14" s="11" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D14" s="12"/>
-      <s:c r="E14" s="13"/>
-      <s:c r="F14" s="14"/>
-      <s:c r="G14" s="15"/>
+      <s:c r="D14" s="12" t="n">
+        <s:v>30532.7</s:v>
+      </s:c>
+      <s:c r="E14" s="13" t="n">
+        <s:v>8321.03</s:v>
+      </s:c>
+      <s:c r="F14" s="14" t="n">
+        <s:v>366.7</s:v>
+      </s:c>
+      <s:c r="G14" s="15" t="n">
+        <s:v>6539.23</s:v>
+      </s:c>
       <s:c r="J14"/>
       <s:c r="K14"/>
       <s:c r="L14"/>
@@ -1660,10 +1764,18 @@
       <s:c r="C15" s="11" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D15" s="12"/>
-      <s:c r="E15" s="13"/>
-      <s:c r="F15" s="14"/>
-      <s:c r="G15" s="15"/>
+      <s:c r="D15" s="12" t="n">
+        <s:v>30208.7</s:v>
+      </s:c>
+      <s:c r="E15" s="13" t="n">
+        <s:v>8313.62</s:v>
+      </s:c>
+      <s:c r="F15" s="14" t="n">
+        <s:v>305.5</s:v>
+      </s:c>
+      <s:c r="G15" s="15" t="n">
+        <s:v>6117.45</s:v>
+      </s:c>
       <s:c r="J15"/>
       <s:c r="K15"/>
       <s:c r="L15"/>
@@ -1680,10 +1792,18 @@
       <s:c r="C16" s="11" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D16" s="12"/>
-      <s:c r="E16" s="13"/>
-      <s:c r="F16" s="14"/>
-      <s:c r="G16" s="15"/>
+      <s:c r="D16" s="12" t="n">
+        <s:v>30002.9</s:v>
+      </s:c>
+      <s:c r="E16" s="13" t="n">
+        <s:v>8310.78</s:v>
+      </s:c>
+      <s:c r="F16" s="14" t="n">
+        <s:v>282.8</s:v>
+      </s:c>
+      <s:c r="G16" s="15" t="n">
+        <s:v>5718.7</s:v>
+      </s:c>
       <s:c r="J16"/>
       <s:c r="K16"/>
       <s:c r="L16"/>
@@ -1700,10 +1820,18 @@
       <s:c r="C17" s="11" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D17" s="12"/>
-      <s:c r="E17" s="13"/>
-      <s:c r="F17" s="14"/>
-      <s:c r="G17" s="15"/>
+      <s:c r="D17" s="12" t="n">
+        <s:v>29841.4</s:v>
+      </s:c>
+      <s:c r="E17" s="13" t="n">
+        <s:v>8306.77</s:v>
+      </s:c>
+      <s:c r="F17" s="14" t="n">
+        <s:v>245.4</s:v>
+      </s:c>
+      <s:c r="G17" s="15" t="n">
+        <s:v>5635.1</s:v>
+      </s:c>
       <s:c r="J17"/>
       <s:c r="K17"/>
       <s:c r="L17"/>
@@ -1720,10 +1848,18 @@
       <s:c r="C18" s="11" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D18" s="12"/>
-      <s:c r="E18" s="13"/>
-      <s:c r="F18" s="14"/>
-      <s:c r="G18" s="15"/>
+      <s:c r="D18" s="12" t="n">
+        <s:v>29617.6</s:v>
+      </s:c>
+      <s:c r="E18" s="13" t="n">
+        <s:v>8314.25</s:v>
+      </s:c>
+      <s:c r="F18" s="14" t="n">
+        <s:v>242.6</s:v>
+      </s:c>
+      <s:c r="G18" s="15" t="n">
+        <s:v>5118.26</s:v>
+      </s:c>
       <s:c r="J18"/>
       <s:c r="K18"/>
       <s:c r="L18"/>
@@ -1740,10 +1876,18 @@
       <s:c r="C19" s="11" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D19" s="12"/>
-      <s:c r="E19" s="13"/>
-      <s:c r="F19" s="14"/>
-      <s:c r="G19" s="15"/>
+      <s:c r="D19" s="12" t="n">
+        <s:v>29206.9</s:v>
+      </s:c>
+      <s:c r="E19" s="13" t="n">
+        <s:v>8311.43</s:v>
+      </s:c>
+      <s:c r="F19" s="14" t="n">
+        <s:v>240</s:v>
+      </s:c>
+      <s:c r="G19" s="15" t="n">
+        <s:v>5658.34</s:v>
+      </s:c>
       <s:c r="J19"/>
       <s:c r="K19"/>
       <s:c r="L19"/>
@@ -1760,10 +1904,18 @@
       <s:c r="C20" s="11" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D20" s="12"/>
-      <s:c r="E20" s="13"/>
-      <s:c r="F20" s="14"/>
-      <s:c r="G20" s="15"/>
+      <s:c r="D20" s="12" t="n">
+        <s:v>29371.4</s:v>
+      </s:c>
+      <s:c r="E20" s="13" t="n">
+        <s:v>8308.01</s:v>
+      </s:c>
+      <s:c r="F20" s="14" t="n">
+        <s:v>225.1</s:v>
+      </s:c>
+      <s:c r="G20" s="15" t="n">
+        <s:v>5322.15</s:v>
+      </s:c>
       <s:c r="J20"/>
       <s:c r="K20"/>
       <s:c r="L20"/>
@@ -1780,10 +1932,18 @@
       <s:c r="C21" s="11" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D21" s="12"/>
-      <s:c r="E21" s="13"/>
-      <s:c r="F21" s="14"/>
-      <s:c r="G21" s="15"/>
+      <s:c r="D21" s="12" t="n">
+        <s:v>29549.9</s:v>
+      </s:c>
+      <s:c r="E21" s="13" t="n">
+        <s:v>8304.61</s:v>
+      </s:c>
+      <s:c r="F21" s="14" t="n">
+        <s:v>226.1</s:v>
+      </s:c>
+      <s:c r="G21" s="15" t="n">
+        <s:v>5267.13</s:v>
+      </s:c>
       <s:c r="J21"/>
       <s:c r="K21"/>
       <s:c r="L21"/>
@@ -1800,10 +1960,18 @@
       <s:c r="C22" s="11" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D22" s="12"/>
-      <s:c r="E22" s="13"/>
-      <s:c r="F22" s="14"/>
-      <s:c r="G22" s="15"/>
+      <s:c r="D22" s="12" t="n">
+        <s:v>29860.6</s:v>
+      </s:c>
+      <s:c r="E22" s="13" t="n">
+        <s:v>8304.14</s:v>
+      </s:c>
+      <s:c r="F22" s="14" t="n">
+        <s:v>236</s:v>
+      </s:c>
+      <s:c r="G22" s="15" t="n">
+        <s:v>5436.72</s:v>
+      </s:c>
       <s:c r="J22"/>
       <s:c r="K22"/>
       <s:c r="L22"/>
@@ -1820,10 +1988,18 @@
       <s:c r="C23" s="11" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D23" s="12"/>
-      <s:c r="E23" s="13"/>
-      <s:c r="F23" s="14"/>
-      <s:c r="G23" s="15"/>
+      <s:c r="D23" s="12" t="n">
+        <s:v>29778.6</s:v>
+      </s:c>
+      <s:c r="E23" s="13" t="n">
+        <s:v>8305.02</s:v>
+      </s:c>
+      <s:c r="F23" s="14" t="n">
+        <s:v>243.6</s:v>
+      </s:c>
+      <s:c r="G23" s="15" t="n">
+        <s:v>4925.02</s:v>
+      </s:c>
       <s:c r="J23"/>
       <s:c r="K23"/>
       <s:c r="L23"/>
@@ -1840,10 +2016,18 @@
       <s:c r="C24" s="11" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D24" s="12"/>
-      <s:c r="E24" s="13"/>
-      <s:c r="F24" s="14"/>
-      <s:c r="G24" s="15"/>
+      <s:c r="D24" s="12" t="n">
+        <s:v>29974.9</s:v>
+      </s:c>
+      <s:c r="E24" s="13" t="n">
+        <s:v>8308.92</s:v>
+      </s:c>
+      <s:c r="F24" s="14" t="n">
+        <s:v>265.1</s:v>
+      </s:c>
+      <s:c r="G24" s="15" t="n">
+        <s:v>5447.66</s:v>
+      </s:c>
       <s:c r="J24"/>
       <s:c r="K24"/>
       <s:c r="L24"/>
@@ -1860,10 +2044,18 @@
       <s:c r="C25" s="11" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D25" s="12"/>
-      <s:c r="E25" s="13"/>
-      <s:c r="F25" s="14"/>
-      <s:c r="G25" s="15"/>
+      <s:c r="D25" s="12" t="n">
+        <s:v>29952.3</s:v>
+      </s:c>
+      <s:c r="E25" s="13" t="n">
+        <s:v>8312.03</s:v>
+      </s:c>
+      <s:c r="F25" s="14" t="n">
+        <s:v>338.7</s:v>
+      </s:c>
+      <s:c r="G25" s="15" t="n">
+        <s:v>5498.77</s:v>
+      </s:c>
       <s:c r="J25"/>
       <s:c r="K25"/>
       <s:c r="L25"/>
@@ -1880,10 +2072,18 @@
       <s:c r="C26" s="11" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D26" s="12"/>
-      <s:c r="E26" s="13"/>
-      <s:c r="F26" s="14"/>
-      <s:c r="G26" s="15"/>
+      <s:c r="D26" s="12" t="n">
+        <s:v>29842.2</s:v>
+      </s:c>
+      <s:c r="E26" s="13" t="n">
+        <s:v>8086.15</s:v>
+      </s:c>
+      <s:c r="F26" s="14" t="n">
+        <s:v>588.1</s:v>
+      </s:c>
+      <s:c r="G26" s="15" t="n">
+        <s:v>5057.25</s:v>
+      </s:c>
       <s:c r="J26"/>
       <s:c r="K26"/>
       <s:c r="L26"/>
@@ -1900,10 +2100,18 @@
       <s:c r="C27" s="11" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D27" s="12"/>
-      <s:c r="E27" s="13"/>
-      <s:c r="F27" s="14"/>
-      <s:c r="G27" s="15"/>
+      <s:c r="D27" s="12" t="n">
+        <s:v>29937.6</s:v>
+      </s:c>
+      <s:c r="E27" s="13" t="n">
+        <s:v>7652.84</s:v>
+      </s:c>
+      <s:c r="F27" s="14" t="n">
+        <s:v>1026.6</s:v>
+      </s:c>
+      <s:c r="G27" s="15" t="n">
+        <s:v>4874.4</s:v>
+      </s:c>
       <s:c r="J27"/>
       <s:c r="K27"/>
       <s:c r="L27"/>
@@ -1920,10 +2128,18 @@
       <s:c r="C28" s="11" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D28" s="12"/>
-      <s:c r="E28" s="13"/>
-      <s:c r="F28" s="14"/>
-      <s:c r="G28" s="15"/>
+      <s:c r="D28" s="12" t="n">
+        <s:v>29858.3</s:v>
+      </s:c>
+      <s:c r="E28" s="13" t="n">
+        <s:v>6968.93</s:v>
+      </s:c>
+      <s:c r="F28" s="14" t="n">
+        <s:v>1619.1</s:v>
+      </s:c>
+      <s:c r="G28" s="15" t="n">
+        <s:v>4622.62</s:v>
+      </s:c>
       <s:c r="J28"/>
       <s:c r="K28"/>
       <s:c r="L28"/>
@@ -1940,10 +2156,18 @@
       <s:c r="C29" s="11" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D29" s="12"/>
-      <s:c r="E29" s="13"/>
-      <s:c r="F29" s="14"/>
-      <s:c r="G29" s="15"/>
+      <s:c r="D29" s="12" t="n">
+        <s:v>29261.4</s:v>
+      </s:c>
+      <s:c r="E29" s="13" t="n">
+        <s:v>6295.53</s:v>
+      </s:c>
+      <s:c r="F29" s="14" t="n">
+        <s:v>2297</s:v>
+      </s:c>
+      <s:c r="G29" s="15" t="n">
+        <s:v>4432.75</s:v>
+      </s:c>
       <s:c r="J29"/>
       <s:c r="K29"/>
       <s:c r="L29"/>
@@ -1960,10 +2184,18 @@
       <s:c r="C30" s="11" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D30" s="12"/>
-      <s:c r="E30" s="13"/>
-      <s:c r="F30" s="14"/>
-      <s:c r="G30" s="15"/>
+      <s:c r="D30" s="12" t="n">
+        <s:v>28976.1</s:v>
+      </s:c>
+      <s:c r="E30" s="13" t="n">
+        <s:v>5830.52</s:v>
+      </s:c>
+      <s:c r="F30" s="14" t="n">
+        <s:v>3083.4</s:v>
+      </s:c>
+      <s:c r="G30" s="15" t="n">
+        <s:v>4215.98</s:v>
+      </s:c>
       <s:c r="J30"/>
       <s:c r="K30"/>
       <s:c r="L30"/>
@@ -1980,10 +2212,18 @@
       <s:c r="C31" s="11" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D31" s="12"/>
-      <s:c r="E31" s="13"/>
-      <s:c r="F31" s="14"/>
-      <s:c r="G31" s="15"/>
+      <s:c r="D31" s="12" t="n">
+        <s:v>28766.7</s:v>
+      </s:c>
+      <s:c r="E31" s="13" t="n">
+        <s:v>5347.89</s:v>
+      </s:c>
+      <s:c r="F31" s="14" t="n">
+        <s:v>3994.7</s:v>
+      </s:c>
+      <s:c r="G31" s="15" t="n">
+        <s:v>4314.35</s:v>
+      </s:c>
       <s:c r="J31"/>
       <s:c r="K31"/>
       <s:c r="L31"/>
@@ -2000,10 +2240,18 @@
       <s:c r="C32" s="11" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D32" s="12"/>
-      <s:c r="E32" s="13"/>
-      <s:c r="F32" s="14"/>
-      <s:c r="G32" s="15"/>
+      <s:c r="D32" s="12" t="n">
+        <s:v>28405.9</s:v>
+      </s:c>
+      <s:c r="E32" s="13" t="n">
+        <s:v>4884.39</s:v>
+      </s:c>
+      <s:c r="F32" s="14" t="n">
+        <s:v>4862.1</s:v>
+      </s:c>
+      <s:c r="G32" s="15" t="n">
+        <s:v>4966.57</s:v>
+      </s:c>
       <s:c r="J32"/>
       <s:c r="K32"/>
       <s:c r="L32"/>
@@ -2020,10 +2268,18 @@
       <s:c r="C33" s="11" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D33" s="12"/>
-      <s:c r="E33" s="13"/>
-      <s:c r="F33" s="14"/>
-      <s:c r="G33" s="15"/>
+      <s:c r="D33" s="12" t="n">
+        <s:v>28139</s:v>
+      </s:c>
+      <s:c r="E33" s="13" t="n">
+        <s:v>4472.38</s:v>
+      </s:c>
+      <s:c r="F33" s="14" t="n">
+        <s:v>5679.9</s:v>
+      </s:c>
+      <s:c r="G33" s="15" t="n">
+        <s:v>5201.93</s:v>
+      </s:c>
       <s:c r="J33"/>
       <s:c r="K33"/>
       <s:c r="L33"/>
@@ -2040,10 +2296,18 @@
       <s:c r="C34" s="11" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D34" s="12"/>
-      <s:c r="E34" s="13"/>
-      <s:c r="F34" s="14"/>
-      <s:c r="G34" s="15"/>
+      <s:c r="D34" s="12" t="n">
+        <s:v>28321.5</s:v>
+      </s:c>
+      <s:c r="E34" s="13" t="n">
+        <s:v>4120.02</s:v>
+      </s:c>
+      <s:c r="F34" s="14" t="n">
+        <s:v>6493.7</s:v>
+      </s:c>
+      <s:c r="G34" s="15" t="n">
+        <s:v>5870.3</s:v>
+      </s:c>
       <s:c r="J34"/>
       <s:c r="K34"/>
       <s:c r="L34"/>
@@ -2060,10 +2324,18 @@
       <s:c r="C35" s="11" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D35" s="12"/>
-      <s:c r="E35" s="13"/>
-      <s:c r="F35" s="14"/>
-      <s:c r="G35" s="15"/>
+      <s:c r="D35" s="12" t="n">
+        <s:v>27732.6</s:v>
+      </s:c>
+      <s:c r="E35" s="13" t="n">
+        <s:v>4067.44</s:v>
+      </s:c>
+      <s:c r="F35" s="14" t="n">
+        <s:v>7257.6</s:v>
+      </s:c>
+      <s:c r="G35" s="15" t="n">
+        <s:v>6309.08</s:v>
+      </s:c>
       <s:c r="J35"/>
       <s:c r="K35"/>
       <s:c r="L35"/>
@@ -2080,10 +2352,18 @@
       <s:c r="C36" s="11" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D36" s="12"/>
-      <s:c r="E36" s="13"/>
-      <s:c r="F36" s="14"/>
-      <s:c r="G36" s="15"/>
+      <s:c r="D36" s="12" t="n">
+        <s:v>27461.6</s:v>
+      </s:c>
+      <s:c r="E36" s="13" t="n">
+        <s:v>4100.66</s:v>
+      </s:c>
+      <s:c r="F36" s="14" t="n">
+        <s:v>7990.8</s:v>
+      </s:c>
+      <s:c r="G36" s="15" t="n">
+        <s:v>7324.08</s:v>
+      </s:c>
       <s:c r="J36"/>
       <s:c r="K36"/>
       <s:c r="L36"/>
@@ -2100,10 +2380,18 @@
       <s:c r="C37" s="11" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D37" s="12"/>
-      <s:c r="E37" s="13"/>
-      <s:c r="F37" s="14"/>
-      <s:c r="G37" s="15"/>
+      <s:c r="D37" s="12" t="n">
+        <s:v>27499.2</s:v>
+      </s:c>
+      <s:c r="E37" s="13" t="n">
+        <s:v>4127.97</s:v>
+      </s:c>
+      <s:c r="F37" s="14" t="n">
+        <s:v>8705.2</s:v>
+      </s:c>
+      <s:c r="G37" s="15" t="n">
+        <s:v>7632.27</s:v>
+      </s:c>
       <s:c r="J37"/>
       <s:c r="K37"/>
       <s:c r="L37"/>
@@ -2120,10 +2408,18 @@
       <s:c r="C38" s="11" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D38" s="12"/>
-      <s:c r="E38" s="13"/>
-      <s:c r="F38" s="14"/>
-      <s:c r="G38" s="15"/>
+      <s:c r="D38" s="12" t="n">
+        <s:v>27154.2</s:v>
+      </s:c>
+      <s:c r="E38" s="13" t="n">
+        <s:v>4160.09</s:v>
+      </s:c>
+      <s:c r="F38" s="14" t="n">
+        <s:v>9245.3</s:v>
+      </s:c>
+      <s:c r="G38" s="15" t="n">
+        <s:v>7640.82</s:v>
+      </s:c>
       <s:c r="J38"/>
       <s:c r="K38"/>
       <s:c r="L38"/>
@@ -2140,10 +2436,18 @@
       <s:c r="C39" s="11" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D39" s="12"/>
-      <s:c r="E39" s="13"/>
-      <s:c r="F39" s="14"/>
-      <s:c r="G39" s="15"/>
+      <s:c r="D39" s="12" t="n">
+        <s:v>27045.6</s:v>
+      </s:c>
+      <s:c r="E39" s="13" t="n">
+        <s:v>4203.04</s:v>
+      </s:c>
+      <s:c r="F39" s="14" t="n">
+        <s:v>9618.2</s:v>
+      </s:c>
+      <s:c r="G39" s="15" t="n">
+        <s:v>7941.75</s:v>
+      </s:c>
       <s:c r="J39"/>
       <s:c r="K39"/>
       <s:c r="L39"/>
@@ -2160,10 +2464,18 @@
       <s:c r="C40" s="11" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D40" s="12"/>
-      <s:c r="E40" s="13"/>
-      <s:c r="F40" s="14"/>
-      <s:c r="G40" s="15"/>
+      <s:c r="D40" s="12" t="n">
+        <s:v>26806.6</s:v>
+      </s:c>
+      <s:c r="E40" s="13" t="n">
+        <s:v>4235.81</s:v>
+      </s:c>
+      <s:c r="F40" s="14" t="n">
+        <s:v>10200.7</s:v>
+      </s:c>
+      <s:c r="G40" s="15" t="n">
+        <s:v>7854.61</s:v>
+      </s:c>
       <s:c r="J40"/>
       <s:c r="K40"/>
       <s:c r="L40"/>
@@ -2180,10 +2492,18 @@
       <s:c r="C41" s="11" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D41" s="12"/>
-      <s:c r="E41" s="13"/>
-      <s:c r="F41" s="14"/>
-      <s:c r="G41" s="15"/>
+      <s:c r="D41" s="12" t="n">
+        <s:v>26449.7</s:v>
+      </s:c>
+      <s:c r="E41" s="13" t="n">
+        <s:v>4256.36</s:v>
+      </s:c>
+      <s:c r="F41" s="14" t="n">
+        <s:v>10607.5</s:v>
+      </s:c>
+      <s:c r="G41" s="15" t="n">
+        <s:v>7558.82</s:v>
+      </s:c>
       <s:c r="J41"/>
       <s:c r="K41"/>
       <s:c r="L41"/>
@@ -2200,10 +2520,18 @@
       <s:c r="C42" s="11" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D42" s="12"/>
-      <s:c r="E42" s="13"/>
-      <s:c r="F42" s="14"/>
-      <s:c r="G42" s="15"/>
+      <s:c r="D42" s="12" t="n">
+        <s:v>26379.5</s:v>
+      </s:c>
+      <s:c r="E42" s="13" t="n">
+        <s:v>4285.81</s:v>
+      </s:c>
+      <s:c r="F42" s="14" t="n">
+        <s:v>11015.1</s:v>
+      </s:c>
+      <s:c r="G42" s="15" t="n">
+        <s:v>7753.42</s:v>
+      </s:c>
       <s:c r="J42"/>
       <s:c r="K42"/>
       <s:c r="L42"/>
@@ -2220,10 +2548,18 @@
       <s:c r="C43" s="11" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D43" s="12"/>
-      <s:c r="E43" s="13"/>
-      <s:c r="F43" s="14"/>
-      <s:c r="G43" s="15"/>
+      <s:c r="D43" s="12" t="n">
+        <s:v>26124.7</s:v>
+      </s:c>
+      <s:c r="E43" s="13" t="n">
+        <s:v>4303.16</s:v>
+      </s:c>
+      <s:c r="F43" s="14" t="n">
+        <s:v>11434.8</s:v>
+      </s:c>
+      <s:c r="G43" s="15" t="n">
+        <s:v>7941.51</s:v>
+      </s:c>
       <s:c r="J43"/>
       <s:c r="K43"/>
       <s:c r="L43"/>
@@ -2240,10 +2576,18 @@
       <s:c r="C44" s="11" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D44" s="12"/>
-      <s:c r="E44" s="13"/>
-      <s:c r="F44" s="14"/>
-      <s:c r="G44" s="15"/>
+      <s:c r="D44" s="12" t="n">
+        <s:v>26334.8</s:v>
+      </s:c>
+      <s:c r="E44" s="13" t="n">
+        <s:v>4323.39</s:v>
+      </s:c>
+      <s:c r="F44" s="14" t="n">
+        <s:v>11654.6</s:v>
+      </s:c>
+      <s:c r="G44" s="15" t="n">
+        <s:v>7783.04</s:v>
+      </s:c>
       <s:c r="J44"/>
       <s:c r="K44"/>
       <s:c r="L44"/>
@@ -2260,10 +2604,18 @@
       <s:c r="C45" s="11" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D45" s="12"/>
-      <s:c r="E45" s="13"/>
-      <s:c r="F45" s="14"/>
-      <s:c r="G45" s="15"/>
+      <s:c r="D45" s="12" t="n">
+        <s:v>26416.9</s:v>
+      </s:c>
+      <s:c r="E45" s="13" t="n">
+        <s:v>4341.36</s:v>
+      </s:c>
+      <s:c r="F45" s="14" t="n">
+        <s:v>11874.6</s:v>
+      </s:c>
+      <s:c r="G45" s="15" t="n">
+        <s:v>7559.63</s:v>
+      </s:c>
       <s:c r="J45"/>
       <s:c r="K45"/>
       <s:c r="L45"/>
@@ -2280,10 +2632,18 @@
       <s:c r="C46" s="11" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D46" s="12"/>
-      <s:c r="E46" s="13"/>
-      <s:c r="F46" s="14"/>
-      <s:c r="G46" s="15"/>
+      <s:c r="D46" s="12" t="n">
+        <s:v>28661.6</s:v>
+      </s:c>
+      <s:c r="E46" s="13" t="n">
+        <s:v>4336.2</s:v>
+      </s:c>
+      <s:c r="F46" s="14" t="n">
+        <s:v>12256</s:v>
+      </s:c>
+      <s:c r="G46" s="15" t="n">
+        <s:v>7931.75</s:v>
+      </s:c>
       <s:c r="J46"/>
       <s:c r="K46"/>
       <s:c r="L46"/>
@@ -2300,10 +2660,18 @@
       <s:c r="C47" s="11" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D47" s="12"/>
-      <s:c r="E47" s="13"/>
-      <s:c r="F47" s="14"/>
-      <s:c r="G47" s="15"/>
+      <s:c r="D47" s="12" t="n">
+        <s:v>28774.2</s:v>
+      </s:c>
+      <s:c r="E47" s="13" t="n">
+        <s:v>4354.74</s:v>
+      </s:c>
+      <s:c r="F47" s="14" t="n">
+        <s:v>12379</s:v>
+      </s:c>
+      <s:c r="G47" s="15" t="n">
+        <s:v>7246.3</s:v>
+      </s:c>
       <s:c r="J47"/>
       <s:c r="K47"/>
       <s:c r="L47"/>
@@ -2320,10 +2688,18 @@
       <s:c r="C48" s="11" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D48" s="12"/>
-      <s:c r="E48" s="13"/>
-      <s:c r="F48" s="14"/>
-      <s:c r="G48" s="15"/>
+      <s:c r="D48" s="12" t="n">
+        <s:v>28180.9</s:v>
+      </s:c>
+      <s:c r="E48" s="13" t="n">
+        <s:v>4350.51</s:v>
+      </s:c>
+      <s:c r="F48" s="14" t="n">
+        <s:v>12479.2</s:v>
+      </s:c>
+      <s:c r="G48" s="15" t="n">
+        <s:v>6619.66</s:v>
+      </s:c>
       <s:c r="J48"/>
       <s:c r="K48"/>
       <s:c r="L48"/>
@@ -2340,10 +2716,18 @@
       <s:c r="C49" s="11" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D49" s="12"/>
-      <s:c r="E49" s="13"/>
-      <s:c r="F49" s="14"/>
-      <s:c r="G49" s="15"/>
+      <s:c r="D49" s="12" t="n">
+        <s:v>26766.7</s:v>
+      </s:c>
+      <s:c r="E49" s="13" t="n">
+        <s:v>4350.5</s:v>
+      </s:c>
+      <s:c r="F49" s="14" t="n">
+        <s:v>12504.1</s:v>
+      </s:c>
+      <s:c r="G49" s="15" t="n">
+        <s:v>5919.4</s:v>
+      </s:c>
       <s:c r="J49"/>
       <s:c r="K49"/>
       <s:c r="L49"/>
@@ -2360,10 +2744,18 @@
       <s:c r="C50" s="11" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D50" s="12"/>
-      <s:c r="E50" s="13"/>
-      <s:c r="F50" s="14"/>
-      <s:c r="G50" s="15"/>
+      <s:c r="D50" s="12" t="n">
+        <s:v>26675.1</s:v>
+      </s:c>
+      <s:c r="E50" s="13" t="n">
+        <s:v>4360.91</s:v>
+      </s:c>
+      <s:c r="F50" s="14" t="n">
+        <s:v>12500.7</s:v>
+      </s:c>
+      <s:c r="G50" s="15" t="n">
+        <s:v>5544.53</s:v>
+      </s:c>
       <s:c r="J50"/>
       <s:c r="K50"/>
       <s:c r="L50"/>
@@ -2380,10 +2772,18 @@
       <s:c r="C51" s="11" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D51" s="12"/>
-      <s:c r="E51" s="13"/>
-      <s:c r="F51" s="14"/>
-      <s:c r="G51" s="15"/>
+      <s:c r="D51" s="12" t="n">
+        <s:v>26701.7</s:v>
+      </s:c>
+      <s:c r="E51" s="13" t="n">
+        <s:v>4351.69</s:v>
+      </s:c>
+      <s:c r="F51" s="14" t="n">
+        <s:v>12425.6</s:v>
+      </s:c>
+      <s:c r="G51" s="15" t="n">
+        <s:v>5327.69</s:v>
+      </s:c>
       <s:c r="J51"/>
       <s:c r="K51"/>
       <s:c r="L51"/>
@@ -2400,10 +2800,18 @@
       <s:c r="C52" s="11" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D52" s="12"/>
-      <s:c r="E52" s="13"/>
-      <s:c r="F52" s="14"/>
-      <s:c r="G52" s="15"/>
+      <s:c r="D52" s="12" t="n">
+        <s:v>27146.6</s:v>
+      </s:c>
+      <s:c r="E52" s="13" t="n">
+        <s:v>4364.26</s:v>
+      </s:c>
+      <s:c r="F52" s="14" t="n">
+        <s:v>12386.3</s:v>
+      </s:c>
+      <s:c r="G52" s="15" t="n">
+        <s:v>5288.72</s:v>
+      </s:c>
       <s:c r="J52"/>
       <s:c r="K52"/>
       <s:c r="L52"/>
@@ -2420,10 +2828,18 @@
       <s:c r="C53" s="11" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D53" s="12"/>
-      <s:c r="E53" s="13"/>
-      <s:c r="F53" s="14"/>
-      <s:c r="G53" s="15"/>
+      <s:c r="D53" s="12" t="n">
+        <s:v>26692.4</s:v>
+      </s:c>
+      <s:c r="E53" s="13" t="n">
+        <s:v>4361.49</s:v>
+      </s:c>
+      <s:c r="F53" s="14" t="n">
+        <s:v>12265.5</s:v>
+      </s:c>
+      <s:c r="G53" s="15" t="n">
+        <s:v>5270.08</s:v>
+      </s:c>
       <s:c r="J53"/>
       <s:c r="K53"/>
       <s:c r="L53"/>
@@ -2440,10 +2856,18 @@
       <s:c r="C54" s="11" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D54" s="12"/>
-      <s:c r="E54" s="13"/>
-      <s:c r="F54" s="14"/>
-      <s:c r="G54" s="15"/>
+      <s:c r="D54" s="12" t="n">
+        <s:v>27489.5</s:v>
+      </s:c>
+      <s:c r="E54" s="13" t="n">
+        <s:v>4348.82</s:v>
+      </s:c>
+      <s:c r="F54" s="14" t="n">
+        <s:v>12121.9</s:v>
+      </s:c>
+      <s:c r="G54" s="15" t="n">
+        <s:v>5719.1</s:v>
+      </s:c>
       <s:c r="J54"/>
       <s:c r="K54"/>
       <s:c r="L54"/>
@@ -2460,10 +2884,18 @@
       <s:c r="C55" s="11" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D55" s="12"/>
-      <s:c r="E55" s="13"/>
-      <s:c r="F55" s="14"/>
-      <s:c r="G55" s="15"/>
+      <s:c r="D55" s="12" t="n">
+        <s:v>27649.7</s:v>
+      </s:c>
+      <s:c r="E55" s="13" t="n">
+        <s:v>4340.05</s:v>
+      </s:c>
+      <s:c r="F55" s="14" t="n">
+        <s:v>11953</s:v>
+      </s:c>
+      <s:c r="G55" s="15" t="n">
+        <s:v>5327.76</s:v>
+      </s:c>
       <s:c r="J55"/>
       <s:c r="K55"/>
       <s:c r="L55"/>
@@ -2480,10 +2912,18 @@
       <s:c r="C56" s="11" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D56" s="12"/>
-      <s:c r="E56" s="13"/>
-      <s:c r="F56" s="14"/>
-      <s:c r="G56" s="15"/>
+      <s:c r="D56" s="12" t="n">
+        <s:v>28154.4</s:v>
+      </s:c>
+      <s:c r="E56" s="13" t="n">
+        <s:v>4325.89</s:v>
+      </s:c>
+      <s:c r="F56" s="14" t="n">
+        <s:v>11828.6</s:v>
+      </s:c>
+      <s:c r="G56" s="15" t="n">
+        <s:v>5500.21</s:v>
+      </s:c>
       <s:c r="J56"/>
       <s:c r="K56"/>
       <s:c r="L56"/>
@@ -2500,10 +2940,18 @@
       <s:c r="C57" s="11" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D57" s="12"/>
-      <s:c r="E57" s="13"/>
-      <s:c r="F57" s="14"/>
-      <s:c r="G57" s="15"/>
+      <s:c r="D57" s="12" t="n">
+        <s:v>28288.5</s:v>
+      </s:c>
+      <s:c r="E57" s="13" t="n">
+        <s:v>4319.12</s:v>
+      </s:c>
+      <s:c r="F57" s="14" t="n">
+        <s:v>11612.3</s:v>
+      </s:c>
+      <s:c r="G57" s="15" t="n">
+        <s:v>5473.3</s:v>
+      </s:c>
       <s:c r="J57"/>
       <s:c r="K57"/>
       <s:c r="L57"/>
@@ -2520,10 +2968,18 @@
       <s:c r="C58" s="11" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D58" s="12"/>
-      <s:c r="E58" s="13"/>
-      <s:c r="F58" s="14"/>
-      <s:c r="G58" s="15"/>
+      <s:c r="D58" s="12" t="n">
+        <s:v>28816.9</s:v>
+      </s:c>
+      <s:c r="E58" s="13" t="n">
+        <s:v>4299.6</s:v>
+      </s:c>
+      <s:c r="F58" s="14" t="n">
+        <s:v>11270.2</s:v>
+      </s:c>
+      <s:c r="G58" s="15" t="n">
+        <s:v>4991.43</s:v>
+      </s:c>
       <s:c r="J58"/>
       <s:c r="K58"/>
       <s:c r="L58"/>
@@ -2540,10 +2996,18 @@
       <s:c r="C59" s="11" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D59" s="12"/>
-      <s:c r="E59" s="13"/>
-      <s:c r="F59" s="14"/>
-      <s:c r="G59" s="15"/>
+      <s:c r="D59" s="12" t="n">
+        <s:v>29054.4</s:v>
+      </s:c>
+      <s:c r="E59" s="13" t="n">
+        <s:v>4283.88</s:v>
+      </s:c>
+      <s:c r="F59" s="14" t="n">
+        <s:v>10840.8</s:v>
+      </s:c>
+      <s:c r="G59" s="15" t="n">
+        <s:v>5817.81</s:v>
+      </s:c>
       <s:c r="J59"/>
       <s:c r="K59"/>
       <s:c r="L59"/>
@@ -2560,10 +3024,18 @@
       <s:c r="C60" s="11" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D60" s="12"/>
-      <s:c r="E60" s="13"/>
-      <s:c r="F60" s="14"/>
-      <s:c r="G60" s="15"/>
+      <s:c r="D60" s="12" t="n">
+        <s:v>29697.8</s:v>
+      </s:c>
+      <s:c r="E60" s="13" t="n">
+        <s:v>4270.83</s:v>
+      </s:c>
+      <s:c r="F60" s="14" t="n">
+        <s:v>10352</s:v>
+      </s:c>
+      <s:c r="G60" s="15" t="n">
+        <s:v>5405.3</s:v>
+      </s:c>
       <s:c r="J60"/>
       <s:c r="K60"/>
       <s:c r="L60"/>
@@ -2580,10 +3052,18 @@
       <s:c r="C61" s="11" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D61" s="12"/>
-      <s:c r="E61" s="13"/>
-      <s:c r="F61" s="14"/>
-      <s:c r="G61" s="15"/>
+      <s:c r="D61" s="12" t="n">
+        <s:v>29741.5</s:v>
+      </s:c>
+      <s:c r="E61" s="13" t="n">
+        <s:v>4248.97</s:v>
+      </s:c>
+      <s:c r="F61" s="14" t="n">
+        <s:v>9864.9</s:v>
+      </s:c>
+      <s:c r="G61" s="15" t="n">
+        <s:v>5291.25</s:v>
+      </s:c>
       <s:c r="J61"/>
       <s:c r="K61"/>
       <s:c r="L61"/>
@@ -2600,10 +3080,18 @@
       <s:c r="C62" s="11" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D62" s="12"/>
-      <s:c r="E62" s="13"/>
-      <s:c r="F62" s="14"/>
-      <s:c r="G62" s="15"/>
+      <s:c r="D62" s="12" t="n">
+        <s:v>30216.2</s:v>
+      </s:c>
+      <s:c r="E62" s="13" t="n">
+        <s:v>4315.55</s:v>
+      </s:c>
+      <s:c r="F62" s="14" t="n">
+        <s:v>9300.2</s:v>
+      </s:c>
+      <s:c r="G62" s="15" t="n">
+        <s:v>5452.39</s:v>
+      </s:c>
       <s:c r="J62"/>
       <s:c r="K62"/>
       <s:c r="L62"/>
@@ -2620,10 +3108,18 @@
       <s:c r="C63" s="11" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D63" s="12"/>
-      <s:c r="E63" s="13"/>
-      <s:c r="F63" s="14"/>
-      <s:c r="G63" s="15"/>
+      <s:c r="D63" s="12" t="n">
+        <s:v>30937.5</s:v>
+      </s:c>
+      <s:c r="E63" s="13" t="n">
+        <s:v>4692.98</s:v>
+      </s:c>
+      <s:c r="F63" s="14" t="n">
+        <s:v>8299.1</s:v>
+      </s:c>
+      <s:c r="G63" s="15" t="n">
+        <s:v>5223.38</s:v>
+      </s:c>
       <s:c r="J63"/>
       <s:c r="K63"/>
       <s:c r="L63"/>
@@ -2640,10 +3136,18 @@
       <s:c r="C64" s="11" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D64" s="12"/>
-      <s:c r="E64" s="13"/>
-      <s:c r="F64" s="14"/>
-      <s:c r="G64" s="15"/>
+      <s:c r="D64" s="12" t="n">
+        <s:v>31749.9</s:v>
+      </s:c>
+      <s:c r="E64" s="13" t="n">
+        <s:v>5112.47</s:v>
+      </s:c>
+      <s:c r="F64" s="14" t="n">
+        <s:v>7580</s:v>
+      </s:c>
+      <s:c r="G64" s="15" t="n">
+        <s:v>4963.88</s:v>
+      </s:c>
       <s:c r="J64"/>
       <s:c r="K64"/>
       <s:c r="L64"/>
@@ -2660,10 +3164,18 @@
       <s:c r="C65" s="11" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D65" s="12"/>
-      <s:c r="E65" s="13"/>
-      <s:c r="F65" s="14"/>
-      <s:c r="G65" s="15"/>
+      <s:c r="D65" s="12" t="n">
+        <s:v>32906.9</s:v>
+      </s:c>
+      <s:c r="E65" s="13" t="n">
+        <s:v>5782.03</s:v>
+      </s:c>
+      <s:c r="F65" s="14" t="n">
+        <s:v>6956</s:v>
+      </s:c>
+      <s:c r="G65" s="15" t="n">
+        <s:v>5316.33</s:v>
+      </s:c>
       <s:c r="J65"/>
       <s:c r="K65"/>
       <s:c r="L65"/>
@@ -2680,10 +3192,18 @@
       <s:c r="C66" s="11" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D66" s="12"/>
-      <s:c r="E66" s="13"/>
-      <s:c r="F66" s="14"/>
-      <s:c r="G66" s="15"/>
+      <s:c r="D66" s="12" t="n">
+        <s:v>33351.2</s:v>
+      </s:c>
+      <s:c r="E66" s="13" t="n">
+        <s:v>6451.4</s:v>
+      </s:c>
+      <s:c r="F66" s="14" t="n">
+        <s:v>5847.9</s:v>
+      </s:c>
+      <s:c r="G66" s="15" t="n">
+        <s:v>6434.8</s:v>
+      </s:c>
       <s:c r="J66"/>
       <s:c r="K66"/>
       <s:c r="L66"/>
@@ -2700,10 +3220,18 @@
       <s:c r="C67" s="11" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D67" s="12"/>
-      <s:c r="E67" s="13"/>
-      <s:c r="F67" s="14"/>
-      <s:c r="G67" s="15"/>
+      <s:c r="D67" s="12" t="n">
+        <s:v>34277.6</s:v>
+      </s:c>
+      <s:c r="E67" s="13" t="n">
+        <s:v>6912.71</s:v>
+      </s:c>
+      <s:c r="F67" s="14" t="n">
+        <s:v>5178.8</s:v>
+      </s:c>
+      <s:c r="G67" s="15" t="n">
+        <s:v>6700.65</s:v>
+      </s:c>
       <s:c r="J67"/>
       <s:c r="K67"/>
       <s:c r="L67"/>
@@ -2720,10 +3248,18 @@
       <s:c r="C68" s="11" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D68" s="12"/>
-      <s:c r="E68" s="13"/>
-      <s:c r="F68" s="14"/>
-      <s:c r="G68" s="15"/>
+      <s:c r="D68" s="12" t="n">
+        <s:v>35155.4</s:v>
+      </s:c>
+      <s:c r="E68" s="13" t="n">
+        <s:v>7380.96</s:v>
+      </s:c>
+      <s:c r="F68" s="14" t="n">
+        <s:v>4388.8</s:v>
+      </s:c>
+      <s:c r="G68" s="15" t="n">
+        <s:v>7347.99</s:v>
+      </s:c>
       <s:c r="J68"/>
       <s:c r="K68"/>
       <s:c r="L68"/>
@@ -2740,10 +3276,18 @@
       <s:c r="C69" s="11" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D69" s="12"/>
-      <s:c r="E69" s="13"/>
-      <s:c r="F69" s="14"/>
-      <s:c r="G69" s="15"/>
+      <s:c r="D69" s="12" t="n">
+        <s:v>36298</s:v>
+      </s:c>
+      <s:c r="E69" s="13" t="n">
+        <s:v>7842.57</s:v>
+      </s:c>
+      <s:c r="F69" s="14" t="n">
+        <s:v>3456.4</s:v>
+      </s:c>
+      <s:c r="G69" s="15" t="n">
+        <s:v>7794.8</s:v>
+      </s:c>
       <s:c r="J69"/>
       <s:c r="K69"/>
       <s:c r="L69"/>
@@ -2760,10 +3304,18 @@
       <s:c r="C70" s="11" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D70" s="12"/>
-      <s:c r="E70" s="13"/>
-      <s:c r="F70" s="14"/>
-      <s:c r="G70" s="15"/>
+      <s:c r="D70" s="12" t="n">
+        <s:v>37111.9</s:v>
+      </s:c>
+      <s:c r="E70" s="13" t="n">
+        <s:v>8256.45</s:v>
+      </s:c>
+      <s:c r="F70" s="14" t="n">
+        <s:v>2592.9</s:v>
+      </s:c>
+      <s:c r="G70" s="15" t="n">
+        <s:v>8104.77</s:v>
+      </s:c>
       <s:c r="J70"/>
       <s:c r="K70"/>
       <s:c r="L70"/>
@@ -2780,10 +3332,18 @@
       <s:c r="C71" s="11" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D71" s="12"/>
-      <s:c r="E71" s="13"/>
-      <s:c r="F71" s="14"/>
-      <s:c r="G71" s="15"/>
+      <s:c r="D71" s="12" t="n">
+        <s:v>37784.3</s:v>
+      </s:c>
+      <s:c r="E71" s="13" t="n">
+        <s:v>8468.58</s:v>
+      </s:c>
+      <s:c r="F71" s="14" t="n">
+        <s:v>1958.8</s:v>
+      </s:c>
+      <s:c r="G71" s="15" t="n">
+        <s:v>8625.91</s:v>
+      </s:c>
       <s:c r="J71"/>
       <s:c r="K71"/>
       <s:c r="L71"/>
@@ -2800,10 +3360,18 @@
       <s:c r="C72" s="11" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D72" s="12"/>
-      <s:c r="E72" s="13"/>
-      <s:c r="F72" s="14"/>
-      <s:c r="G72" s="15"/>
+      <s:c r="D72" s="12" t="n">
+        <s:v>38378.5</s:v>
+      </s:c>
+      <s:c r="E72" s="13" t="n">
+        <s:v>8434.82</s:v>
+      </s:c>
+      <s:c r="F72" s="14" t="n">
+        <s:v>1392</s:v>
+      </s:c>
+      <s:c r="G72" s="15" t="n">
+        <s:v>9476.2</s:v>
+      </s:c>
       <s:c r="J72"/>
       <s:c r="K72"/>
       <s:c r="L72"/>
@@ -2820,10 +3388,18 @@
       <s:c r="C73" s="11" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D73" s="12"/>
-      <s:c r="E73" s="13"/>
-      <s:c r="F73" s="14"/>
-      <s:c r="G73" s="15"/>
+      <s:c r="D73" s="12" t="n">
+        <s:v>38332.7</s:v>
+      </s:c>
+      <s:c r="E73" s="13" t="n">
+        <s:v>8411.46</s:v>
+      </s:c>
+      <s:c r="F73" s="14" t="n">
+        <s:v>1021.8</s:v>
+      </s:c>
+      <s:c r="G73" s="15" t="n">
+        <s:v>10145.05</s:v>
+      </s:c>
       <s:c r="J73"/>
       <s:c r="K73"/>
       <s:c r="L73"/>
@@ -2840,10 +3416,18 @@
       <s:c r="C74" s="11" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D74" s="12"/>
-      <s:c r="E74" s="13"/>
-      <s:c r="F74" s="14"/>
-      <s:c r="G74" s="15"/>
+      <s:c r="D74" s="12" t="n">
+        <s:v>38433.1</s:v>
+      </s:c>
+      <s:c r="E74" s="13" t="n">
+        <s:v>8396.99</s:v>
+      </s:c>
+      <s:c r="F74" s="14" t="n">
+        <s:v>732.1</s:v>
+      </s:c>
+      <s:c r="G74" s="15" t="n">
+        <s:v>10965.2</s:v>
+      </s:c>
       <s:c r="J74"/>
       <s:c r="K74"/>
       <s:c r="L74"/>
@@ -2860,10 +3444,18 @@
       <s:c r="C75" s="11" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D75" s="12"/>
-      <s:c r="E75" s="13"/>
-      <s:c r="F75" s="14"/>
-      <s:c r="G75" s="15"/>
+      <s:c r="D75" s="12" t="n">
+        <s:v>38054.9</s:v>
+      </s:c>
+      <s:c r="E75" s="13" t="n">
+        <s:v>8385.13</s:v>
+      </s:c>
+      <s:c r="F75" s="14" t="n">
+        <s:v>523.4</s:v>
+      </s:c>
+      <s:c r="G75" s="15" t="n">
+        <s:v>10533.09</s:v>
+      </s:c>
       <s:c r="J75"/>
       <s:c r="K75"/>
       <s:c r="L75"/>
@@ -2880,10 +3472,18 @@
       <s:c r="C76" s="11" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D76" s="12"/>
-      <s:c r="E76" s="13"/>
-      <s:c r="F76" s="14"/>
-      <s:c r="G76" s="15"/>
+      <s:c r="D76" s="12" t="n">
+        <s:v>37921.9</s:v>
+      </s:c>
+      <s:c r="E76" s="13" t="n">
+        <s:v>8380.19</s:v>
+      </s:c>
+      <s:c r="F76" s="14" t="n">
+        <s:v>538.8</s:v>
+      </s:c>
+      <s:c r="G76" s="15" t="n">
+        <s:v>10549.47</s:v>
+      </s:c>
       <s:c r="J76"/>
       <s:c r="K76"/>
       <s:c r="L76"/>
@@ -2900,10 +3500,18 @@
       <s:c r="C77" s="11" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D77" s="12"/>
-      <s:c r="E77" s="13"/>
-      <s:c r="F77" s="14"/>
-      <s:c r="G77" s="15"/>
+      <s:c r="D77" s="12" t="n">
+        <s:v>37804.5</s:v>
+      </s:c>
+      <s:c r="E77" s="13" t="n">
+        <s:v>8378.85</s:v>
+      </s:c>
+      <s:c r="F77" s="14" t="n">
+        <s:v>602.4</s:v>
+      </s:c>
+      <s:c r="G77" s="15" t="n">
+        <s:v>10755.61</s:v>
+      </s:c>
       <s:c r="J77"/>
       <s:c r="K77"/>
       <s:c r="L77"/>
@@ -2920,10 +3528,18 @@
       <s:c r="C78" s="11" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D78" s="12"/>
-      <s:c r="E78" s="13"/>
-      <s:c r="F78" s="14"/>
-      <s:c r="G78" s="15"/>
+      <s:c r="D78" s="12" t="n">
+        <s:v>37672.4</s:v>
+      </s:c>
+      <s:c r="E78" s="13" t="n">
+        <s:v>8386.74</s:v>
+      </s:c>
+      <s:c r="F78" s="14" t="n">
+        <s:v>719.1</s:v>
+      </s:c>
+      <s:c r="G78" s="15" t="n">
+        <s:v>10609.88</s:v>
+      </s:c>
       <s:c r="J78"/>
       <s:c r="K78"/>
       <s:c r="L78"/>
@@ -2940,10 +3556,18 @@
       <s:c r="C79" s="11" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D79" s="12"/>
-      <s:c r="E79" s="13"/>
-      <s:c r="F79" s="14"/>
-      <s:c r="G79" s="15"/>
+      <s:c r="D79" s="12" t="n">
+        <s:v>37536.9</s:v>
+      </s:c>
+      <s:c r="E79" s="13" t="n">
+        <s:v>8401.35</s:v>
+      </s:c>
+      <s:c r="F79" s="14" t="n">
+        <s:v>838.1</s:v>
+      </s:c>
+      <s:c r="G79" s="15" t="n">
+        <s:v>11227.15</s:v>
+      </s:c>
       <s:c r="J79"/>
       <s:c r="K79"/>
       <s:c r="L79"/>
@@ -2960,10 +3584,18 @@
       <s:c r="C80" s="11" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D80" s="12"/>
-      <s:c r="E80" s="13"/>
-      <s:c r="F80" s="14"/>
-      <s:c r="G80" s="15"/>
+      <s:c r="D80" s="12" t="n">
+        <s:v>36640.5</s:v>
+      </s:c>
+      <s:c r="E80" s="13" t="n">
+        <s:v>8418.45</s:v>
+      </s:c>
+      <s:c r="F80" s="14" t="n">
+        <s:v>926.5</s:v>
+      </s:c>
+      <s:c r="G80" s="15" t="n">
+        <s:v>10628.49</s:v>
+      </s:c>
       <s:c r="J80"/>
       <s:c r="K80"/>
       <s:c r="L80"/>
@@ -2980,10 +3612,18 @@
       <s:c r="C81" s="11" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D81" s="12"/>
-      <s:c r="E81" s="13"/>
-      <s:c r="F81" s="14"/>
-      <s:c r="G81" s="15"/>
+      <s:c r="D81" s="12" t="n">
+        <s:v>36683.7</s:v>
+      </s:c>
+      <s:c r="E81" s="13" t="n">
+        <s:v>8436.26</s:v>
+      </s:c>
+      <s:c r="F81" s="14" t="n">
+        <s:v>952.8</s:v>
+      </s:c>
+      <s:c r="G81" s="15" t="n">
+        <s:v>10737.62</s:v>
+      </s:c>
       <s:c r="J81"/>
       <s:c r="K81"/>
       <s:c r="L81"/>
@@ -3000,10 +3640,18 @@
       <s:c r="C82" s="11" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D82" s="12"/>
-      <s:c r="E82" s="13"/>
-      <s:c r="F82" s="14"/>
-      <s:c r="G82" s="15"/>
+      <s:c r="D82" s="12" t="n">
+        <s:v>36478.7</s:v>
+      </s:c>
+      <s:c r="E82" s="13" t="n">
+        <s:v>8432.15</s:v>
+      </s:c>
+      <s:c r="F82" s="14" t="n">
+        <s:v>966.5</s:v>
+      </s:c>
+      <s:c r="G82" s="15" t="n">
+        <s:v>11002.8</s:v>
+      </s:c>
       <s:c r="J82"/>
       <s:c r="K82"/>
       <s:c r="L82"/>
@@ -3020,10 +3668,18 @@
       <s:c r="C83" s="11" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D83" s="12"/>
-      <s:c r="E83" s="13"/>
-      <s:c r="F83" s="14"/>
-      <s:c r="G83" s="15"/>
+      <s:c r="D83" s="12" t="n">
+        <s:v>35943.5</s:v>
+      </s:c>
+      <s:c r="E83" s="13" t="n">
+        <s:v>8430.89</s:v>
+      </s:c>
+      <s:c r="F83" s="14" t="n">
+        <s:v>939.1</s:v>
+      </s:c>
+      <s:c r="G83" s="15" t="n">
+        <s:v>10458.93</s:v>
+      </s:c>
       <s:c r="J83"/>
       <s:c r="K83"/>
       <s:c r="L83"/>
@@ -3040,10 +3696,18 @@
       <s:c r="C84" s="11" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D84" s="12"/>
-      <s:c r="E84" s="13"/>
-      <s:c r="F84" s="14"/>
-      <s:c r="G84" s="15"/>
+      <s:c r="D84" s="12" t="n">
+        <s:v>35996.9</s:v>
+      </s:c>
+      <s:c r="E84" s="13" t="n">
+        <s:v>8429.68</s:v>
+      </s:c>
+      <s:c r="F84" s="14" t="n">
+        <s:v>938.2</s:v>
+      </s:c>
+      <s:c r="G84" s="15" t="n">
+        <s:v>10968.23</s:v>
+      </s:c>
       <s:c r="J84"/>
       <s:c r="K84"/>
       <s:c r="L84"/>
@@ -3060,10 +3724,18 @@
       <s:c r="C85" s="11" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D85" s="12"/>
-      <s:c r="E85" s="13"/>
-      <s:c r="F85" s="14"/>
-      <s:c r="G85" s="15"/>
+      <s:c r="D85" s="12" t="n">
+        <s:v>35405.6</s:v>
+      </s:c>
+      <s:c r="E85" s="13" t="n">
+        <s:v>8428.67</s:v>
+      </s:c>
+      <s:c r="F85" s="14" t="n">
+        <s:v>963.3</s:v>
+      </s:c>
+      <s:c r="G85" s="15" t="n">
+        <s:v>10545.02</s:v>
+      </s:c>
       <s:c r="J85"/>
       <s:c r="K85"/>
       <s:c r="L85"/>
@@ -3080,10 +3752,18 @@
       <s:c r="C86" s="11" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D86" s="12"/>
-      <s:c r="E86" s="13"/>
-      <s:c r="F86" s="14"/>
-      <s:c r="G86" s="15"/>
+      <s:c r="D86" s="12" t="n">
+        <s:v>35153.8</s:v>
+      </s:c>
+      <s:c r="E86" s="13" t="n">
+        <s:v>8401.38</s:v>
+      </s:c>
+      <s:c r="F86" s="14" t="n">
+        <s:v>984.6</s:v>
+      </s:c>
+      <s:c r="G86" s="15" t="n">
+        <s:v>10811.5</s:v>
+      </s:c>
       <s:c r="J86"/>
       <s:c r="K86"/>
       <s:c r="L86"/>
@@ -3100,10 +3780,18 @@
       <s:c r="C87" s="11" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D87" s="12"/>
-      <s:c r="E87" s="13"/>
-      <s:c r="F87" s="14"/>
-      <s:c r="G87" s="15"/>
+      <s:c r="D87" s="12" t="n">
+        <s:v>34895.6</s:v>
+      </s:c>
+      <s:c r="E87" s="13" t="n">
+        <s:v>8389.77</s:v>
+      </s:c>
+      <s:c r="F87" s="14" t="n">
+        <s:v>1043.5</s:v>
+      </s:c>
+      <s:c r="G87" s="15" t="n">
+        <s:v>10038.24</s:v>
+      </s:c>
       <s:c r="J87"/>
       <s:c r="K87"/>
       <s:c r="L87"/>
@@ -3120,10 +3808,18 @@
       <s:c r="C88" s="11" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D88" s="12"/>
-      <s:c r="E88" s="13"/>
-      <s:c r="F88" s="14"/>
-      <s:c r="G88" s="15"/>
+      <s:c r="D88" s="12" t="n">
+        <s:v>34332.3</s:v>
+      </s:c>
+      <s:c r="E88" s="13" t="n">
+        <s:v>8379.44</s:v>
+      </s:c>
+      <s:c r="F88" s="14" t="n">
+        <s:v>1037</s:v>
+      </s:c>
+      <s:c r="G88" s="15" t="n">
+        <s:v>9520.22</s:v>
+      </s:c>
       <s:c r="J88"/>
       <s:c r="K88"/>
       <s:c r="L88"/>
@@ -3140,10 +3836,18 @@
       <s:c r="C89" s="11" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D89" s="12"/>
-      <s:c r="E89" s="13"/>
-      <s:c r="F89" s="14"/>
-      <s:c r="G89" s="15"/>
+      <s:c r="D89" s="12" t="n">
+        <s:v>33689.7</s:v>
+      </s:c>
+      <s:c r="E89" s="13" t="n">
+        <s:v>8369.55</s:v>
+      </s:c>
+      <s:c r="F89" s="14" t="n">
+        <s:v>952.3</s:v>
+      </s:c>
+      <s:c r="G89" s="15" t="n">
+        <s:v>9429.58</s:v>
+      </s:c>
       <s:c r="J89"/>
       <s:c r="K89"/>
       <s:c r="L89"/>
@@ -3160,10 +3864,18 @@
       <s:c r="C90" s="11" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D90" s="12"/>
-      <s:c r="E90" s="13"/>
-      <s:c r="F90" s="14"/>
-      <s:c r="G90" s="15"/>
+      <s:c r="D90" s="12" t="n">
+        <s:v>33376.1</s:v>
+      </s:c>
+      <s:c r="E90" s="13" t="n">
+        <s:v>8319.07</s:v>
+      </s:c>
+      <s:c r="F90" s="14" t="n">
+        <s:v>851.8</s:v>
+      </s:c>
+      <s:c r="G90" s="15" t="n">
+        <s:v>8708.48</s:v>
+      </s:c>
       <s:c r="J90"/>
       <s:c r="K90"/>
       <s:c r="L90"/>
@@ -3180,10 +3892,18 @@
       <s:c r="C91" s="11" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D91" s="12"/>
-      <s:c r="E91" s="13"/>
-      <s:c r="F91" s="14"/>
-      <s:c r="G91" s="15"/>
+      <s:c r="D91" s="12" t="n">
+        <s:v>32889.9</s:v>
+      </s:c>
+      <s:c r="E91" s="13" t="n">
+        <s:v>8317.69</s:v>
+      </s:c>
+      <s:c r="F91" s="14" t="n">
+        <s:v>955.8</s:v>
+      </s:c>
+      <s:c r="G91" s="15" t="n">
+        <s:v>8065.55</s:v>
+      </s:c>
       <s:c r="J91"/>
       <s:c r="K91"/>
       <s:c r="L91"/>
@@ -3200,10 +3920,18 @@
       <s:c r="C92" s="11" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D92" s="12"/>
-      <s:c r="E92" s="13"/>
-      <s:c r="F92" s="14"/>
-      <s:c r="G92" s="15"/>
+      <s:c r="D92" s="12" t="n">
+        <s:v>32352.3</s:v>
+      </s:c>
+      <s:c r="E92" s="13" t="n">
+        <s:v>8315.49</s:v>
+      </s:c>
+      <s:c r="F92" s="14" t="n">
+        <s:v>1090</s:v>
+      </s:c>
+      <s:c r="G92" s="15" t="n">
+        <s:v>7659.22</s:v>
+      </s:c>
       <s:c r="J92"/>
       <s:c r="K92"/>
       <s:c r="L92"/>
@@ -3220,10 +3948,18 @@
       <s:c r="C93" s="11" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D93" s="12"/>
-      <s:c r="E93" s="13"/>
-      <s:c r="F93" s="14"/>
-      <s:c r="G93" s="15"/>
+      <s:c r="D93" s="12" t="n">
+        <s:v>31691.8</s:v>
+      </s:c>
+      <s:c r="E93" s="13" t="n">
+        <s:v>8313.56</s:v>
+      </s:c>
+      <s:c r="F93" s="14" t="n">
+        <s:v>1127.1</s:v>
+      </s:c>
+      <s:c r="G93" s="15" t="n">
+        <s:v>6963.52</s:v>
+      </s:c>
       <s:c r="J93"/>
       <s:c r="K93"/>
       <s:c r="L93"/>
@@ -3240,10 +3976,18 @@
       <s:c r="C94" s="11" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D94" s="12"/>
-      <s:c r="E94" s="13"/>
-      <s:c r="F94" s="14"/>
-      <s:c r="G94" s="15"/>
+      <s:c r="D94" s="12" t="n">
+        <s:v>30965.8</s:v>
+      </s:c>
+      <s:c r="E94" s="13" t="n">
+        <s:v>8311.97</s:v>
+      </s:c>
+      <s:c r="F94" s="14" t="n">
+        <s:v>1138.5</s:v>
+      </s:c>
+      <s:c r="G94" s="15" t="n">
+        <s:v>6720.41</s:v>
+      </s:c>
       <s:c r="J94"/>
       <s:c r="K94"/>
       <s:c r="L94"/>
@@ -3260,10 +4004,18 @@
       <s:c r="C95" s="11" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D95" s="12"/>
-      <s:c r="E95" s="13"/>
-      <s:c r="F95" s="14"/>
-      <s:c r="G95" s="15"/>
+      <s:c r="D95" s="12" t="n">
+        <s:v>30412.7</s:v>
+      </s:c>
+      <s:c r="E95" s="13" t="n">
+        <s:v>8308.31</s:v>
+      </s:c>
+      <s:c r="F95" s="14" t="n">
+        <s:v>1139.6</s:v>
+      </s:c>
+      <s:c r="G95" s="15" t="n">
+        <s:v>6237.13</s:v>
+      </s:c>
       <s:c r="J95"/>
       <s:c r="K95"/>
       <s:c r="L95"/>
@@ -3280,10 +4032,18 @@
       <s:c r="C96" s="11" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D96" s="12"/>
-      <s:c r="E96" s="13"/>
-      <s:c r="F96" s="14"/>
-      <s:c r="G96" s="15"/>
+      <s:c r="D96" s="12" t="n">
+        <s:v>29745.3</s:v>
+      </s:c>
+      <s:c r="E96" s="13" t="n">
+        <s:v>8304.56</s:v>
+      </s:c>
+      <s:c r="F96" s="14" t="n">
+        <s:v>1154.6</s:v>
+      </s:c>
+      <s:c r="G96" s="15" t="n">
+        <s:v>5858.18</s:v>
+      </s:c>
       <s:c r="J96"/>
       <s:c r="K96"/>
       <s:c r="L96"/>
@@ -3302,10 +4062,18 @@
       <s:c r="C97" s="11" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D97" s="12"/>
-      <s:c r="E97" s="13"/>
-      <s:c r="F97" s="14"/>
-      <s:c r="G97" s="15"/>
+      <s:c r="D97" s="12" t="n">
+        <s:v>29764.5</s:v>
+      </s:c>
+      <s:c r="E97" s="13" t="n">
+        <s:v>8300.64</s:v>
+      </s:c>
+      <s:c r="F97" s="14" t="n">
+        <s:v>1110.6</s:v>
+      </s:c>
+      <s:c r="G97" s="15" t="n">
+        <s:v>5668.7</s:v>
+      </s:c>
       <s:c r="J97"/>
       <s:c r="K97"/>
       <s:c r="L97"/>
@@ -3518,17 +4286,39 @@
       </s:c>
       <s:c r="D2" s="1"/>
       <s:c r="E2" s="1"/>
-      <s:c r="F2" s="1"/>
-      <s:c r="G2" s="1"/>
-      <s:c r="H2" s="1"/>
-      <s:c r="I2" s="1"/>
-      <s:c r="J2" s="1"/>
-      <s:c r="K2" s="1"/>
-      <s:c r="L2" s="1"/>
-      <s:c r="M2" s="1"/>
-      <s:c r="N2" s="1"/>
-      <s:c r="O2" s="1"/>
-      <s:c r="P2" s="1"/>
+      <s:c r="F2" s="1" t="n">
+        <s:v>630</s:v>
+      </s:c>
+      <s:c r="G2" s="1" t="n">
+        <s:v>2345.07</s:v>
+      </s:c>
+      <s:c r="H2" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I2" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L2" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N2" s="1" t="n">
+        <s:v>19405.83</s:v>
+      </s:c>
+      <s:c r="O2" s="1" t="n">
+        <s:v>1010.74</s:v>
+      </s:c>
+      <s:c r="P2" s="1" t="n">
+        <s:v>67</s:v>
+      </s:c>
     </s:row>
     <s:row r="3" s="1" customFormat="1" spans="1:16">
       <s:c r="A3" s="6" t="n">
@@ -3542,17 +4332,39 @@
       </s:c>
       <s:c r="D3" s="1"/>
       <s:c r="E3" s="1"/>
-      <s:c r="F3" s="1"/>
-      <s:c r="G3" s="1"/>
-      <s:c r="H3" s="1"/>
-      <s:c r="I3" s="1"/>
-      <s:c r="J3" s="1"/>
-      <s:c r="K3" s="1"/>
-      <s:c r="L3" s="1"/>
-      <s:c r="M3" s="1"/>
-      <s:c r="N3" s="1"/>
-      <s:c r="O3" s="1"/>
-      <s:c r="P3" s="1"/>
+      <s:c r="F3" s="1" t="n">
+        <s:v>970</s:v>
+      </s:c>
+      <s:c r="G3" s="1" t="n">
+        <s:v>2367.37</s:v>
+      </s:c>
+      <s:c r="H3" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I3" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L3" s="1" t="n">
+        <s:v>398.78</s:v>
+      </s:c>
+      <s:c r="M3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N3" s="1" t="n">
+        <s:v>19700.81</s:v>
+      </s:c>
+      <s:c r="O3" s="1" t="n">
+        <s:v>998.43</s:v>
+      </s:c>
+      <s:c r="P3" s="1" t="n">
+        <s:v>67</s:v>
+      </s:c>
     </s:row>
     <s:row r="4" s="1" customFormat="1" spans="1:16">
       <s:c r="A4" s="6" t="n">
@@ -3566,17 +4378,39 @@
       </s:c>
       <s:c r="D4" s="1"/>
       <s:c r="E4" s="1"/>
-      <s:c r="F4" s="1"/>
-      <s:c r="G4" s="1"/>
-      <s:c r="H4" s="1"/>
-      <s:c r="I4" s="1"/>
-      <s:c r="J4" s="1"/>
-      <s:c r="K4" s="1"/>
-      <s:c r="L4" s="1"/>
-      <s:c r="M4" s="1"/>
-      <s:c r="N4" s="1"/>
-      <s:c r="O4" s="1"/>
-      <s:c r="P4" s="1"/>
+      <s:c r="F4" s="1" t="n">
+        <s:v>1030</s:v>
+      </s:c>
+      <s:c r="G4" s="1" t="n">
+        <s:v>2318.76</s:v>
+      </s:c>
+      <s:c r="H4" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I4" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J4" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K4" s="1" t="n">
+        <s:v>148.7</s:v>
+      </s:c>
+      <s:c r="L4" s="1" t="n">
+        <s:v>389.6</s:v>
+      </s:c>
+      <s:c r="M4" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N4" s="1" t="n">
+        <s:v>19351.94</s:v>
+      </s:c>
+      <s:c r="O4" s="1" t="n">
+        <s:v>1029.28</s:v>
+      </s:c>
+      <s:c r="P4" s="1" t="n">
+        <s:v>67</s:v>
+      </s:c>
     </s:row>
     <s:row r="5" s="1" customFormat="1" spans="1:16">
       <s:c r="A5" s="6" t="n">
@@ -3590,17 +4424,39 @@
       </s:c>
       <s:c r="D5" s="1"/>
       <s:c r="E5" s="1"/>
-      <s:c r="F5" s="1"/>
-      <s:c r="G5" s="1"/>
-      <s:c r="H5" s="1"/>
-      <s:c r="I5" s="1"/>
-      <s:c r="J5" s="1"/>
-      <s:c r="K5" s="1"/>
-      <s:c r="L5" s="1"/>
-      <s:c r="M5" s="1"/>
-      <s:c r="N5" s="1"/>
-      <s:c r="O5" s="1"/>
-      <s:c r="P5" s="1"/>
+      <s:c r="F5" s="1" t="n">
+        <s:v>970</s:v>
+      </s:c>
+      <s:c r="G5" s="1" t="n">
+        <s:v>2339.66</s:v>
+      </s:c>
+      <s:c r="H5" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I5" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J5" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K5" s="1" t="n">
+        <s:v>148.6</s:v>
+      </s:c>
+      <s:c r="L5" s="1" t="n">
+        <s:v>389.91</s:v>
+      </s:c>
+      <s:c r="M5" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N5" s="1" t="n">
+        <s:v>19434.83</s:v>
+      </s:c>
+      <s:c r="O5" s="1" t="n">
+        <s:v>1022.42</s:v>
+      </s:c>
+      <s:c r="P5" s="1" t="n">
+        <s:v>67</s:v>
+      </s:c>
     </s:row>
     <s:row r="6" s="1" customFormat="1" spans="1:16">
       <s:c r="A6" s="6" t="n">
@@ -3614,17 +4470,39 @@
       </s:c>
       <s:c r="D6" s="1"/>
       <s:c r="E6" s="1"/>
-      <s:c r="F6" s="1"/>
-      <s:c r="G6" s="1"/>
-      <s:c r="H6" s="1"/>
-      <s:c r="I6" s="1"/>
-      <s:c r="J6" s="1"/>
-      <s:c r="K6" s="1"/>
-      <s:c r="L6" s="1"/>
-      <s:c r="M6" s="1"/>
-      <s:c r="N6" s="1"/>
-      <s:c r="O6" s="1"/>
-      <s:c r="P6" s="1"/>
+      <s:c r="F6" s="1" t="n">
+        <s:v>260</s:v>
+      </s:c>
+      <s:c r="G6" s="1" t="n">
+        <s:v>2339.73</s:v>
+      </s:c>
+      <s:c r="H6" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I6" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J6" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K6" s="1" t="n">
+        <s:v>149.4</s:v>
+      </s:c>
+      <s:c r="L6" s="1" t="n">
+        <s:v>391.81</s:v>
+      </s:c>
+      <s:c r="M6" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N6" s="1" t="n">
+        <s:v>20319.01</s:v>
+      </s:c>
+      <s:c r="O6" s="1" t="n">
+        <s:v>912.66</s:v>
+      </s:c>
+      <s:c r="P6" s="1" t="n">
+        <s:v>67</s:v>
+      </s:c>
     </s:row>
     <s:row r="7" s="1" customFormat="1" spans="1:16">
       <s:c r="A7" s="6" t="n">
@@ -3638,17 +4516,39 @@
       </s:c>
       <s:c r="D7" s="1"/>
       <s:c r="E7" s="1"/>
-      <s:c r="F7" s="1"/>
-      <s:c r="G7" s="1"/>
-      <s:c r="H7" s="1"/>
-      <s:c r="I7" s="1"/>
-      <s:c r="J7" s="1"/>
-      <s:c r="K7" s="1"/>
-      <s:c r="L7" s="1"/>
-      <s:c r="M7" s="1"/>
-      <s:c r="N7" s="1"/>
-      <s:c r="O7" s="1"/>
-      <s:c r="P7" s="1"/>
+      <s:c r="F7" s="1" t="n">
+        <s:v>200</s:v>
+      </s:c>
+      <s:c r="G7" s="1" t="n">
+        <s:v>2343.05</s:v>
+      </s:c>
+      <s:c r="H7" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I7" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J7" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K7" s="1" t="n">
+        <s:v>148.7</s:v>
+      </s:c>
+      <s:c r="L7" s="1" t="n">
+        <s:v>388.96</s:v>
+      </s:c>
+      <s:c r="M7" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N7" s="1" t="n">
+        <s:v>19587.92</s:v>
+      </s:c>
+      <s:c r="O7" s="1" t="n">
+        <s:v>850.37</s:v>
+      </s:c>
+      <s:c r="P7" s="1" t="n">
+        <s:v>67</s:v>
+      </s:c>
     </s:row>
     <s:row r="8" s="1" customFormat="1" spans="1:16">
       <s:c r="A8" s="6" t="n">
@@ -3662,17 +4562,39 @@
       </s:c>
       <s:c r="D8" s="1"/>
       <s:c r="E8" s="1"/>
-      <s:c r="F8" s="1"/>
-      <s:c r="G8" s="1"/>
-      <s:c r="H8" s="1"/>
-      <s:c r="I8" s="1"/>
-      <s:c r="J8" s="1"/>
-      <s:c r="K8" s="1"/>
-      <s:c r="L8" s="1"/>
-      <s:c r="M8" s="1"/>
-      <s:c r="N8" s="1"/>
-      <s:c r="O8" s="1"/>
-      <s:c r="P8" s="1"/>
+      <s:c r="F8" s="1" t="n">
+        <s:v>250</s:v>
+      </s:c>
+      <s:c r="G8" s="1" t="n">
+        <s:v>2285.28</s:v>
+      </s:c>
+      <s:c r="H8" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I8" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J8" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K8" s="1" t="n">
+        <s:v>149.8</s:v>
+      </s:c>
+      <s:c r="L8" s="1" t="n">
+        <s:v>390.23</s:v>
+      </s:c>
+      <s:c r="M8" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N8" s="1" t="n">
+        <s:v>19140.45</s:v>
+      </s:c>
+      <s:c r="O8" s="1" t="n">
+        <s:v>838.25</s:v>
+      </s:c>
+      <s:c r="P8" s="1" t="n">
+        <s:v>67</s:v>
+      </s:c>
     </s:row>
     <s:row r="9" s="1" customFormat="1" spans="1:16">
       <s:c r="A9" s="6" t="n">
@@ -3686,17 +4608,39 @@
       </s:c>
       <s:c r="D9" s="1"/>
       <s:c r="E9" s="1"/>
-      <s:c r="F9" s="1"/>
-      <s:c r="G9" s="1"/>
-      <s:c r="H9" s="1"/>
-      <s:c r="I9" s="1"/>
-      <s:c r="J9" s="1"/>
-      <s:c r="K9" s="1"/>
-      <s:c r="L9" s="1"/>
-      <s:c r="M9" s="1"/>
-      <s:c r="N9" s="1"/>
-      <s:c r="O9" s="1"/>
-      <s:c r="P9" s="1"/>
+      <s:c r="F9" s="1" t="n">
+        <s:v>560</s:v>
+      </s:c>
+      <s:c r="G9" s="1" t="n">
+        <s:v>2273.32</s:v>
+      </s:c>
+      <s:c r="H9" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I9" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J9" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K9" s="1" t="n">
+        <s:v>149.4</s:v>
+      </s:c>
+      <s:c r="L9" s="1" t="n">
+        <s:v>389.6</s:v>
+      </s:c>
+      <s:c r="M9" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N9" s="1" t="n">
+        <s:v>19550.08</s:v>
+      </s:c>
+      <s:c r="O9" s="1" t="n">
+        <s:v>804.61</s:v>
+      </s:c>
+      <s:c r="P9" s="1" t="n">
+        <s:v>67</s:v>
+      </s:c>
     </s:row>
     <s:row r="10" s="1" customFormat="1" spans="1:16">
       <s:c r="A10" s="6" t="n">
@@ -3710,17 +4654,39 @@
       </s:c>
       <s:c r="D10" s="1"/>
       <s:c r="E10" s="1"/>
-      <s:c r="F10" s="1"/>
-      <s:c r="G10" s="1"/>
-      <s:c r="H10" s="1"/>
-      <s:c r="I10" s="1"/>
-      <s:c r="J10" s="1"/>
-      <s:c r="K10" s="1"/>
-      <s:c r="L10" s="1"/>
-      <s:c r="M10" s="1"/>
-      <s:c r="N10" s="1"/>
-      <s:c r="O10" s="1"/>
-      <s:c r="P10" s="1"/>
+      <s:c r="F10" s="1" t="n">
+        <s:v>1530</s:v>
+      </s:c>
+      <s:c r="G10" s="1" t="n">
+        <s:v>2260.95</s:v>
+      </s:c>
+      <s:c r="H10" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I10" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J10" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K10" s="1" t="n">
+        <s:v>419.9</s:v>
+      </s:c>
+      <s:c r="L10" s="1" t="n">
+        <s:v>389.6</s:v>
+      </s:c>
+      <s:c r="M10" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N10" s="1" t="n">
+        <s:v>18740.92</s:v>
+      </s:c>
+      <s:c r="O10" s="1" t="n">
+        <s:v>705.86</s:v>
+      </s:c>
+      <s:c r="P10" s="1" t="n">
+        <s:v>67</s:v>
+      </s:c>
     </s:row>
     <s:row r="11" s="1" customFormat="1" spans="1:16">
       <s:c r="A11" s="6" t="n">
@@ -3734,17 +4700,39 @@
       </s:c>
       <s:c r="D11" s="1"/>
       <s:c r="E11" s="1"/>
-      <s:c r="F11" s="1"/>
-      <s:c r="G11" s="1"/>
-      <s:c r="H11" s="1"/>
-      <s:c r="I11" s="1"/>
-      <s:c r="J11" s="1"/>
-      <s:c r="K11" s="1"/>
-      <s:c r="L11" s="1"/>
-      <s:c r="M11" s="1"/>
-      <s:c r="N11" s="1"/>
-      <s:c r="O11" s="1"/>
-      <s:c r="P11" s="1"/>
+      <s:c r="F11" s="1" t="n">
+        <s:v>1850</s:v>
+      </s:c>
+      <s:c r="G11" s="1" t="n">
+        <s:v>2275.41</s:v>
+      </s:c>
+      <s:c r="H11" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I11" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J11" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K11" s="1" t="n">
+        <s:v>599.3</s:v>
+      </s:c>
+      <s:c r="L11" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M11" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N11" s="1" t="n">
+        <s:v>19757.4</s:v>
+      </s:c>
+      <s:c r="O11" s="1" t="n">
+        <s:v>617.9</s:v>
+      </s:c>
+      <s:c r="P11" s="1" t="n">
+        <s:v>67</s:v>
+      </s:c>
     </s:row>
     <s:row r="12" s="1" customFormat="1" spans="1:16">
       <s:c r="A12" s="6" t="n">
@@ -3758,17 +4746,39 @@
       </s:c>
       <s:c r="D12" s="1"/>
       <s:c r="E12" s="1"/>
-      <s:c r="F12" s="1"/>
-      <s:c r="G12" s="1"/>
-      <s:c r="H12" s="1"/>
-      <s:c r="I12" s="1"/>
-      <s:c r="J12" s="1"/>
-      <s:c r="K12" s="1"/>
-      <s:c r="L12" s="1"/>
-      <s:c r="M12" s="1"/>
-      <s:c r="N12" s="1"/>
-      <s:c r="O12" s="1"/>
-      <s:c r="P12" s="1"/>
+      <s:c r="F12" s="1" t="n">
+        <s:v>1740</s:v>
+      </s:c>
+      <s:c r="G12" s="1" t="n">
+        <s:v>2249.82</s:v>
+      </s:c>
+      <s:c r="H12" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I12" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J12" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K12" s="1" t="n">
+        <s:v>598.6</s:v>
+      </s:c>
+      <s:c r="L12" s="1" t="n">
+        <s:v>396.25</s:v>
+      </s:c>
+      <s:c r="M12" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N12" s="1" t="n">
+        <s:v>19337.89</s:v>
+      </s:c>
+      <s:c r="O12" s="1" t="n">
+        <s:v>555.87</s:v>
+      </s:c>
+      <s:c r="P12" s="1" t="n">
+        <s:v>67</s:v>
+      </s:c>
     </s:row>
     <s:row r="13" s="1" customFormat="1" spans="1:16">
       <s:c r="A13" s="6" t="n">
@@ -3782,17 +4792,39 @@
       </s:c>
       <s:c r="D13" s="1"/>
       <s:c r="E13" s="1"/>
-      <s:c r="F13" s="1"/>
-      <s:c r="G13" s="1"/>
-      <s:c r="H13" s="1"/>
-      <s:c r="I13" s="1"/>
-      <s:c r="J13" s="1"/>
-      <s:c r="K13" s="1"/>
-      <s:c r="L13" s="1"/>
-      <s:c r="M13" s="1"/>
-      <s:c r="N13" s="1"/>
-      <s:c r="O13" s="1"/>
-      <s:c r="P13" s="1"/>
+      <s:c r="F13" s="1" t="n">
+        <s:v>1400</s:v>
+      </s:c>
+      <s:c r="G13" s="1" t="n">
+        <s:v>2255.7</s:v>
+      </s:c>
+      <s:c r="H13" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I13" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J13" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K13" s="1" t="n">
+        <s:v>597.6</s:v>
+      </s:c>
+      <s:c r="L13" s="1" t="n">
+        <s:v>389.6</s:v>
+      </s:c>
+      <s:c r="M13" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N13" s="1" t="n">
+        <s:v>19214.19</s:v>
+      </s:c>
+      <s:c r="O13" s="1" t="n">
+        <s:v>533.44</s:v>
+      </s:c>
+      <s:c r="P13" s="1" t="n">
+        <s:v>67</s:v>
+      </s:c>
     </s:row>
     <s:row r="14" s="1" customFormat="1" spans="1:16">
       <s:c r="A14" s="6" t="n">
@@ -3806,17 +4838,39 @@
       </s:c>
       <s:c r="D14" s="1"/>
       <s:c r="E14" s="1"/>
-      <s:c r="F14" s="1"/>
-      <s:c r="G14" s="1"/>
-      <s:c r="H14" s="1"/>
-      <s:c r="I14" s="1"/>
-      <s:c r="J14" s="1"/>
-      <s:c r="K14" s="1"/>
-      <s:c r="L14" s="1"/>
-      <s:c r="M14" s="1"/>
-      <s:c r="N14" s="1"/>
-      <s:c r="O14" s="1"/>
-      <s:c r="P14" s="1"/>
+      <s:c r="F14" s="1" t="n">
+        <s:v>480</s:v>
+      </s:c>
+      <s:c r="G14" s="1" t="n">
+        <s:v>2302.83</s:v>
+      </s:c>
+      <s:c r="H14" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I14" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K14" s="1" t="n">
+        <s:v>900.8</s:v>
+      </s:c>
+      <s:c r="L14" s="1" t="n">
+        <s:v>388.65</s:v>
+      </s:c>
+      <s:c r="M14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N14" s="1" t="n">
+        <s:v>19568.97</s:v>
+      </s:c>
+      <s:c r="O14" s="1" t="n">
+        <s:v>520.55</s:v>
+      </s:c>
+      <s:c r="P14" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="15" s="1" customFormat="1" spans="1:16">
       <s:c r="A15" s="6" t="n">
@@ -3830,17 +4884,39 @@
       </s:c>
       <s:c r="D15" s="1"/>
       <s:c r="E15" s="1"/>
-      <s:c r="F15" s="1"/>
-      <s:c r="G15" s="1"/>
-      <s:c r="H15" s="1"/>
-      <s:c r="I15" s="1"/>
-      <s:c r="J15" s="1"/>
-      <s:c r="K15" s="1"/>
-      <s:c r="L15" s="1"/>
-      <s:c r="M15" s="1"/>
-      <s:c r="N15" s="1"/>
-      <s:c r="O15" s="1"/>
-      <s:c r="P15" s="1"/>
+      <s:c r="F15" s="1" t="n">
+        <s:v>240</s:v>
+      </s:c>
+      <s:c r="G15" s="1" t="n">
+        <s:v>2302.7</s:v>
+      </s:c>
+      <s:c r="H15" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I15" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K15" s="1" t="n">
+        <s:v>898.3</s:v>
+      </s:c>
+      <s:c r="L15" s="1" t="n">
+        <s:v>389.91</s:v>
+      </s:c>
+      <s:c r="M15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N15" s="1" t="n">
+        <s:v>19815.32</s:v>
+      </s:c>
+      <s:c r="O15" s="1" t="n">
+        <s:v>474.88</s:v>
+      </s:c>
+      <s:c r="P15" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="16" s="1" customFormat="1" spans="1:16">
       <s:c r="A16" s="6" t="n">
@@ -3854,17 +4930,39 @@
       </s:c>
       <s:c r="D16" s="1"/>
       <s:c r="E16" s="1"/>
-      <s:c r="F16" s="1"/>
-      <s:c r="G16" s="1"/>
-      <s:c r="H16" s="1"/>
-      <s:c r="I16" s="1"/>
-      <s:c r="J16" s="1"/>
-      <s:c r="K16" s="1"/>
-      <s:c r="L16" s="1"/>
-      <s:c r="M16" s="1"/>
-      <s:c r="N16" s="1"/>
-      <s:c r="O16" s="1"/>
-      <s:c r="P16" s="1"/>
+      <s:c r="F16" s="1" t="n">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="G16" s="1" t="n">
+        <s:v>2303.56</s:v>
+      </s:c>
+      <s:c r="H16" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I16" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K16" s="1" t="n">
+        <s:v>1093.6</s:v>
+      </s:c>
+      <s:c r="L16" s="1" t="n">
+        <s:v>389.28</s:v>
+      </s:c>
+      <s:c r="M16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N16" s="1" t="n">
+        <s:v>19874.79</s:v>
+      </s:c>
+      <s:c r="O16" s="1" t="n">
+        <s:v>415.77</s:v>
+      </s:c>
+      <s:c r="P16" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="17" s="1" customFormat="1" spans="1:16">
       <s:c r="A17" s="6" t="n">
@@ -3878,17 +4976,39 @@
       </s:c>
       <s:c r="D17" s="1"/>
       <s:c r="E17" s="1"/>
-      <s:c r="F17" s="1"/>
-      <s:c r="G17" s="1"/>
-      <s:c r="H17" s="1"/>
-      <s:c r="I17" s="1"/>
-      <s:c r="J17" s="1"/>
-      <s:c r="K17" s="1"/>
-      <s:c r="L17" s="1"/>
-      <s:c r="M17" s="1"/>
-      <s:c r="N17" s="1"/>
-      <s:c r="O17" s="1"/>
-      <s:c r="P17" s="1"/>
+      <s:c r="F17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G17" s="1" t="n">
+        <s:v>2332.96</s:v>
+      </s:c>
+      <s:c r="H17" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I17" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K17" s="1" t="n">
+        <s:v>1089.7</s:v>
+      </s:c>
+      <s:c r="L17" s="1" t="n">
+        <s:v>389.91</s:v>
+      </s:c>
+      <s:c r="M17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N17" s="1" t="n">
+        <s:v>19924.37</s:v>
+      </s:c>
+      <s:c r="O17" s="1" t="n">
+        <s:v>381.47</s:v>
+      </s:c>
+      <s:c r="P17" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="18" s="1" customFormat="1" spans="1:16">
       <s:c r="A18" s="6" t="n">
@@ -3902,17 +5022,39 @@
       </s:c>
       <s:c r="D18" s="1"/>
       <s:c r="E18" s="1"/>
-      <s:c r="F18" s="1"/>
-      <s:c r="G18" s="1"/>
-      <s:c r="H18" s="1"/>
-      <s:c r="I18" s="1"/>
-      <s:c r="J18" s="1"/>
-      <s:c r="K18" s="1"/>
-      <s:c r="L18" s="1"/>
-      <s:c r="M18" s="1"/>
-      <s:c r="N18" s="1"/>
-      <s:c r="O18" s="1"/>
-      <s:c r="P18" s="1"/>
+      <s:c r="F18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G18" s="1" t="n">
+        <s:v>2305.34</s:v>
+      </s:c>
+      <s:c r="H18" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I18" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K18" s="1" t="n">
+        <s:v>1086</s:v>
+      </s:c>
+      <s:c r="L18" s="1" t="n">
+        <s:v>389.91</s:v>
+      </s:c>
+      <s:c r="M18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N18" s="1" t="n">
+        <s:v>20363.06</s:v>
+      </s:c>
+      <s:c r="O18" s="1" t="n">
+        <s:v>348.59</s:v>
+      </s:c>
+      <s:c r="P18" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="19" s="1" customFormat="1" spans="1:16">
       <s:c r="A19" s="6" t="n">
@@ -3926,17 +5068,39 @@
       </s:c>
       <s:c r="D19" s="1"/>
       <s:c r="E19" s="1"/>
-      <s:c r="F19" s="1"/>
-      <s:c r="G19" s="1"/>
-      <s:c r="H19" s="1"/>
-      <s:c r="I19" s="1"/>
-      <s:c r="J19" s="1"/>
-      <s:c r="K19" s="1"/>
-      <s:c r="L19" s="1"/>
-      <s:c r="M19" s="1"/>
-      <s:c r="N19" s="1"/>
-      <s:c r="O19" s="1"/>
-      <s:c r="P19" s="1"/>
+      <s:c r="F19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G19" s="1" t="n">
+        <s:v>2308.73</s:v>
+      </s:c>
+      <s:c r="H19" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I19" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K19" s="1" t="n">
+        <s:v>1082.6</s:v>
+      </s:c>
+      <s:c r="L19" s="1" t="n">
+        <s:v>389.91</s:v>
+      </s:c>
+      <s:c r="M19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N19" s="1" t="n">
+        <s:v>20015.31</s:v>
+      </s:c>
+      <s:c r="O19" s="1" t="n">
+        <s:v>314.55</s:v>
+      </s:c>
+      <s:c r="P19" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="20" s="1" customFormat="1" spans="1:16">
       <s:c r="A20" s="6" t="n">
@@ -3950,17 +5114,39 @@
       </s:c>
       <s:c r="D20" s="1"/>
       <s:c r="E20" s="1"/>
-      <s:c r="F20" s="1"/>
-      <s:c r="G20" s="1"/>
-      <s:c r="H20" s="1"/>
-      <s:c r="I20" s="1"/>
-      <s:c r="J20" s="1"/>
-      <s:c r="K20" s="1"/>
-      <s:c r="L20" s="1"/>
-      <s:c r="M20" s="1"/>
-      <s:c r="N20" s="1"/>
-      <s:c r="O20" s="1"/>
-      <s:c r="P20" s="1"/>
+      <s:c r="F20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G20" s="1" t="n">
+        <s:v>2281.32</s:v>
+      </s:c>
+      <s:c r="H20" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I20" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K20" s="1" t="n">
+        <s:v>940.8</s:v>
+      </s:c>
+      <s:c r="L20" s="1" t="n">
+        <s:v>390.23</s:v>
+      </s:c>
+      <s:c r="M20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N20" s="1" t="n">
+        <s:v>20059.59</s:v>
+      </s:c>
+      <s:c r="O20" s="1" t="n">
+        <s:v>296.97</s:v>
+      </s:c>
+      <s:c r="P20" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="21" s="1" customFormat="1" spans="1:16">
       <s:c r="A21" s="6" t="n">
@@ -3974,17 +5160,39 @@
       </s:c>
       <s:c r="D21" s="1"/>
       <s:c r="E21" s="1"/>
-      <s:c r="F21" s="1"/>
-      <s:c r="G21" s="1"/>
-      <s:c r="H21" s="1"/>
-      <s:c r="I21" s="1"/>
-      <s:c r="J21" s="1"/>
-      <s:c r="K21" s="1"/>
-      <s:c r="L21" s="1"/>
-      <s:c r="M21" s="1"/>
-      <s:c r="N21" s="1"/>
-      <s:c r="O21" s="1"/>
-      <s:c r="P21" s="1"/>
+      <s:c r="F21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G21" s="1" t="n">
+        <s:v>2322</s:v>
+      </s:c>
+      <s:c r="H21" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I21" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K21" s="1" t="n">
+        <s:v>653.6</s:v>
+      </s:c>
+      <s:c r="L21" s="1" t="n">
+        <s:v>389.28</s:v>
+      </s:c>
+      <s:c r="M21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N21" s="1" t="n">
+        <s:v>20209.94</s:v>
+      </s:c>
+      <s:c r="O21" s="1" t="n">
+        <s:v>294.79</s:v>
+      </s:c>
+      <s:c r="P21" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="22" s="1" customFormat="1" spans="1:16">
       <s:c r="A22" s="6" t="n">
@@ -3998,17 +5206,39 @@
       </s:c>
       <s:c r="D22" s="1"/>
       <s:c r="E22" s="1"/>
-      <s:c r="F22" s="1"/>
-      <s:c r="G22" s="1"/>
-      <s:c r="H22" s="1"/>
-      <s:c r="I22" s="1"/>
-      <s:c r="J22" s="1"/>
-      <s:c r="K22" s="1"/>
-      <s:c r="L22" s="1"/>
-      <s:c r="M22" s="1"/>
-      <s:c r="N22" s="1"/>
-      <s:c r="O22" s="1"/>
-      <s:c r="P22" s="1"/>
+      <s:c r="F22" s="1" t="n">
+        <s:v>260</s:v>
+      </s:c>
+      <s:c r="G22" s="1" t="n">
+        <s:v>2360</s:v>
+      </s:c>
+      <s:c r="H22" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I22" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K22" s="1" t="n">
+        <s:v>498.5</s:v>
+      </s:c>
+      <s:c r="L22" s="1" t="n">
+        <s:v>389.91</s:v>
+      </s:c>
+      <s:c r="M22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N22" s="1" t="n">
+        <s:v>20544.06</s:v>
+      </s:c>
+      <s:c r="O22" s="1" t="n">
+        <s:v>291.02</s:v>
+      </s:c>
+      <s:c r="P22" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="23" s="1" customFormat="1" spans="1:16">
       <s:c r="A23" s="6" t="n">
@@ -4022,17 +5252,39 @@
       </s:c>
       <s:c r="D23" s="1"/>
       <s:c r="E23" s="1"/>
-      <s:c r="F23" s="1"/>
-      <s:c r="G23" s="1"/>
-      <s:c r="H23" s="1"/>
-      <s:c r="I23" s="1"/>
-      <s:c r="J23" s="1"/>
-      <s:c r="K23" s="1"/>
-      <s:c r="L23" s="1"/>
-      <s:c r="M23" s="1"/>
-      <s:c r="N23" s="1"/>
-      <s:c r="O23" s="1"/>
-      <s:c r="P23" s="1"/>
+      <s:c r="F23" s="1" t="n">
+        <s:v>380</s:v>
+      </s:c>
+      <s:c r="G23" s="1" t="n">
+        <s:v>2375.61</s:v>
+      </s:c>
+      <s:c r="H23" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I23" s="1" t="n">
+        <s:v>3.75</s:v>
+      </s:c>
+      <s:c r="J23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K23" s="1" t="n">
+        <s:v>499.5</s:v>
+      </s:c>
+      <s:c r="L23" s="1" t="n">
+        <s:v>389.6</s:v>
+      </s:c>
+      <s:c r="M23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N23" s="1" t="n">
+        <s:v>20682.72</s:v>
+      </s:c>
+      <s:c r="O23" s="1" t="n">
+        <s:v>274.19</s:v>
+      </s:c>
+      <s:c r="P23" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="24" s="1" customFormat="1" spans="1:16">
       <s:c r="A24" s="6" t="n">
@@ -4046,17 +5298,39 @@
       </s:c>
       <s:c r="D24" s="1"/>
       <s:c r="E24" s="1"/>
-      <s:c r="F24" s="1"/>
-      <s:c r="G24" s="1"/>
-      <s:c r="H24" s="1"/>
-      <s:c r="I24" s="1"/>
-      <s:c r="J24" s="1"/>
-      <s:c r="K24" s="1"/>
-      <s:c r="L24" s="1"/>
-      <s:c r="M24" s="1"/>
-      <s:c r="N24" s="1"/>
-      <s:c r="O24" s="1"/>
-      <s:c r="P24" s="1"/>
+      <s:c r="F24" s="1" t="n">
+        <s:v>440</s:v>
+      </s:c>
+      <s:c r="G24" s="1" t="n">
+        <s:v>2416.08</s:v>
+      </s:c>
+      <s:c r="H24" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I24" s="1" t="n">
+        <s:v>5.19</s:v>
+      </s:c>
+      <s:c r="J24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L24" s="1" t="n">
+        <s:v>389.28</s:v>
+      </s:c>
+      <s:c r="M24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N24" s="1" t="n">
+        <s:v>20702.63</s:v>
+      </s:c>
+      <s:c r="O24" s="1" t="n">
+        <s:v>280.88</s:v>
+      </s:c>
+      <s:c r="P24" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="25" s="1" customFormat="1" spans="1:16">
       <s:c r="A25" s="6" t="n">
@@ -4070,17 +5344,39 @@
       </s:c>
       <s:c r="D25" s="1"/>
       <s:c r="E25" s="1"/>
-      <s:c r="F25" s="1"/>
-      <s:c r="G25" s="1"/>
-      <s:c r="H25" s="1"/>
-      <s:c r="I25" s="1"/>
-      <s:c r="J25" s="1"/>
-      <s:c r="K25" s="1"/>
-      <s:c r="L25" s="1"/>
-      <s:c r="M25" s="1"/>
-      <s:c r="N25" s="1"/>
-      <s:c r="O25" s="1"/>
-      <s:c r="P25" s="1"/>
+      <s:c r="F25" s="1" t="n">
+        <s:v>640</s:v>
+      </s:c>
+      <s:c r="G25" s="1" t="n">
+        <s:v>2403.35</s:v>
+      </s:c>
+      <s:c r="H25" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I25" s="1" t="n">
+        <s:v>97.62</s:v>
+      </s:c>
+      <s:c r="J25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L25" s="1" t="n">
+        <s:v>390.23</s:v>
+      </s:c>
+      <s:c r="M25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N25" s="1" t="n">
+        <s:v>20537.19</s:v>
+      </s:c>
+      <s:c r="O25" s="1" t="n">
+        <s:v>279.22</s:v>
+      </s:c>
+      <s:c r="P25" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="26" s="1" customFormat="1" spans="1:16">
       <s:c r="A26" s="6" t="n">
@@ -4094,17 +5390,39 @@
       </s:c>
       <s:c r="D26" s="1"/>
       <s:c r="E26" s="1"/>
-      <s:c r="F26" s="1"/>
-      <s:c r="G26" s="1"/>
-      <s:c r="H26" s="1"/>
-      <s:c r="I26" s="1"/>
-      <s:c r="J26" s="1"/>
-      <s:c r="K26" s="1"/>
-      <s:c r="L26" s="1"/>
-      <s:c r="M26" s="1"/>
-      <s:c r="N26" s="1"/>
-      <s:c r="O26" s="1"/>
-      <s:c r="P26" s="1"/>
+      <s:c r="F26" s="1" t="n">
+        <s:v>820</s:v>
+      </s:c>
+      <s:c r="G26" s="1" t="n">
+        <s:v>2407.6</s:v>
+      </s:c>
+      <s:c r="H26" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I26" s="1" t="n">
+        <s:v>280.64</s:v>
+      </s:c>
+      <s:c r="J26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L26" s="1" t="n">
+        <s:v>388.33</s:v>
+      </s:c>
+      <s:c r="M26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N26" s="1" t="n">
+        <s:v>20644.51</s:v>
+      </s:c>
+      <s:c r="O26" s="1" t="n">
+        <s:v>293.04</s:v>
+      </s:c>
+      <s:c r="P26" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="27" s="1" customFormat="1" spans="1:16">
       <s:c r="A27" s="6" t="n">
@@ -4118,17 +5436,39 @@
       </s:c>
       <s:c r="D27" s="1"/>
       <s:c r="E27" s="1"/>
-      <s:c r="F27" s="1"/>
-      <s:c r="G27" s="1"/>
-      <s:c r="H27" s="1"/>
-      <s:c r="I27" s="1"/>
-      <s:c r="J27" s="1"/>
-      <s:c r="K27" s="1"/>
-      <s:c r="L27" s="1"/>
-      <s:c r="M27" s="1"/>
-      <s:c r="N27" s="1"/>
-      <s:c r="O27" s="1"/>
-      <s:c r="P27" s="1"/>
+      <s:c r="F27" s="1" t="n">
+        <s:v>790</s:v>
+      </s:c>
+      <s:c r="G27" s="1" t="n">
+        <s:v>2396.53</s:v>
+      </s:c>
+      <s:c r="H27" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I27" s="1" t="n">
+        <s:v>665.29</s:v>
+      </s:c>
+      <s:c r="J27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K27" s="1" t="n">
+        <s:v>250.4</s:v>
+      </s:c>
+      <s:c r="L27" s="1" t="n">
+        <s:v>240.49</s:v>
+      </s:c>
+      <s:c r="M27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N27" s="1" t="n">
+        <s:v>20198</s:v>
+      </s:c>
+      <s:c r="O27" s="1" t="n">
+        <s:v>308.2</s:v>
+      </s:c>
+      <s:c r="P27" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="28" s="1" customFormat="1" spans="1:16">
       <s:c r="A28" s="6" t="n">
@@ -4142,17 +5482,39 @@
       </s:c>
       <s:c r="D28" s="1"/>
       <s:c r="E28" s="1"/>
-      <s:c r="F28" s="1"/>
-      <s:c r="G28" s="1"/>
-      <s:c r="H28" s="1"/>
-      <s:c r="I28" s="1"/>
-      <s:c r="J28" s="1"/>
-      <s:c r="K28" s="1"/>
-      <s:c r="L28" s="1"/>
-      <s:c r="M28" s="1"/>
-      <s:c r="N28" s="1"/>
-      <s:c r="O28" s="1"/>
-      <s:c r="P28" s="1"/>
+      <s:c r="F28" s="1" t="n">
+        <s:v>825</s:v>
+      </s:c>
+      <s:c r="G28" s="1" t="n">
+        <s:v>2419.97</s:v>
+      </s:c>
+      <s:c r="H28" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I28" s="1" t="n">
+        <s:v>1157.68</s:v>
+      </s:c>
+      <s:c r="J28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K28" s="1" t="n">
+        <s:v>403.3</s:v>
+      </s:c>
+      <s:c r="L28" s="1" t="n">
+        <s:v>43.06</s:v>
+      </s:c>
+      <s:c r="M28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N28" s="1" t="n">
+        <s:v>19890.5</s:v>
+      </s:c>
+      <s:c r="O28" s="1" t="n">
+        <s:v>327.1</s:v>
+      </s:c>
+      <s:c r="P28" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="29" s="1" customFormat="1" spans="1:16">
       <s:c r="A29" s="6" t="n">
@@ -4166,17 +5528,39 @@
       </s:c>
       <s:c r="D29" s="1"/>
       <s:c r="E29" s="1"/>
-      <s:c r="F29" s="1"/>
-      <s:c r="G29" s="1"/>
-      <s:c r="H29" s="1"/>
-      <s:c r="I29" s="1"/>
-      <s:c r="J29" s="1"/>
-      <s:c r="K29" s="1"/>
-      <s:c r="L29" s="1"/>
-      <s:c r="M29" s="1"/>
-      <s:c r="N29" s="1"/>
-      <s:c r="O29" s="1"/>
-      <s:c r="P29" s="1"/>
+      <s:c r="F29" s="1" t="n">
+        <s:v>645</s:v>
+      </s:c>
+      <s:c r="G29" s="1" t="n">
+        <s:v>2436.19</s:v>
+      </s:c>
+      <s:c r="H29" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I29" s="1" t="n">
+        <s:v>1774.78</s:v>
+      </s:c>
+      <s:c r="J29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K29" s="1" t="n">
+        <s:v>497.6</s:v>
+      </s:c>
+      <s:c r="L29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N29" s="1" t="n">
+        <s:v>19216.27</s:v>
+      </s:c>
+      <s:c r="O29" s="1" t="n">
+        <s:v>339.97</s:v>
+      </s:c>
+      <s:c r="P29" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="30" s="1" customFormat="1" spans="1:16">
       <s:c r="A30" s="6" t="n">
@@ -4190,17 +5574,39 @@
       </s:c>
       <s:c r="D30" s="1"/>
       <s:c r="E30" s="1"/>
-      <s:c r="F30" s="1"/>
-      <s:c r="G30" s="1"/>
-      <s:c r="H30" s="1"/>
-      <s:c r="I30" s="1"/>
-      <s:c r="J30" s="1"/>
-      <s:c r="K30" s="1"/>
-      <s:c r="L30" s="1"/>
-      <s:c r="M30" s="1"/>
-      <s:c r="N30" s="1"/>
-      <s:c r="O30" s="1"/>
-      <s:c r="P30" s="1"/>
+      <s:c r="F30" s="1" t="n">
+        <s:v>95</s:v>
+      </s:c>
+      <s:c r="G30" s="1" t="n">
+        <s:v>2456.76</s:v>
+      </s:c>
+      <s:c r="H30" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I30" s="1" t="n">
+        <s:v>2545.56</s:v>
+      </s:c>
+      <s:c r="J30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K30" s="1" t="n">
+        <s:v>497.6</s:v>
+      </s:c>
+      <s:c r="L30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N30" s="1" t="n">
+        <s:v>18777.94</s:v>
+      </s:c>
+      <s:c r="O30" s="1" t="n">
+        <s:v>325.75</s:v>
+      </s:c>
+      <s:c r="P30" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="31" s="1" customFormat="1" spans="1:16">
       <s:c r="A31" s="6" t="n">
@@ -4214,17 +5620,39 @@
       </s:c>
       <s:c r="D31" s="1"/>
       <s:c r="E31" s="1"/>
-      <s:c r="F31" s="1"/>
-      <s:c r="G31" s="1"/>
-      <s:c r="H31" s="1"/>
-      <s:c r="I31" s="1"/>
-      <s:c r="J31" s="1"/>
-      <s:c r="K31" s="1"/>
-      <s:c r="L31" s="1"/>
-      <s:c r="M31" s="1"/>
-      <s:c r="N31" s="1"/>
-      <s:c r="O31" s="1"/>
-      <s:c r="P31" s="1"/>
+      <s:c r="F31" s="1" t="n">
+        <s:v>95</s:v>
+      </s:c>
+      <s:c r="G31" s="1" t="n">
+        <s:v>2502.24</s:v>
+      </s:c>
+      <s:c r="H31" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I31" s="1" t="n">
+        <s:v>3410.77</s:v>
+      </s:c>
+      <s:c r="J31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K31" s="1" t="n">
+        <s:v>497.6</s:v>
+      </s:c>
+      <s:c r="L31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N31" s="1" t="n">
+        <s:v>17463.83</s:v>
+      </s:c>
+      <s:c r="O31" s="1" t="n">
+        <s:v>333.16</s:v>
+      </s:c>
+      <s:c r="P31" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="32" s="1" customFormat="1" spans="1:16">
       <s:c r="A32" s="6" t="n">
@@ -4238,17 +5666,39 @@
       </s:c>
       <s:c r="D32" s="1"/>
       <s:c r="E32" s="1"/>
-      <s:c r="F32" s="1"/>
-      <s:c r="G32" s="1"/>
-      <s:c r="H32" s="1"/>
-      <s:c r="I32" s="1"/>
-      <s:c r="J32" s="1"/>
-      <s:c r="K32" s="1"/>
-      <s:c r="L32" s="1"/>
-      <s:c r="M32" s="1"/>
-      <s:c r="N32" s="1"/>
-      <s:c r="O32" s="1"/>
-      <s:c r="P32" s="1"/>
+      <s:c r="F32" s="1" t="n">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="G32" s="1" t="n">
+        <s:v>2581.36</s:v>
+      </s:c>
+      <s:c r="H32" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I32" s="1" t="n">
+        <s:v>4295.53</s:v>
+      </s:c>
+      <s:c r="J32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K32" s="1" t="n">
+        <s:v>497</s:v>
+      </s:c>
+      <s:c r="L32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N32" s="1" t="n">
+        <s:v>15816.12</s:v>
+      </s:c>
+      <s:c r="O32" s="1" t="n">
+        <s:v>325.4</s:v>
+      </s:c>
+      <s:c r="P32" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="33" s="1" customFormat="1" spans="1:16">
       <s:c r="A33" s="6" t="n">
@@ -4262,17 +5712,39 @@
       </s:c>
       <s:c r="D33" s="1"/>
       <s:c r="E33" s="1"/>
-      <s:c r="F33" s="1"/>
-      <s:c r="G33" s="1"/>
-      <s:c r="H33" s="1"/>
-      <s:c r="I33" s="1"/>
-      <s:c r="J33" s="1"/>
-      <s:c r="K33" s="1"/>
-      <s:c r="L33" s="1"/>
-      <s:c r="M33" s="1"/>
-      <s:c r="N33" s="1"/>
-      <s:c r="O33" s="1"/>
-      <s:c r="P33" s="1"/>
+      <s:c r="F33" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G33" s="1" t="n">
+        <s:v>2686.17</s:v>
+      </s:c>
+      <s:c r="H33" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I33" s="1" t="n">
+        <s:v>5179.17</s:v>
+      </s:c>
+      <s:c r="J33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K33" s="1" t="n">
+        <s:v>252.1</s:v>
+      </s:c>
+      <s:c r="L33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N33" s="1" t="n">
+        <s:v>14295.37</s:v>
+      </s:c>
+      <s:c r="O33" s="1" t="n">
+        <s:v>336.09</s:v>
+      </s:c>
+      <s:c r="P33" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="34" s="1" customFormat="1" spans="1:16">
       <s:c r="A34" s="6" t="n">
@@ -4286,17 +5758,39 @@
       </s:c>
       <s:c r="D34" s="1"/>
       <s:c r="E34" s="1"/>
-      <s:c r="F34" s="1"/>
-      <s:c r="G34" s="1"/>
-      <s:c r="H34" s="1"/>
-      <s:c r="I34" s="1"/>
-      <s:c r="J34" s="1"/>
-      <s:c r="K34" s="1"/>
-      <s:c r="L34" s="1"/>
-      <s:c r="M34" s="1"/>
-      <s:c r="N34" s="1"/>
-      <s:c r="O34" s="1"/>
-      <s:c r="P34" s="1"/>
+      <s:c r="F34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G34" s="1" t="n">
+        <s:v>2711.54</s:v>
+      </s:c>
+      <s:c r="H34" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I34" s="1" t="n">
+        <s:v>6094.25</s:v>
+      </s:c>
+      <s:c r="J34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N34" s="1" t="n">
+        <s:v>12974.96</s:v>
+      </s:c>
+      <s:c r="O34" s="1" t="n">
+        <s:v>312.15</s:v>
+      </s:c>
+      <s:c r="P34" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="35" s="1" customFormat="1" spans="1:16">
       <s:c r="A35" s="6" t="n">
@@ -4310,17 +5804,39 @@
       </s:c>
       <s:c r="D35" s="1"/>
       <s:c r="E35" s="1"/>
-      <s:c r="F35" s="1"/>
-      <s:c r="G35" s="1"/>
-      <s:c r="H35" s="1"/>
-      <s:c r="I35" s="1"/>
-      <s:c r="J35" s="1"/>
-      <s:c r="K35" s="1"/>
-      <s:c r="L35" s="1"/>
-      <s:c r="M35" s="1"/>
-      <s:c r="N35" s="1"/>
-      <s:c r="O35" s="1"/>
-      <s:c r="P35" s="1"/>
+      <s:c r="F35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G35" s="1" t="n">
+        <s:v>2767.37</s:v>
+      </s:c>
+      <s:c r="H35" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I35" s="1" t="n">
+        <s:v>6885.92</s:v>
+      </s:c>
+      <s:c r="J35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K35" s="1" t="n">
+        <s:v>-26.2</s:v>
+      </s:c>
+      <s:c r="L35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N35" s="1" t="n">
+        <s:v>11896.29</s:v>
+      </s:c>
+      <s:c r="O35" s="1" t="n">
+        <s:v>285.11</s:v>
+      </s:c>
+      <s:c r="P35" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="36" s="1" customFormat="1" spans="1:16">
       <s:c r="A36" s="6" t="n">
@@ -4334,17 +5850,39 @@
       </s:c>
       <s:c r="D36" s="1"/>
       <s:c r="E36" s="1"/>
-      <s:c r="F36" s="1"/>
-      <s:c r="G36" s="1"/>
-      <s:c r="H36" s="1"/>
-      <s:c r="I36" s="1"/>
-      <s:c r="J36" s="1"/>
-      <s:c r="K36" s="1"/>
-      <s:c r="L36" s="1"/>
-      <s:c r="M36" s="1"/>
-      <s:c r="N36" s="1"/>
-      <s:c r="O36" s="1"/>
-      <s:c r="P36" s="1"/>
+      <s:c r="F36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G36" s="1" t="n">
+        <s:v>2849.48</s:v>
+      </s:c>
+      <s:c r="H36" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I36" s="1" t="n">
+        <s:v>7650.4</s:v>
+      </s:c>
+      <s:c r="J36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K36" s="1" t="n">
+        <s:v>-20.7</s:v>
+      </s:c>
+      <s:c r="L36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N36" s="1" t="n">
+        <s:v>9894.22</s:v>
+      </s:c>
+      <s:c r="O36" s="1" t="n">
+        <s:v>243.6</s:v>
+      </s:c>
+      <s:c r="P36" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="37" s="1" customFormat="1" spans="1:16">
       <s:c r="A37" s="6" t="n">
@@ -4358,17 +5896,39 @@
       </s:c>
       <s:c r="D37" s="1"/>
       <s:c r="E37" s="1"/>
-      <s:c r="F37" s="1"/>
-      <s:c r="G37" s="1"/>
-      <s:c r="H37" s="1"/>
-      <s:c r="I37" s="1"/>
-      <s:c r="J37" s="1"/>
-      <s:c r="K37" s="1"/>
-      <s:c r="L37" s="1"/>
-      <s:c r="M37" s="1"/>
-      <s:c r="N37" s="1"/>
-      <s:c r="O37" s="1"/>
-      <s:c r="P37" s="1"/>
+      <s:c r="F37" s="1" t="n">
+        <s:v>-100</s:v>
+      </s:c>
+      <s:c r="G37" s="1" t="n">
+        <s:v>2859.4</s:v>
+      </s:c>
+      <s:c r="H37" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I37" s="1" t="n">
+        <s:v>8239.79</s:v>
+      </s:c>
+      <s:c r="J37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K37" s="1" t="n">
+        <s:v>-887</s:v>
+      </s:c>
+      <s:c r="L37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N37" s="1" t="n">
+        <s:v>9325.44</s:v>
+      </s:c>
+      <s:c r="O37" s="1" t="n">
+        <s:v>218.77</s:v>
+      </s:c>
+      <s:c r="P37" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="38" s="1" customFormat="1" spans="1:16">
       <s:c r="A38" s="6" t="n">
@@ -4382,17 +5942,39 @@
       </s:c>
       <s:c r="D38" s="1"/>
       <s:c r="E38" s="1"/>
-      <s:c r="F38" s="1"/>
-      <s:c r="G38" s="1"/>
-      <s:c r="H38" s="1"/>
-      <s:c r="I38" s="1"/>
-      <s:c r="J38" s="1"/>
-      <s:c r="K38" s="1"/>
-      <s:c r="L38" s="1"/>
-      <s:c r="M38" s="1"/>
-      <s:c r="N38" s="1"/>
-      <s:c r="O38" s="1"/>
-      <s:c r="P38" s="1"/>
+      <s:c r="F38" s="1" t="n">
+        <s:v>-890</s:v>
+      </s:c>
+      <s:c r="G38" s="1" t="n">
+        <s:v>2888.58</s:v>
+      </s:c>
+      <s:c r="H38" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I38" s="1" t="n">
+        <s:v>8830.55</s:v>
+      </s:c>
+      <s:c r="J38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K38" s="1" t="n">
+        <s:v>-1134.3</s:v>
+      </s:c>
+      <s:c r="L38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N38" s="1" t="n">
+        <s:v>9433.34</s:v>
+      </s:c>
+      <s:c r="O38" s="1" t="n">
+        <s:v>192.53</s:v>
+      </s:c>
+      <s:c r="P38" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="39" s="1" customFormat="1" spans="1:16">
       <s:c r="A39" s="6" t="n">
@@ -4406,17 +5988,39 @@
       </s:c>
       <s:c r="D39" s="1"/>
       <s:c r="E39" s="1"/>
-      <s:c r="F39" s="1"/>
-      <s:c r="G39" s="1"/>
-      <s:c r="H39" s="1"/>
-      <s:c r="I39" s="1"/>
-      <s:c r="J39" s="1"/>
-      <s:c r="K39" s="1"/>
-      <s:c r="L39" s="1"/>
-      <s:c r="M39" s="1"/>
-      <s:c r="N39" s="1"/>
-      <s:c r="O39" s="1"/>
-      <s:c r="P39" s="1"/>
+      <s:c r="F39" s="1" t="n">
+        <s:v>-1690</s:v>
+      </s:c>
+      <s:c r="G39" s="1" t="n">
+        <s:v>2907.78</s:v>
+      </s:c>
+      <s:c r="H39" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I39" s="1" t="n">
+        <s:v>9366.9</s:v>
+      </s:c>
+      <s:c r="J39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K39" s="1" t="n">
+        <s:v>-1135.6</s:v>
+      </s:c>
+      <s:c r="L39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N39" s="1" t="n">
+        <s:v>9582.24</s:v>
+      </s:c>
+      <s:c r="O39" s="1" t="n">
+        <s:v>188.68</s:v>
+      </s:c>
+      <s:c r="P39" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="40" s="1" customFormat="1" spans="1:16">
       <s:c r="A40" s="6" t="n">
@@ -4430,17 +6034,39 @@
       </s:c>
       <s:c r="D40" s="1"/>
       <s:c r="E40" s="1"/>
-      <s:c r="F40" s="1"/>
-      <s:c r="G40" s="1"/>
-      <s:c r="H40" s="1"/>
-      <s:c r="I40" s="1"/>
-      <s:c r="J40" s="1"/>
-      <s:c r="K40" s="1"/>
-      <s:c r="L40" s="1"/>
-      <s:c r="M40" s="1"/>
-      <s:c r="N40" s="1"/>
-      <s:c r="O40" s="1"/>
-      <s:c r="P40" s="1"/>
+      <s:c r="F40" s="1" t="n">
+        <s:v>-2203</s:v>
+      </s:c>
+      <s:c r="G40" s="1" t="n">
+        <s:v>2950.7</s:v>
+      </s:c>
+      <s:c r="H40" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I40" s="1" t="n">
+        <s:v>9871.55</s:v>
+      </s:c>
+      <s:c r="J40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K40" s="1" t="n">
+        <s:v>-1131.9</s:v>
+      </s:c>
+      <s:c r="L40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N40" s="1" t="n">
+        <s:v>9253.55</s:v>
+      </s:c>
+      <s:c r="O40" s="1" t="n">
+        <s:v>183.61</s:v>
+      </s:c>
+      <s:c r="P40" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="41" s="1" customFormat="1" spans="1:16">
       <s:c r="A41" s="6" t="n">
@@ -4454,17 +6080,39 @@
       </s:c>
       <s:c r="D41" s="1"/>
       <s:c r="E41" s="1"/>
-      <s:c r="F41" s="1"/>
-      <s:c r="G41" s="1"/>
-      <s:c r="H41" s="1"/>
-      <s:c r="I41" s="1"/>
-      <s:c r="J41" s="1"/>
-      <s:c r="K41" s="1"/>
-      <s:c r="L41" s="1"/>
-      <s:c r="M41" s="1"/>
-      <s:c r="N41" s="1"/>
-      <s:c r="O41" s="1"/>
-      <s:c r="P41" s="1"/>
+      <s:c r="F41" s="1" t="n">
+        <s:v>-2463</s:v>
+      </s:c>
+      <s:c r="G41" s="1" t="n">
+        <s:v>2989.35</s:v>
+      </s:c>
+      <s:c r="H41" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I41" s="1" t="n">
+        <s:v>10220.62</s:v>
+      </s:c>
+      <s:c r="J41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K41" s="1" t="n">
+        <s:v>-1130.4</s:v>
+      </s:c>
+      <s:c r="L41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N41" s="1" t="n">
+        <s:v>9088.71</s:v>
+      </s:c>
+      <s:c r="O41" s="1" t="n">
+        <s:v>174.93</s:v>
+      </s:c>
+      <s:c r="P41" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="42" s="1" customFormat="1" spans="1:16">
       <s:c r="A42" s="6" t="n">
@@ -4478,17 +6126,39 @@
       </s:c>
       <s:c r="D42" s="1"/>
       <s:c r="E42" s="1"/>
-      <s:c r="F42" s="1"/>
-      <s:c r="G42" s="1"/>
-      <s:c r="H42" s="1"/>
-      <s:c r="I42" s="1"/>
-      <s:c r="J42" s="1"/>
-      <s:c r="K42" s="1"/>
-      <s:c r="L42" s="1"/>
-      <s:c r="M42" s="1"/>
-      <s:c r="N42" s="1"/>
-      <s:c r="O42" s="1"/>
-      <s:c r="P42" s="1"/>
+      <s:c r="F42" s="1" t="n">
+        <s:v>-3153</s:v>
+      </s:c>
+      <s:c r="G42" s="1" t="n">
+        <s:v>3013.4</s:v>
+      </s:c>
+      <s:c r="H42" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I42" s="1" t="n">
+        <s:v>10500.45</s:v>
+      </s:c>
+      <s:c r="J42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K42" s="1" t="n">
+        <s:v>-1125.5</s:v>
+      </s:c>
+      <s:c r="L42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N42" s="1" t="n">
+        <s:v>9344.64</s:v>
+      </s:c>
+      <s:c r="O42" s="1" t="n">
+        <s:v>154.12</s:v>
+      </s:c>
+      <s:c r="P42" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="43" s="1" customFormat="1" spans="1:16">
       <s:c r="A43" s="6" t="n">
@@ -4502,17 +6172,39 @@
       </s:c>
       <s:c r="D43" s="1"/>
       <s:c r="E43" s="1"/>
-      <s:c r="F43" s="1"/>
-      <s:c r="G43" s="1"/>
-      <s:c r="H43" s="1"/>
-      <s:c r="I43" s="1"/>
-      <s:c r="J43" s="1"/>
-      <s:c r="K43" s="1"/>
-      <s:c r="L43" s="1"/>
-      <s:c r="M43" s="1"/>
-      <s:c r="N43" s="1"/>
-      <s:c r="O43" s="1"/>
-      <s:c r="P43" s="1"/>
+      <s:c r="F43" s="1" t="n">
+        <s:v>-3343</s:v>
+      </s:c>
+      <s:c r="G43" s="1" t="n">
+        <s:v>3089.68</s:v>
+      </s:c>
+      <s:c r="H43" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I43" s="1" t="n">
+        <s:v>10878.21</s:v>
+      </s:c>
+      <s:c r="J43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K43" s="1" t="n">
+        <s:v>-1127.7</s:v>
+      </s:c>
+      <s:c r="L43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N43" s="1" t="n">
+        <s:v>8960.28</s:v>
+      </s:c>
+      <s:c r="O43" s="1" t="n">
+        <s:v>154.68</s:v>
+      </s:c>
+      <s:c r="P43" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="44" s="1" customFormat="1" spans="1:16">
       <s:c r="A44" s="6" t="n">
@@ -4526,17 +6218,39 @@
       </s:c>
       <s:c r="D44" s="1"/>
       <s:c r="E44" s="1"/>
-      <s:c r="F44" s="1"/>
-      <s:c r="G44" s="1"/>
-      <s:c r="H44" s="1"/>
-      <s:c r="I44" s="1"/>
-      <s:c r="J44" s="1"/>
-      <s:c r="K44" s="1"/>
-      <s:c r="L44" s="1"/>
-      <s:c r="M44" s="1"/>
-      <s:c r="N44" s="1"/>
-      <s:c r="O44" s="1"/>
-      <s:c r="P44" s="1"/>
+      <s:c r="F44" s="1" t="n">
+        <s:v>-3503</s:v>
+      </s:c>
+      <s:c r="G44" s="1" t="n">
+        <s:v>3123.18</s:v>
+      </s:c>
+      <s:c r="H44" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I44" s="1" t="n">
+        <s:v>11171.86</s:v>
+      </s:c>
+      <s:c r="J44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K44" s="1" t="n">
+        <s:v>-1122.9</s:v>
+      </s:c>
+      <s:c r="L44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N44" s="1" t="n">
+        <s:v>8633.09</s:v>
+      </s:c>
+      <s:c r="O44" s="1" t="n">
+        <s:v>161.1</s:v>
+      </s:c>
+      <s:c r="P44" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="45" s="1" customFormat="1" spans="1:16">
       <s:c r="A45" s="6" t="n">
@@ -4550,17 +6264,39 @@
       </s:c>
       <s:c r="D45" s="1"/>
       <s:c r="E45" s="1"/>
-      <s:c r="F45" s="1"/>
-      <s:c r="G45" s="1"/>
-      <s:c r="H45" s="1"/>
-      <s:c r="I45" s="1"/>
-      <s:c r="J45" s="1"/>
-      <s:c r="K45" s="1"/>
-      <s:c r="L45" s="1"/>
-      <s:c r="M45" s="1"/>
-      <s:c r="N45" s="1"/>
-      <s:c r="O45" s="1"/>
-      <s:c r="P45" s="1"/>
+      <s:c r="F45" s="1" t="n">
+        <s:v>-3553</s:v>
+      </s:c>
+      <s:c r="G45" s="1" t="n">
+        <s:v>3167.65</s:v>
+      </s:c>
+      <s:c r="H45" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I45" s="1" t="n">
+        <s:v>11412.22</s:v>
+      </s:c>
+      <s:c r="J45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K45" s="1" t="n">
+        <s:v>-1122.3</s:v>
+      </s:c>
+      <s:c r="L45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N45" s="1" t="n">
+        <s:v>8958.34</s:v>
+      </s:c>
+      <s:c r="O45" s="1" t="n">
+        <s:v>170.61</s:v>
+      </s:c>
+      <s:c r="P45" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="46" s="1" customFormat="1" spans="1:16">
       <s:c r="A46" s="6" t="n">
@@ -4574,17 +6310,39 @@
       </s:c>
       <s:c r="D46" s="1"/>
       <s:c r="E46" s="1"/>
-      <s:c r="F46" s="1"/>
-      <s:c r="G46" s="1"/>
-      <s:c r="H46" s="1"/>
-      <s:c r="I46" s="1"/>
-      <s:c r="J46" s="1"/>
-      <s:c r="K46" s="1"/>
-      <s:c r="L46" s="1"/>
-      <s:c r="M46" s="1"/>
-      <s:c r="N46" s="1"/>
-      <s:c r="O46" s="1"/>
-      <s:c r="P46" s="1"/>
+      <s:c r="F46" s="1" t="n">
+        <s:v>-3493</s:v>
+      </s:c>
+      <s:c r="G46" s="1" t="n">
+        <s:v>3168.06</s:v>
+      </s:c>
+      <s:c r="H46" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I46" s="1" t="n">
+        <s:v>11628.8</s:v>
+      </s:c>
+      <s:c r="J46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K46" s="1" t="n">
+        <s:v>-1119.2</s:v>
+      </s:c>
+      <s:c r="L46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N46" s="1" t="n">
+        <s:v>9528.97</s:v>
+      </s:c>
+      <s:c r="O46" s="1" t="n">
+        <s:v>175.97</s:v>
+      </s:c>
+      <s:c r="P46" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="47" s="1" customFormat="1" spans="1:16">
       <s:c r="A47" s="6" t="n">
@@ -4598,17 +6356,39 @@
       </s:c>
       <s:c r="D47" s="1"/>
       <s:c r="E47" s="1"/>
-      <s:c r="F47" s="1"/>
-      <s:c r="G47" s="1"/>
-      <s:c r="H47" s="1"/>
-      <s:c r="I47" s="1"/>
-      <s:c r="J47" s="1"/>
-      <s:c r="K47" s="1"/>
-      <s:c r="L47" s="1"/>
-      <s:c r="M47" s="1"/>
-      <s:c r="N47" s="1"/>
-      <s:c r="O47" s="1"/>
-      <s:c r="P47" s="1"/>
+      <s:c r="F47" s="1" t="n">
+        <s:v>-3273</s:v>
+      </s:c>
+      <s:c r="G47" s="1" t="n">
+        <s:v>3185.63</s:v>
+      </s:c>
+      <s:c r="H47" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I47" s="1" t="n">
+        <s:v>11810.05</s:v>
+      </s:c>
+      <s:c r="J47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K47" s="1" t="n">
+        <s:v>-1117.3</s:v>
+      </s:c>
+      <s:c r="L47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N47" s="1" t="n">
+        <s:v>10604.41</s:v>
+      </s:c>
+      <s:c r="O47" s="1" t="n">
+        <s:v>179.41</s:v>
+      </s:c>
+      <s:c r="P47" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="48" s="1" customFormat="1" spans="1:16">
       <s:c r="A48" s="6" t="n">
@@ -4622,17 +6402,39 @@
       </s:c>
       <s:c r="D48" s="1"/>
       <s:c r="E48" s="1"/>
-      <s:c r="F48" s="1"/>
-      <s:c r="G48" s="1"/>
-      <s:c r="H48" s="1"/>
-      <s:c r="I48" s="1"/>
-      <s:c r="J48" s="1"/>
-      <s:c r="K48" s="1"/>
-      <s:c r="L48" s="1"/>
-      <s:c r="M48" s="1"/>
-      <s:c r="N48" s="1"/>
-      <s:c r="O48" s="1"/>
-      <s:c r="P48" s="1"/>
+      <s:c r="F48" s="1" t="n">
+        <s:v>-3223</s:v>
+      </s:c>
+      <s:c r="G48" s="1" t="n">
+        <s:v>3186.27</s:v>
+      </s:c>
+      <s:c r="H48" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I48" s="1" t="n">
+        <s:v>11837.02</s:v>
+      </s:c>
+      <s:c r="J48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K48" s="1" t="n">
+        <s:v>-1116.9</s:v>
+      </s:c>
+      <s:c r="L48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N48" s="1" t="n">
+        <s:v>11039.39</s:v>
+      </s:c>
+      <s:c r="O48" s="1" t="n">
+        <s:v>183.23</s:v>
+      </s:c>
+      <s:c r="P48" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="49" s="1" customFormat="1" spans="1:16">
       <s:c r="A49" s="6" t="n">
@@ -4646,17 +6448,39 @@
       </s:c>
       <s:c r="D49" s="1"/>
       <s:c r="E49" s="1"/>
-      <s:c r="F49" s="1"/>
-      <s:c r="G49" s="1"/>
-      <s:c r="H49" s="1"/>
-      <s:c r="I49" s="1"/>
-      <s:c r="J49" s="1"/>
-      <s:c r="K49" s="1"/>
-      <s:c r="L49" s="1"/>
-      <s:c r="M49" s="1"/>
-      <s:c r="N49" s="1"/>
-      <s:c r="O49" s="1"/>
-      <s:c r="P49" s="1"/>
+      <s:c r="F49" s="1" t="n">
+        <s:v>-3273</s:v>
+      </s:c>
+      <s:c r="G49" s="1" t="n">
+        <s:v>3163.02</s:v>
+      </s:c>
+      <s:c r="H49" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I49" s="1" t="n">
+        <s:v>11951.38</s:v>
+      </s:c>
+      <s:c r="J49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K49" s="1" t="n">
+        <s:v>-1119.5</s:v>
+      </s:c>
+      <s:c r="L49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N49" s="1" t="n">
+        <s:v>10480.74</s:v>
+      </s:c>
+      <s:c r="O49" s="1" t="n">
+        <s:v>207.66</s:v>
+      </s:c>
+      <s:c r="P49" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="50" s="1" customFormat="1" spans="1:16">
       <s:c r="A50" s="6" t="n">
@@ -4670,17 +6494,39 @@
       </s:c>
       <s:c r="D50" s="1"/>
       <s:c r="E50" s="1"/>
-      <s:c r="F50" s="1"/>
-      <s:c r="G50" s="1"/>
-      <s:c r="H50" s="1"/>
-      <s:c r="I50" s="1"/>
-      <s:c r="J50" s="1"/>
-      <s:c r="K50" s="1"/>
-      <s:c r="L50" s="1"/>
-      <s:c r="M50" s="1"/>
-      <s:c r="N50" s="1"/>
-      <s:c r="O50" s="1"/>
-      <s:c r="P50" s="1"/>
+      <s:c r="F50" s="1" t="n">
+        <s:v>-3743</s:v>
+      </s:c>
+      <s:c r="G50" s="1" t="n">
+        <s:v>3134.86</s:v>
+      </s:c>
+      <s:c r="H50" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I50" s="1" t="n">
+        <s:v>11978.13</s:v>
+      </s:c>
+      <s:c r="J50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K50" s="1" t="n">
+        <s:v>-1116.4</s:v>
+      </s:c>
+      <s:c r="L50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N50" s="1" t="n">
+        <s:v>10947.63</s:v>
+      </s:c>
+      <s:c r="O50" s="1" t="n">
+        <s:v>200.79</s:v>
+      </s:c>
+      <s:c r="P50" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="51" s="1" customFormat="1" spans="1:16">
       <s:c r="A51" s="6" t="n">
@@ -4694,17 +6540,39 @@
       </s:c>
       <s:c r="D51" s="1"/>
       <s:c r="E51" s="1"/>
-      <s:c r="F51" s="1"/>
-      <s:c r="G51" s="1"/>
-      <s:c r="H51" s="1"/>
-      <s:c r="I51" s="1"/>
-      <s:c r="J51" s="1"/>
-      <s:c r="K51" s="1"/>
-      <s:c r="L51" s="1"/>
-      <s:c r="M51" s="1"/>
-      <s:c r="N51" s="1"/>
-      <s:c r="O51" s="1"/>
-      <s:c r="P51" s="1"/>
+      <s:c r="F51" s="1" t="n">
+        <s:v>-3753</s:v>
+      </s:c>
+      <s:c r="G51" s="1" t="n">
+        <s:v>3148.19</s:v>
+      </s:c>
+      <s:c r="H51" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I51" s="1" t="n">
+        <s:v>11902.72</s:v>
+      </s:c>
+      <s:c r="J51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K51" s="1" t="n">
+        <s:v>-1116.6</s:v>
+      </s:c>
+      <s:c r="L51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N51" s="1" t="n">
+        <s:v>10541.67</s:v>
+      </s:c>
+      <s:c r="O51" s="1" t="n">
+        <s:v>193.93</s:v>
+      </s:c>
+      <s:c r="P51" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="52" s="1" customFormat="1" spans="1:16">
       <s:c r="A52" s="6" t="n">
@@ -4718,17 +6586,39 @@
       </s:c>
       <s:c r="D52" s="1"/>
       <s:c r="E52" s="1"/>
-      <s:c r="F52" s="1"/>
-      <s:c r="G52" s="1"/>
-      <s:c r="H52" s="1"/>
-      <s:c r="I52" s="1"/>
-      <s:c r="J52" s="1"/>
-      <s:c r="K52" s="1"/>
-      <s:c r="L52" s="1"/>
-      <s:c r="M52" s="1"/>
-      <s:c r="N52" s="1"/>
-      <s:c r="O52" s="1"/>
-      <s:c r="P52" s="1"/>
+      <s:c r="F52" s="1" t="n">
+        <s:v>-3723</s:v>
+      </s:c>
+      <s:c r="G52" s="1" t="n">
+        <s:v>3167.22</s:v>
+      </s:c>
+      <s:c r="H52" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I52" s="1" t="n">
+        <s:v>11829.74</s:v>
+      </s:c>
+      <s:c r="J52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K52" s="1" t="n">
+        <s:v>-1111.2</s:v>
+      </s:c>
+      <s:c r="L52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N52" s="1" t="n">
+        <s:v>10843.2</s:v>
+      </s:c>
+      <s:c r="O52" s="1" t="n">
+        <s:v>196.54</s:v>
+      </s:c>
+      <s:c r="P52" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="53" s="1" customFormat="1" spans="1:16">
       <s:c r="A53" s="6" t="n">
@@ -4742,17 +6632,39 @@
       </s:c>
       <s:c r="D53" s="1"/>
       <s:c r="E53" s="1"/>
-      <s:c r="F53" s="1"/>
-      <s:c r="G53" s="1"/>
-      <s:c r="H53" s="1"/>
-      <s:c r="I53" s="1"/>
-      <s:c r="J53" s="1"/>
-      <s:c r="K53" s="1"/>
-      <s:c r="L53" s="1"/>
-      <s:c r="M53" s="1"/>
-      <s:c r="N53" s="1"/>
-      <s:c r="O53" s="1"/>
-      <s:c r="P53" s="1"/>
+      <s:c r="F53" s="1" t="n">
+        <s:v>-3253</s:v>
+      </s:c>
+      <s:c r="G53" s="1" t="n">
+        <s:v>3155.06</s:v>
+      </s:c>
+      <s:c r="H53" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I53" s="1" t="n">
+        <s:v>11680.8</s:v>
+      </s:c>
+      <s:c r="J53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K53" s="1" t="n">
+        <s:v>-1108.9</s:v>
+      </s:c>
+      <s:c r="L53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N53" s="1" t="n">
+        <s:v>11078.7</s:v>
+      </s:c>
+      <s:c r="O53" s="1" t="n">
+        <s:v>180.64</s:v>
+      </s:c>
+      <s:c r="P53" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="54" s="1" customFormat="1" spans="1:16">
       <s:c r="A54" s="6" t="n">
@@ -4766,17 +6678,39 @@
       </s:c>
       <s:c r="D54" s="1"/>
       <s:c r="E54" s="1"/>
-      <s:c r="F54" s="1"/>
-      <s:c r="G54" s="1"/>
-      <s:c r="H54" s="1"/>
-      <s:c r="I54" s="1"/>
-      <s:c r="J54" s="1"/>
-      <s:c r="K54" s="1"/>
-      <s:c r="L54" s="1"/>
-      <s:c r="M54" s="1"/>
-      <s:c r="N54" s="1"/>
-      <s:c r="O54" s="1"/>
-      <s:c r="P54" s="1"/>
+      <s:c r="F54" s="1" t="n">
+        <s:v>-2793</s:v>
+      </s:c>
+      <s:c r="G54" s="1" t="n">
+        <s:v>3164.38</s:v>
+      </s:c>
+      <s:c r="H54" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I54" s="1" t="n">
+        <s:v>11547.49</s:v>
+      </s:c>
+      <s:c r="J54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K54" s="1" t="n">
+        <s:v>-1109</s:v>
+      </s:c>
+      <s:c r="L54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N54" s="1" t="n">
+        <s:v>10646.83</s:v>
+      </s:c>
+      <s:c r="O54" s="1" t="n">
+        <s:v>174.91</s:v>
+      </s:c>
+      <s:c r="P54" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="55" s="1" customFormat="1" spans="1:16">
       <s:c r="A55" s="6" t="n">
@@ -4790,17 +6724,39 @@
       </s:c>
       <s:c r="D55" s="1"/>
       <s:c r="E55" s="1"/>
-      <s:c r="F55" s="1"/>
-      <s:c r="G55" s="1"/>
-      <s:c r="H55" s="1"/>
-      <s:c r="I55" s="1"/>
-      <s:c r="J55" s="1"/>
-      <s:c r="K55" s="1"/>
-      <s:c r="L55" s="1"/>
-      <s:c r="M55" s="1"/>
-      <s:c r="N55" s="1"/>
-      <s:c r="O55" s="1"/>
-      <s:c r="P55" s="1"/>
+      <s:c r="F55" s="1" t="n">
+        <s:v>-2453</s:v>
+      </s:c>
+      <s:c r="G55" s="1" t="n">
+        <s:v>3142.01</s:v>
+      </s:c>
+      <s:c r="H55" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I55" s="1" t="n">
+        <s:v>11355.82</s:v>
+      </s:c>
+      <s:c r="J55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K55" s="1" t="n">
+        <s:v>-1106.3</s:v>
+      </s:c>
+      <s:c r="L55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N55" s="1" t="n">
+        <s:v>10980.78</s:v>
+      </s:c>
+      <s:c r="O55" s="1" t="n">
+        <s:v>180.8</s:v>
+      </s:c>
+      <s:c r="P55" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="56" s="1" customFormat="1" spans="1:16">
       <s:c r="A56" s="6" t="n">
@@ -4814,17 +6770,39 @@
       </s:c>
       <s:c r="D56" s="1"/>
       <s:c r="E56" s="1"/>
-      <s:c r="F56" s="1"/>
-      <s:c r="G56" s="1"/>
-      <s:c r="H56" s="1"/>
-      <s:c r="I56" s="1"/>
-      <s:c r="J56" s="1"/>
-      <s:c r="K56" s="1"/>
-      <s:c r="L56" s="1"/>
-      <s:c r="M56" s="1"/>
-      <s:c r="N56" s="1"/>
-      <s:c r="O56" s="1"/>
-      <s:c r="P56" s="1"/>
+      <s:c r="F56" s="1" t="n">
+        <s:v>-1900</s:v>
+      </s:c>
+      <s:c r="G56" s="1" t="n">
+        <s:v>3147.65</s:v>
+      </s:c>
+      <s:c r="H56" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I56" s="1" t="n">
+        <s:v>11237.15</s:v>
+      </s:c>
+      <s:c r="J56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K56" s="1" t="n">
+        <s:v>-1105.2</s:v>
+      </s:c>
+      <s:c r="L56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N56" s="1" t="n">
+        <s:v>10963.85</s:v>
+      </s:c>
+      <s:c r="O56" s="1" t="n">
+        <s:v>183.35</s:v>
+      </s:c>
+      <s:c r="P56" s="1" t="n">
+        <s:v>68</s:v>
+      </s:c>
     </s:row>
     <s:row r="57" s="1" customFormat="1" spans="1:16">
       <s:c r="A57" s="6" t="n">
@@ -4838,17 +6816,39 @@
       </s:c>
       <s:c r="D57" s="1"/>
       <s:c r="E57" s="1"/>
-      <s:c r="F57" s="1"/>
-      <s:c r="G57" s="1"/>
-      <s:c r="H57" s="1"/>
-      <s:c r="I57" s="1"/>
-      <s:c r="J57" s="1"/>
-      <s:c r="K57" s="1"/>
-      <s:c r="L57" s="1"/>
-      <s:c r="M57" s="1"/>
-      <s:c r="N57" s="1"/>
-      <s:c r="O57" s="1"/>
-      <s:c r="P57" s="1"/>
+      <s:c r="F57" s="1" t="n">
+        <s:v>-1490</s:v>
+      </s:c>
+      <s:c r="G57" s="1" t="n">
+        <s:v>3120.32</s:v>
+      </s:c>
+      <s:c r="H57" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I57" s="1" t="n">
+        <s:v>10973.37</s:v>
+      </s:c>
+      <s:c r="J57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K57" s="1" t="n">
+        <s:v>-1101.2</s:v>
+      </s:c>
+      <s:c r="L57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N57" s="1" t="n">
+        <s:v>10951.23</s:v>
+      </s:c>
+      <s:c r="O57" s="1" t="n">
+        <s:v>181.49</s:v>
+      </s:c>
+      <s:c r="P57" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="58" s="1" customFormat="1" spans="1:16">
       <s:c r="A58" s="6" t="n">
@@ -4862,17 +6862,39 @@
       </s:c>
       <s:c r="D58" s="1"/>
       <s:c r="E58" s="1"/>
-      <s:c r="F58" s="1"/>
-      <s:c r="G58" s="1"/>
-      <s:c r="H58" s="1"/>
-      <s:c r="I58" s="1"/>
-      <s:c r="J58" s="1"/>
-      <s:c r="K58" s="1"/>
-      <s:c r="L58" s="1"/>
-      <s:c r="M58" s="1"/>
-      <s:c r="N58" s="1"/>
-      <s:c r="O58" s="1"/>
-      <s:c r="P58" s="1"/>
+      <s:c r="F58" s="1" t="n">
+        <s:v>-730</s:v>
+      </s:c>
+      <s:c r="G58" s="1" t="n">
+        <s:v>3104.79</s:v>
+      </s:c>
+      <s:c r="H58" s="1" t="n">
+        <s:v>0.96</s:v>
+      </s:c>
+      <s:c r="I58" s="1" t="n">
+        <s:v>10645.82</s:v>
+      </s:c>
+      <s:c r="J58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K58" s="1" t="n">
+        <s:v>-1106.2</s:v>
+      </s:c>
+      <s:c r="L58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N58" s="1" t="n">
+        <s:v>10879.75</s:v>
+      </s:c>
+      <s:c r="O58" s="1" t="n">
+        <s:v>170.19</s:v>
+      </s:c>
+      <s:c r="P58" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="59" s="1" customFormat="1" spans="1:16">
       <s:c r="A59" s="6" t="n">
@@ -4886,17 +6908,39 @@
       </s:c>
       <s:c r="D59" s="1"/>
       <s:c r="E59" s="1"/>
-      <s:c r="F59" s="1"/>
-      <s:c r="G59" s="1"/>
-      <s:c r="H59" s="1"/>
-      <s:c r="I59" s="1"/>
-      <s:c r="J59" s="1"/>
-      <s:c r="K59" s="1"/>
-      <s:c r="L59" s="1"/>
-      <s:c r="M59" s="1"/>
-      <s:c r="N59" s="1"/>
-      <s:c r="O59" s="1"/>
-      <s:c r="P59" s="1"/>
+      <s:c r="F59" s="1" t="n">
+        <s:v>-620</s:v>
+      </s:c>
+      <s:c r="G59" s="1" t="n">
+        <s:v>3072.49</s:v>
+      </s:c>
+      <s:c r="H59" s="1" t="n">
+        <s:v>0.96</s:v>
+      </s:c>
+      <s:c r="I59" s="1" t="n">
+        <s:v>10270.54</s:v>
+      </s:c>
+      <s:c r="J59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K59" s="1" t="n">
+        <s:v>-1102.1</s:v>
+      </s:c>
+      <s:c r="L59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N59" s="1" t="n">
+        <s:v>11799.47</s:v>
+      </s:c>
+      <s:c r="O59" s="1" t="n">
+        <s:v>177.84</s:v>
+      </s:c>
+      <s:c r="P59" s="1" t="n">
+        <s:v>69</s:v>
+      </s:c>
     </s:row>
     <s:row r="60" s="1" customFormat="1" spans="1:16">
       <s:c r="A60" s="6" t="n">
@@ -4910,17 +6954,39 @@
       </s:c>
       <s:c r="D60" s="1"/>
       <s:c r="E60" s="1"/>
-      <s:c r="F60" s="1"/>
-      <s:c r="G60" s="1"/>
-      <s:c r="H60" s="1"/>
-      <s:c r="I60" s="1"/>
-      <s:c r="J60" s="1"/>
-      <s:c r="K60" s="1"/>
-      <s:c r="L60" s="1"/>
-      <s:c r="M60" s="1"/>
-      <s:c r="N60" s="1"/>
-      <s:c r="O60" s="1"/>
-      <s:c r="P60" s="1"/>
+      <s:c r="F60" s="1" t="n">
+        <s:v>-410</s:v>
+      </s:c>
+      <s:c r="G60" s="1" t="n">
+        <s:v>3070.38</s:v>
+      </s:c>
+      <s:c r="H60" s="1" t="n">
+        <s:v>0.96</s:v>
+      </s:c>
+      <s:c r="I60" s="1" t="n">
+        <s:v>9931.07</s:v>
+      </s:c>
+      <s:c r="J60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K60" s="1" t="n">
+        <s:v>-1095.7</s:v>
+      </s:c>
+      <s:c r="L60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N60" s="1" t="n">
+        <s:v>11972.56</s:v>
+      </s:c>
+      <s:c r="O60" s="1" t="n">
+        <s:v>176.34</s:v>
+      </s:c>
+      <s:c r="P60" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="61" s="1" customFormat="1" spans="1:16">
       <s:c r="A61" s="6" t="n">
@@ -4934,17 +7000,39 @@
       </s:c>
       <s:c r="D61" s="1"/>
       <s:c r="E61" s="1"/>
-      <s:c r="F61" s="1"/>
-      <s:c r="G61" s="1"/>
-      <s:c r="H61" s="1"/>
-      <s:c r="I61" s="1"/>
-      <s:c r="J61" s="1"/>
-      <s:c r="K61" s="1"/>
-      <s:c r="L61" s="1"/>
-      <s:c r="M61" s="1"/>
-      <s:c r="N61" s="1"/>
-      <s:c r="O61" s="1"/>
-      <s:c r="P61" s="1"/>
+      <s:c r="F61" s="1" t="n">
+        <s:v>-160</s:v>
+      </s:c>
+      <s:c r="G61" s="1" t="n">
+        <s:v>3047.92</s:v>
+      </s:c>
+      <s:c r="H61" s="1" t="n">
+        <s:v>0.96</s:v>
+      </s:c>
+      <s:c r="I61" s="1" t="n">
+        <s:v>9508.84</s:v>
+      </s:c>
+      <s:c r="J61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K61" s="1" t="n">
+        <s:v>-1097.6</s:v>
+      </s:c>
+      <s:c r="L61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N61" s="1" t="n">
+        <s:v>12874.96</s:v>
+      </s:c>
+      <s:c r="O61" s="1" t="n">
+        <s:v>185.33</s:v>
+      </s:c>
+      <s:c r="P61" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="62" s="1" customFormat="1" spans="1:16">
       <s:c r="A62" s="6" t="n">
@@ -4958,17 +7046,39 @@
       </s:c>
       <s:c r="D62" s="1"/>
       <s:c r="E62" s="1"/>
-      <s:c r="F62" s="1"/>
-      <s:c r="G62" s="1"/>
-      <s:c r="H62" s="1"/>
-      <s:c r="I62" s="1"/>
-      <s:c r="J62" s="1"/>
-      <s:c r="K62" s="1"/>
-      <s:c r="L62" s="1"/>
-      <s:c r="M62" s="1"/>
-      <s:c r="N62" s="1"/>
-      <s:c r="O62" s="1"/>
-      <s:c r="P62" s="1"/>
+      <s:c r="F62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G62" s="1" t="n">
+        <s:v>3011.41</s:v>
+      </s:c>
+      <s:c r="H62" s="1" t="n">
+        <s:v>0.86</s:v>
+      </s:c>
+      <s:c r="I62" s="1" t="n">
+        <s:v>8830.13</s:v>
+      </s:c>
+      <s:c r="J62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K62" s="1" t="n">
+        <s:v>-1092.1</s:v>
+      </s:c>
+      <s:c r="L62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N62" s="1" t="n">
+        <s:v>13585.87</s:v>
+      </s:c>
+      <s:c r="O62" s="1" t="n">
+        <s:v>196.43</s:v>
+      </s:c>
+      <s:c r="P62" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="63" s="1" customFormat="1" spans="1:16">
       <s:c r="A63" s="6" t="n">
@@ -4982,17 +7092,39 @@
       </s:c>
       <s:c r="D63" s="1"/>
       <s:c r="E63" s="1"/>
-      <s:c r="F63" s="1"/>
-      <s:c r="G63" s="1"/>
-      <s:c r="H63" s="1"/>
-      <s:c r="I63" s="1"/>
-      <s:c r="J63" s="1"/>
-      <s:c r="K63" s="1"/>
-      <s:c r="L63" s="1"/>
-      <s:c r="M63" s="1"/>
-      <s:c r="N63" s="1"/>
-      <s:c r="O63" s="1"/>
-      <s:c r="P63" s="1"/>
+      <s:c r="F63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G63" s="1" t="n">
+        <s:v>2978.29</s:v>
+      </s:c>
+      <s:c r="H63" s="1" t="n">
+        <s:v>0.86</s:v>
+      </s:c>
+      <s:c r="I63" s="1" t="n">
+        <s:v>8249.51</s:v>
+      </s:c>
+      <s:c r="J63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K63" s="1" t="n">
+        <s:v>-1090.3</s:v>
+      </s:c>
+      <s:c r="L63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N63" s="1" t="n">
+        <s:v>14857.37</s:v>
+      </s:c>
+      <s:c r="O63" s="1" t="n">
+        <s:v>196.08</s:v>
+      </s:c>
+      <s:c r="P63" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="64" s="1" customFormat="1" spans="1:16">
       <s:c r="A64" s="6" t="n">
@@ -5006,17 +7138,39 @@
       </s:c>
       <s:c r="D64" s="1"/>
       <s:c r="E64" s="1"/>
-      <s:c r="F64" s="1"/>
-      <s:c r="G64" s="1"/>
-      <s:c r="H64" s="1"/>
-      <s:c r="I64" s="1"/>
-      <s:c r="J64" s="1"/>
-      <s:c r="K64" s="1"/>
-      <s:c r="L64" s="1"/>
-      <s:c r="M64" s="1"/>
-      <s:c r="N64" s="1"/>
-      <s:c r="O64" s="1"/>
-      <s:c r="P64" s="1"/>
+      <s:c r="F64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G64" s="1" t="n">
+        <s:v>2938.57</s:v>
+      </s:c>
+      <s:c r="H64" s="1" t="n">
+        <s:v>0.86</s:v>
+      </s:c>
+      <s:c r="I64" s="1" t="n">
+        <s:v>7650.99</s:v>
+      </s:c>
+      <s:c r="J64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K64" s="1" t="n">
+        <s:v>-1088.4</s:v>
+      </s:c>
+      <s:c r="L64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N64" s="1" t="n">
+        <s:v>16339.39</s:v>
+      </s:c>
+      <s:c r="O64" s="1" t="n">
+        <s:v>209.58</s:v>
+      </s:c>
+      <s:c r="P64" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="65" s="1" customFormat="1" spans="1:16">
       <s:c r="A65" s="6" t="n">
@@ -5030,17 +7184,39 @@
       </s:c>
       <s:c r="D65" s="1"/>
       <s:c r="E65" s="1"/>
-      <s:c r="F65" s="1"/>
-      <s:c r="G65" s="1"/>
-      <s:c r="H65" s="1"/>
-      <s:c r="I65" s="1"/>
-      <s:c r="J65" s="1"/>
-      <s:c r="K65" s="1"/>
-      <s:c r="L65" s="1"/>
-      <s:c r="M65" s="1"/>
-      <s:c r="N65" s="1"/>
-      <s:c r="O65" s="1"/>
-      <s:c r="P65" s="1"/>
+      <s:c r="F65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G65" s="1" t="n">
+        <s:v>2875.92</s:v>
+      </s:c>
+      <s:c r="H65" s="1" t="n">
+        <s:v>0.86</s:v>
+      </s:c>
+      <s:c r="I65" s="1" t="n">
+        <s:v>7000.18</s:v>
+      </s:c>
+      <s:c r="J65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K65" s="1" t="n">
+        <s:v>-1087.3</s:v>
+      </s:c>
+      <s:c r="L65" s="1" t="n">
+        <s:v>200</s:v>
+      </s:c>
+      <s:c r="M65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N65" s="1" t="n">
+        <s:v>17508.61</s:v>
+      </s:c>
+      <s:c r="O65" s="1" t="n">
+        <s:v>225.73</s:v>
+      </s:c>
+      <s:c r="P65" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="66" s="1" customFormat="1" spans="1:16">
       <s:c r="A66" s="6" t="n">
@@ -5054,17 +7230,39 @@
       </s:c>
       <s:c r="D66" s="1"/>
       <s:c r="E66" s="1"/>
-      <s:c r="F66" s="1"/>
-      <s:c r="G66" s="1"/>
-      <s:c r="H66" s="1"/>
-      <s:c r="I66" s="1"/>
-      <s:c r="J66" s="1"/>
-      <s:c r="K66" s="1"/>
-      <s:c r="L66" s="1"/>
-      <s:c r="M66" s="1"/>
-      <s:c r="N66" s="1"/>
-      <s:c r="O66" s="1"/>
-      <s:c r="P66" s="1"/>
+      <s:c r="F66" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G66" s="1" t="n">
+        <s:v>2822.17</s:v>
+      </s:c>
+      <s:c r="H66" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I66" s="1" t="n">
+        <s:v>6017.96</s:v>
+      </s:c>
+      <s:c r="J66" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K66" s="1" t="n">
+        <s:v>-796.1</s:v>
+      </s:c>
+      <s:c r="L66" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M66" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N66" s="1" t="n">
+        <s:v>19038.56</s:v>
+      </s:c>
+      <s:c r="O66" s="1" t="n">
+        <s:v>250.02</s:v>
+      </s:c>
+      <s:c r="P66" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="67" s="1" customFormat="1" spans="1:16">
       <s:c r="A67" s="6" t="n">
@@ -5078,17 +7276,39 @@
       </s:c>
       <s:c r="D67" s="1"/>
       <s:c r="E67" s="1"/>
-      <s:c r="F67" s="1"/>
-      <s:c r="G67" s="1"/>
-      <s:c r="H67" s="1"/>
-      <s:c r="I67" s="1"/>
-      <s:c r="J67" s="1"/>
-      <s:c r="K67" s="1"/>
-      <s:c r="L67" s="1"/>
-      <s:c r="M67" s="1"/>
-      <s:c r="N67" s="1"/>
-      <s:c r="O67" s="1"/>
-      <s:c r="P67" s="1"/>
+      <s:c r="F67" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G67" s="1" t="n">
+        <s:v>2793.63</s:v>
+      </s:c>
+      <s:c r="H67" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I67" s="1" t="n">
+        <s:v>5126.46</s:v>
+      </s:c>
+      <s:c r="J67" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K67" s="1" t="n">
+        <s:v>-490</s:v>
+      </s:c>
+      <s:c r="L67" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M67" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N67" s="1" t="n">
+        <s:v>19516.69</s:v>
+      </s:c>
+      <s:c r="O67" s="1" t="n">
+        <s:v>251.53</s:v>
+      </s:c>
+      <s:c r="P67" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="68" s="1" customFormat="1" spans="1:16">
       <s:c r="A68" s="6" t="n">
@@ -5102,17 +7322,39 @@
       </s:c>
       <s:c r="D68" s="1"/>
       <s:c r="E68" s="1"/>
-      <s:c r="F68" s="1"/>
-      <s:c r="G68" s="1"/>
-      <s:c r="H68" s="1"/>
-      <s:c r="I68" s="1"/>
-      <s:c r="J68" s="1"/>
-      <s:c r="K68" s="1"/>
-      <s:c r="L68" s="1"/>
-      <s:c r="M68" s="1"/>
-      <s:c r="N68" s="1"/>
-      <s:c r="O68" s="1"/>
-      <s:c r="P68" s="1"/>
+      <s:c r="F68" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G68" s="1" t="n">
+        <s:v>2732.29</s:v>
+      </s:c>
+      <s:c r="H68" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I68" s="1" t="n">
+        <s:v>4357.17</s:v>
+      </s:c>
+      <s:c r="J68" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K68" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L68" s="1" t="n">
+        <s:v>45.91</s:v>
+      </s:c>
+      <s:c r="M68" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N68" s="1" t="n">
+        <s:v>20108.93</s:v>
+      </s:c>
+      <s:c r="O68" s="1" t="n">
+        <s:v>264.51</s:v>
+      </s:c>
+      <s:c r="P68" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="69" s="1" customFormat="1" spans="1:16">
       <s:c r="A69" s="6" t="n">
@@ -5126,17 +7368,39 @@
       </s:c>
       <s:c r="D69" s="1"/>
       <s:c r="E69" s="1"/>
-      <s:c r="F69" s="1"/>
-      <s:c r="G69" s="1"/>
-      <s:c r="H69" s="1"/>
-      <s:c r="I69" s="1"/>
-      <s:c r="J69" s="1"/>
-      <s:c r="K69" s="1"/>
-      <s:c r="L69" s="1"/>
-      <s:c r="M69" s="1"/>
-      <s:c r="N69" s="1"/>
-      <s:c r="O69" s="1"/>
-      <s:c r="P69" s="1"/>
+      <s:c r="F69" s="1" t="n">
+        <s:v>100</s:v>
+      </s:c>
+      <s:c r="G69" s="1" t="n">
+        <s:v>2710.67</s:v>
+      </s:c>
+      <s:c r="H69" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I69" s="1" t="n">
+        <s:v>3362.45</s:v>
+      </s:c>
+      <s:c r="J69" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K69" s="1" t="n">
+        <s:v>304.6</s:v>
+      </s:c>
+      <s:c r="L69" s="1" t="n">
+        <s:v>72.5</s:v>
+      </s:c>
+      <s:c r="M69" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N69" s="1" t="n">
+        <s:v>20883.38</s:v>
+      </s:c>
+      <s:c r="O69" s="1" t="n">
+        <s:v>362.61</s:v>
+      </s:c>
+      <s:c r="P69" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="70" s="1" customFormat="1" spans="1:16">
       <s:c r="A70" s="6" t="n">
@@ -5150,17 +7414,39 @@
       </s:c>
       <s:c r="D70" s="1"/>
       <s:c r="E70" s="1"/>
-      <s:c r="F70" s="1"/>
-      <s:c r="G70" s="1"/>
-      <s:c r="H70" s="1"/>
-      <s:c r="I70" s="1"/>
-      <s:c r="J70" s="1"/>
-      <s:c r="K70" s="1"/>
-      <s:c r="L70" s="1"/>
-      <s:c r="M70" s="1"/>
-      <s:c r="N70" s="1"/>
-      <s:c r="O70" s="1"/>
-      <s:c r="P70" s="1"/>
+      <s:c r="F70" s="1" t="n">
+        <s:v>820</s:v>
+      </s:c>
+      <s:c r="G70" s="1" t="n">
+        <s:v>2655.06</s:v>
+      </s:c>
+      <s:c r="H70" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I70" s="1" t="n">
+        <s:v>2736.82</s:v>
+      </s:c>
+      <s:c r="J70" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K70" s="1" t="n">
+        <s:v>1109</s:v>
+      </s:c>
+      <s:c r="L70" s="1" t="n">
+        <s:v>72.82</s:v>
+      </s:c>
+      <s:c r="M70" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N70" s="1" t="n">
+        <s:v>21021.19</s:v>
+      </s:c>
+      <s:c r="O70" s="1" t="n">
+        <s:v>377.22</s:v>
+      </s:c>
+      <s:c r="P70" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="71" s="1" customFormat="1" spans="1:16">
       <s:c r="A71" s="6" t="n">
@@ -5174,17 +7460,39 @@
       </s:c>
       <s:c r="D71" s="1"/>
       <s:c r="E71" s="1"/>
-      <s:c r="F71" s="1"/>
-      <s:c r="G71" s="1"/>
-      <s:c r="H71" s="1"/>
-      <s:c r="I71" s="1"/>
-      <s:c r="J71" s="1"/>
-      <s:c r="K71" s="1"/>
-      <s:c r="L71" s="1"/>
-      <s:c r="M71" s="1"/>
-      <s:c r="N71" s="1"/>
-      <s:c r="O71" s="1"/>
-      <s:c r="P71" s="1"/>
+      <s:c r="F71" s="1" t="n">
+        <s:v>1120</s:v>
+      </s:c>
+      <s:c r="G71" s="1" t="n">
+        <s:v>2596.76</s:v>
+      </s:c>
+      <s:c r="H71" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I71" s="1" t="n">
+        <s:v>2072.54</s:v>
+      </s:c>
+      <s:c r="J71" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K71" s="1" t="n">
+        <s:v>1102.2</s:v>
+      </s:c>
+      <s:c r="L71" s="1" t="n">
+        <s:v>100.59</s:v>
+      </s:c>
+      <s:c r="M71" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N71" s="1" t="n">
+        <s:v>21530.28</s:v>
+      </s:c>
+      <s:c r="O71" s="1" t="n">
+        <s:v>407.04</s:v>
+      </s:c>
+      <s:c r="P71" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="72" s="1" customFormat="1" spans="1:16">
       <s:c r="A72" s="6" t="n">
@@ -5198,17 +7506,39 @@
       </s:c>
       <s:c r="D72" s="1"/>
       <s:c r="E72" s="1"/>
-      <s:c r="F72" s="1"/>
-      <s:c r="G72" s="1"/>
-      <s:c r="H72" s="1"/>
-      <s:c r="I72" s="1"/>
-      <s:c r="J72" s="1"/>
-      <s:c r="K72" s="1"/>
-      <s:c r="L72" s="1"/>
-      <s:c r="M72" s="1"/>
-      <s:c r="N72" s="1"/>
-      <s:c r="O72" s="1"/>
-      <s:c r="P72" s="1"/>
+      <s:c r="F72" s="1" t="n">
+        <s:v>1260</s:v>
+      </s:c>
+      <s:c r="G72" s="1" t="n">
+        <s:v>2537.21</s:v>
+      </s:c>
+      <s:c r="H72" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I72" s="1" t="n">
+        <s:v>1439.48</s:v>
+      </s:c>
+      <s:c r="J72" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K72" s="1" t="n">
+        <s:v>1100.7</s:v>
+      </s:c>
+      <s:c r="L72" s="1" t="n">
+        <s:v>369.48</s:v>
+      </s:c>
+      <s:c r="M72" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N72" s="1" t="n">
+        <s:v>21565.87</s:v>
+      </s:c>
+      <s:c r="O72" s="1" t="n">
+        <s:v>482.57</s:v>
+      </s:c>
+      <s:c r="P72" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="73" s="1" customFormat="1" spans="1:16">
       <s:c r="A73" s="6" t="n">
@@ -5222,17 +7552,39 @@
       </s:c>
       <s:c r="D73" s="1"/>
       <s:c r="E73" s="1"/>
-      <s:c r="F73" s="1"/>
-      <s:c r="G73" s="1"/>
-      <s:c r="H73" s="1"/>
-      <s:c r="I73" s="1"/>
-      <s:c r="J73" s="1"/>
-      <s:c r="K73" s="1"/>
-      <s:c r="L73" s="1"/>
-      <s:c r="M73" s="1"/>
-      <s:c r="N73" s="1"/>
-      <s:c r="O73" s="1"/>
-      <s:c r="P73" s="1"/>
+      <s:c r="F73" s="1" t="n">
+        <s:v>1355</s:v>
+      </s:c>
+      <s:c r="G73" s="1" t="n">
+        <s:v>2482.22</s:v>
+      </s:c>
+      <s:c r="H73" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I73" s="1" t="n">
+        <s:v>1004.44</s:v>
+      </s:c>
+      <s:c r="J73" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K73" s="1" t="n">
+        <s:v>1099.5</s:v>
+      </s:c>
+      <s:c r="L73" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M73" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N73" s="1" t="n">
+        <s:v>21563.92</s:v>
+      </s:c>
+      <s:c r="O73" s="1" t="n">
+        <s:v>551.83</s:v>
+      </s:c>
+      <s:c r="P73" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="74" s="1" customFormat="1" spans="1:16">
       <s:c r="A74" s="6" t="n">
@@ -5246,17 +7598,39 @@
       </s:c>
       <s:c r="D74" s="1"/>
       <s:c r="E74" s="1"/>
-      <s:c r="F74" s="1"/>
-      <s:c r="G74" s="1"/>
-      <s:c r="H74" s="1"/>
-      <s:c r="I74" s="1"/>
-      <s:c r="J74" s="1"/>
-      <s:c r="K74" s="1"/>
-      <s:c r="L74" s="1"/>
-      <s:c r="M74" s="1"/>
-      <s:c r="N74" s="1"/>
-      <s:c r="O74" s="1"/>
-      <s:c r="P74" s="1"/>
+      <s:c r="F74" s="1" t="n">
+        <s:v>2030</s:v>
+      </s:c>
+      <s:c r="G74" s="1" t="n">
+        <s:v>2464.43</s:v>
+      </s:c>
+      <s:c r="H74" s="1" t="n">
+        <s:v>1.86</s:v>
+      </s:c>
+      <s:c r="I74" s="1" t="n">
+        <s:v>700.79</s:v>
+      </s:c>
+      <s:c r="J74" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K74" s="1" t="n">
+        <s:v>1101.2</s:v>
+      </s:c>
+      <s:c r="L74" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M74" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N74" s="1" t="n">
+        <s:v>20356.96</s:v>
+      </s:c>
+      <s:c r="O74" s="1" t="n">
+        <s:v>612.07</s:v>
+      </s:c>
+      <s:c r="P74" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="75" s="1" customFormat="1" spans="1:16">
       <s:c r="A75" s="6" t="n">
@@ -5270,17 +7644,39 @@
       </s:c>
       <s:c r="D75" s="1"/>
       <s:c r="E75" s="1"/>
-      <s:c r="F75" s="1"/>
-      <s:c r="G75" s="1"/>
-      <s:c r="H75" s="1"/>
-      <s:c r="I75" s="1"/>
-      <s:c r="J75" s="1"/>
-      <s:c r="K75" s="1"/>
-      <s:c r="L75" s="1"/>
-      <s:c r="M75" s="1"/>
-      <s:c r="N75" s="1"/>
-      <s:c r="O75" s="1"/>
-      <s:c r="P75" s="1"/>
+      <s:c r="F75" s="1" t="n">
+        <s:v>2030</s:v>
+      </s:c>
+      <s:c r="G75" s="1" t="n">
+        <s:v>2497.95</s:v>
+      </s:c>
+      <s:c r="H75" s="1" t="n">
+        <s:v>1.86</s:v>
+      </s:c>
+      <s:c r="I75" s="1" t="n">
+        <s:v>466.99</s:v>
+      </s:c>
+      <s:c r="J75" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K75" s="1" t="n">
+        <s:v>1099.8</s:v>
+      </s:c>
+      <s:c r="L75" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M75" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N75" s="1" t="n">
+        <s:v>20442.12</s:v>
+      </s:c>
+      <s:c r="O75" s="1" t="n">
+        <s:v>674.89</s:v>
+      </s:c>
+      <s:c r="P75" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="76" s="1" customFormat="1" spans="1:16">
       <s:c r="A76" s="6" t="n">
@@ -5294,17 +7690,39 @@
       </s:c>
       <s:c r="D76" s="1"/>
       <s:c r="E76" s="1"/>
-      <s:c r="F76" s="1"/>
-      <s:c r="G76" s="1"/>
-      <s:c r="H76" s="1"/>
-      <s:c r="I76" s="1"/>
-      <s:c r="J76" s="1"/>
-      <s:c r="K76" s="1"/>
-      <s:c r="L76" s="1"/>
-      <s:c r="M76" s="1"/>
-      <s:c r="N76" s="1"/>
-      <s:c r="O76" s="1"/>
-      <s:c r="P76" s="1"/>
+      <s:c r="F76" s="1" t="n">
+        <s:v>2090</s:v>
+      </s:c>
+      <s:c r="G76" s="1" t="n">
+        <s:v>2469.36</s:v>
+      </s:c>
+      <s:c r="H76" s="1" t="n">
+        <s:v>1.86</s:v>
+      </s:c>
+      <s:c r="I76" s="1" t="n">
+        <s:v>249.83</s:v>
+      </s:c>
+      <s:c r="J76" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K76" s="1" t="n">
+        <s:v>1099.8</s:v>
+      </s:c>
+      <s:c r="L76" s="1" t="n">
+        <s:v>369.02</s:v>
+      </s:c>
+      <s:c r="M76" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N76" s="1" t="n">
+        <s:v>20085.67</s:v>
+      </s:c>
+      <s:c r="O76" s="1" t="n">
+        <s:v>729.47</s:v>
+      </s:c>
+      <s:c r="P76" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="77" s="1" customFormat="1" spans="1:16">
       <s:c r="A77" s="6" t="n">
@@ -5318,17 +7736,39 @@
       </s:c>
       <s:c r="D77" s="1"/>
       <s:c r="E77" s="1"/>
-      <s:c r="F77" s="1"/>
-      <s:c r="G77" s="1"/>
-      <s:c r="H77" s="1"/>
-      <s:c r="I77" s="1"/>
-      <s:c r="J77" s="1"/>
-      <s:c r="K77" s="1"/>
-      <s:c r="L77" s="1"/>
-      <s:c r="M77" s="1"/>
-      <s:c r="N77" s="1"/>
-      <s:c r="O77" s="1"/>
-      <s:c r="P77" s="1"/>
+      <s:c r="F77" s="1" t="n">
+        <s:v>2050</s:v>
+      </s:c>
+      <s:c r="G77" s="1" t="n">
+        <s:v>2497.94</s:v>
+      </s:c>
+      <s:c r="H77" s="1" t="n">
+        <s:v>1.86</s:v>
+      </s:c>
+      <s:c r="I77" s="1" t="n">
+        <s:v>247.38</s:v>
+      </s:c>
+      <s:c r="J77" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K77" s="1" t="n">
+        <s:v>1100.6</s:v>
+      </s:c>
+      <s:c r="L77" s="1" t="n">
+        <s:v>363.41</s:v>
+      </s:c>
+      <s:c r="M77" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N77" s="1" t="n">
+        <s:v>19984.71</s:v>
+      </s:c>
+      <s:c r="O77" s="1" t="n">
+        <s:v>750.6</s:v>
+      </s:c>
+      <s:c r="P77" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="78" s="1" customFormat="1" spans="1:16">
       <s:c r="A78" s="6" t="n">
@@ -5342,17 +7782,39 @@
       </s:c>
       <s:c r="D78" s="1"/>
       <s:c r="E78" s="1"/>
-      <s:c r="F78" s="1"/>
-      <s:c r="G78" s="1"/>
-      <s:c r="H78" s="1"/>
-      <s:c r="I78" s="1"/>
-      <s:c r="J78" s="1"/>
-      <s:c r="K78" s="1"/>
-      <s:c r="L78" s="1"/>
-      <s:c r="M78" s="1"/>
-      <s:c r="N78" s="1"/>
-      <s:c r="O78" s="1"/>
-      <s:c r="P78" s="1"/>
+      <s:c r="F78" s="1" t="n">
+        <s:v>1495</s:v>
+      </s:c>
+      <s:c r="G78" s="1" t="n">
+        <s:v>2457.87</s:v>
+      </s:c>
+      <s:c r="H78" s="1" t="n">
+        <s:v>0.83</s:v>
+      </s:c>
+      <s:c r="I78" s="1" t="n">
+        <s:v>242.94</s:v>
+      </s:c>
+      <s:c r="J78" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K78" s="1" t="n">
+        <s:v>999.8</s:v>
+      </s:c>
+      <s:c r="L78" s="1" t="n">
+        <s:v>363.73</s:v>
+      </s:c>
+      <s:c r="M78" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N78" s="1" t="n">
+        <s:v>20499.47</s:v>
+      </s:c>
+      <s:c r="O78" s="1" t="n">
+        <s:v>791.06</s:v>
+      </s:c>
+      <s:c r="P78" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="79" s="1" customFormat="1" spans="1:16">
       <s:c r="A79" s="6" t="n">
@@ -5366,17 +7828,39 @@
       </s:c>
       <s:c r="D79" s="1"/>
       <s:c r="E79" s="1"/>
-      <s:c r="F79" s="1"/>
-      <s:c r="G79" s="1"/>
-      <s:c r="H79" s="1"/>
-      <s:c r="I79" s="1"/>
-      <s:c r="J79" s="1"/>
-      <s:c r="K79" s="1"/>
-      <s:c r="L79" s="1"/>
-      <s:c r="M79" s="1"/>
-      <s:c r="N79" s="1"/>
-      <s:c r="O79" s="1"/>
-      <s:c r="P79" s="1"/>
+      <s:c r="F79" s="1" t="n">
+        <s:v>1280</s:v>
+      </s:c>
+      <s:c r="G79" s="1" t="n">
+        <s:v>2481.8</s:v>
+      </s:c>
+      <s:c r="H79" s="1" t="n">
+        <s:v>0.83</s:v>
+      </s:c>
+      <s:c r="I79" s="1" t="n">
+        <s:v>254.75</s:v>
+      </s:c>
+      <s:c r="J79" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K79" s="1" t="n">
+        <s:v>748.4</s:v>
+      </s:c>
+      <s:c r="L79" s="1" t="n">
+        <s:v>364.19</s:v>
+      </s:c>
+      <s:c r="M79" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N79" s="1" t="n">
+        <s:v>20726.02</s:v>
+      </s:c>
+      <s:c r="O79" s="1" t="n">
+        <s:v>871.81</s:v>
+      </s:c>
+      <s:c r="P79" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="80" s="1" customFormat="1" spans="1:16">
       <s:c r="A80" s="6" t="n">
@@ -5390,17 +7874,39 @@
       </s:c>
       <s:c r="D80" s="1"/>
       <s:c r="E80" s="1"/>
-      <s:c r="F80" s="1"/>
-      <s:c r="G80" s="1"/>
-      <s:c r="H80" s="1"/>
-      <s:c r="I80" s="1"/>
-      <s:c r="J80" s="1"/>
-      <s:c r="K80" s="1"/>
-      <s:c r="L80" s="1"/>
-      <s:c r="M80" s="1"/>
-      <s:c r="N80" s="1"/>
-      <s:c r="O80" s="1"/>
-      <s:c r="P80" s="1"/>
+      <s:c r="F80" s="1" t="n">
+        <s:v>1215</s:v>
+      </s:c>
+      <s:c r="G80" s="1" t="n">
+        <s:v>2479.64</s:v>
+      </s:c>
+      <s:c r="H80" s="1" t="n">
+        <s:v>0.83</s:v>
+      </s:c>
+      <s:c r="I80" s="1" t="n">
+        <s:v>185.8</s:v>
+      </s:c>
+      <s:c r="J80" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K80" s="1" t="n">
+        <s:v>597.2</s:v>
+      </s:c>
+      <s:c r="L80" s="1" t="n">
+        <s:v>363.25</s:v>
+      </s:c>
+      <s:c r="M80" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N80" s="1" t="n">
+        <s:v>20587.6</s:v>
+      </s:c>
+      <s:c r="O80" s="1" t="n">
+        <s:v>947.58</s:v>
+      </s:c>
+      <s:c r="P80" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="81" s="1" customFormat="1" spans="1:16">
       <s:c r="A81" s="6" t="n">
@@ -5414,17 +7920,39 @@
       </s:c>
       <s:c r="D81" s="1"/>
       <s:c r="E81" s="1"/>
-      <s:c r="F81" s="1"/>
-      <s:c r="G81" s="1"/>
-      <s:c r="H81" s="1"/>
-      <s:c r="I81" s="1"/>
-      <s:c r="J81" s="1"/>
-      <s:c r="K81" s="1"/>
-      <s:c r="L81" s="1"/>
-      <s:c r="M81" s="1"/>
-      <s:c r="N81" s="1"/>
-      <s:c r="O81" s="1"/>
-      <s:c r="P81" s="1"/>
+      <s:c r="F81" s="1" t="n">
+        <s:v>935</s:v>
+      </s:c>
+      <s:c r="G81" s="1" t="n">
+        <s:v>2531.65</s:v>
+      </s:c>
+      <s:c r="H81" s="1" t="n">
+        <s:v>0.83</s:v>
+      </s:c>
+      <s:c r="I81" s="1" t="n">
+        <s:v>179.5</s:v>
+      </s:c>
+      <s:c r="J81" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K81" s="1" t="n">
+        <s:v>296.3</s:v>
+      </s:c>
+      <s:c r="L81" s="1" t="n">
+        <s:v>363.73</s:v>
+      </s:c>
+      <s:c r="M81" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N81" s="1" t="n">
+        <s:v>20245.11</s:v>
+      </s:c>
+      <s:c r="O81" s="1" t="n">
+        <s:v>1063.69</s:v>
+      </s:c>
+      <s:c r="P81" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="82" s="1" customFormat="1" spans="1:16">
       <s:c r="A82" s="6" t="n">
@@ -5438,17 +7966,39 @@
       </s:c>
       <s:c r="D82" s="1"/>
       <s:c r="E82" s="1"/>
-      <s:c r="F82" s="1"/>
-      <s:c r="G82" s="1"/>
-      <s:c r="H82" s="1"/>
-      <s:c r="I82" s="1"/>
-      <s:c r="J82" s="1"/>
-      <s:c r="K82" s="1"/>
-      <s:c r="L82" s="1"/>
-      <s:c r="M82" s="1"/>
-      <s:c r="N82" s="1"/>
-      <s:c r="O82" s="1"/>
-      <s:c r="P82" s="1"/>
+      <s:c r="F82" s="1" t="n">
+        <s:v>565</s:v>
+      </s:c>
+      <s:c r="G82" s="1" t="n">
+        <s:v>2506.58</s:v>
+      </s:c>
+      <s:c r="H82" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I82" s="1" t="n">
+        <s:v>160.5</s:v>
+      </s:c>
+      <s:c r="J82" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K82" s="1" t="n">
+        <s:v>149</s:v>
+      </s:c>
+      <s:c r="L82" s="1" t="n">
+        <s:v>363.42</s:v>
+      </s:c>
+      <s:c r="M82" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N82" s="1" t="n">
+        <s:v>20707.57</s:v>
+      </s:c>
+      <s:c r="O82" s="1" t="n">
+        <s:v>1155.25</s:v>
+      </s:c>
+      <s:c r="P82" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="83" s="1" customFormat="1" spans="1:16">
       <s:c r="A83" s="6" t="n">
@@ -5462,17 +8012,39 @@
       </s:c>
       <s:c r="D83" s="1"/>
       <s:c r="E83" s="1"/>
-      <s:c r="F83" s="1"/>
-      <s:c r="G83" s="1"/>
-      <s:c r="H83" s="1"/>
-      <s:c r="I83" s="1"/>
-      <s:c r="J83" s="1"/>
-      <s:c r="K83" s="1"/>
-      <s:c r="L83" s="1"/>
-      <s:c r="M83" s="1"/>
-      <s:c r="N83" s="1"/>
-      <s:c r="O83" s="1"/>
-      <s:c r="P83" s="1"/>
+      <s:c r="F83" s="1" t="n">
+        <s:v>560</s:v>
+      </s:c>
+      <s:c r="G83" s="1" t="n">
+        <s:v>2482.67</s:v>
+      </s:c>
+      <s:c r="H83" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I83" s="1" t="n">
+        <s:v>157.5</s:v>
+      </s:c>
+      <s:c r="J83" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K83" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L83" s="1" t="n">
+        <s:v>363.1</s:v>
+      </s:c>
+      <s:c r="M83" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N83" s="1" t="n">
+        <s:v>20677.61</s:v>
+      </s:c>
+      <s:c r="O83" s="1" t="n">
+        <s:v>1182.53</s:v>
+      </s:c>
+      <s:c r="P83" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="84" s="1" customFormat="1" spans="1:16">
       <s:c r="A84" s="6" t="n">
@@ -5486,17 +8058,39 @@
       </s:c>
       <s:c r="D84" s="1"/>
       <s:c r="E84" s="1"/>
-      <s:c r="F84" s="1"/>
-      <s:c r="G84" s="1"/>
-      <s:c r="H84" s="1"/>
-      <s:c r="I84" s="1"/>
-      <s:c r="J84" s="1"/>
-      <s:c r="K84" s="1"/>
-      <s:c r="L84" s="1"/>
-      <s:c r="M84" s="1"/>
-      <s:c r="N84" s="1"/>
-      <s:c r="O84" s="1"/>
-      <s:c r="P84" s="1"/>
+      <s:c r="F84" s="1" t="n">
+        <s:v>540</s:v>
+      </s:c>
+      <s:c r="G84" s="1" t="n">
+        <s:v>2474.33</s:v>
+      </s:c>
+      <s:c r="H84" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I84" s="1" t="n">
+        <s:v>148.9</s:v>
+      </s:c>
+      <s:c r="J84" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K84" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L84" s="1" t="n">
+        <s:v>364.19</s:v>
+      </s:c>
+      <s:c r="M84" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N84" s="1" t="n">
+        <s:v>20292.96</s:v>
+      </s:c>
+      <s:c r="O84" s="1" t="n">
+        <s:v>1184.53</s:v>
+      </s:c>
+      <s:c r="P84" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="85" s="1" customFormat="1" spans="1:16">
       <s:c r="A85" s="6" t="n">
@@ -5510,17 +8104,39 @@
       </s:c>
       <s:c r="D85" s="1"/>
       <s:c r="E85" s="1"/>
-      <s:c r="F85" s="1"/>
-      <s:c r="G85" s="1"/>
-      <s:c r="H85" s="1"/>
-      <s:c r="I85" s="1"/>
-      <s:c r="J85" s="1"/>
-      <s:c r="K85" s="1"/>
-      <s:c r="L85" s="1"/>
-      <s:c r="M85" s="1"/>
-      <s:c r="N85" s="1"/>
-      <s:c r="O85" s="1"/>
-      <s:c r="P85" s="1"/>
+      <s:c r="F85" s="1" t="n">
+        <s:v>455</s:v>
+      </s:c>
+      <s:c r="G85" s="1" t="n">
+        <s:v>2394.7</s:v>
+      </s:c>
+      <s:c r="H85" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I85" s="1" t="n">
+        <s:v>140.65</s:v>
+      </s:c>
+      <s:c r="J85" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K85" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L85" s="1" t="n">
+        <s:v>363.09</s:v>
+      </s:c>
+      <s:c r="M85" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N85" s="1" t="n">
+        <s:v>20442.4</s:v>
+      </s:c>
+      <s:c r="O85" s="1" t="n">
+        <s:v>1167.36</s:v>
+      </s:c>
+      <s:c r="P85" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="86" s="1" customFormat="1" spans="1:16">
       <s:c r="A86" s="6" t="n">
@@ -5534,17 +8150,39 @@
       </s:c>
       <s:c r="D86" s="1"/>
       <s:c r="E86" s="1"/>
-      <s:c r="F86" s="1"/>
-      <s:c r="G86" s="1"/>
-      <s:c r="H86" s="1"/>
-      <s:c r="I86" s="1"/>
-      <s:c r="J86" s="1"/>
-      <s:c r="K86" s="1"/>
-      <s:c r="L86" s="1"/>
-      <s:c r="M86" s="1"/>
-      <s:c r="N86" s="1"/>
-      <s:c r="O86" s="1"/>
-      <s:c r="P86" s="1"/>
+      <s:c r="F86" s="1" t="n">
+        <s:v>370</s:v>
+      </s:c>
+      <s:c r="G86" s="1" t="n">
+        <s:v>2284.87</s:v>
+      </s:c>
+      <s:c r="H86" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I86" s="1" t="n">
+        <s:v>83.7</s:v>
+      </s:c>
+      <s:c r="J86" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K86" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L86" s="1" t="n">
+        <s:v>363.23</s:v>
+      </s:c>
+      <s:c r="M86" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N86" s="1" t="n">
+        <s:v>20195.44</s:v>
+      </s:c>
+      <s:c r="O86" s="1" t="n">
+        <s:v>1108.96</s:v>
+      </s:c>
+      <s:c r="P86" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="87" s="1" customFormat="1" spans="1:16">
       <s:c r="A87" s="6" t="n">
@@ -5558,17 +8196,39 @@
       </s:c>
       <s:c r="D87" s="1"/>
       <s:c r="E87" s="1"/>
-      <s:c r="F87" s="1"/>
-      <s:c r="G87" s="1"/>
-      <s:c r="H87" s="1"/>
-      <s:c r="I87" s="1"/>
-      <s:c r="J87" s="1"/>
-      <s:c r="K87" s="1"/>
-      <s:c r="L87" s="1"/>
-      <s:c r="M87" s="1"/>
-      <s:c r="N87" s="1"/>
-      <s:c r="O87" s="1"/>
-      <s:c r="P87" s="1"/>
+      <s:c r="F87" s="1" t="n">
+        <s:v>370</s:v>
+      </s:c>
+      <s:c r="G87" s="1" t="n">
+        <s:v>2297.19</s:v>
+      </s:c>
+      <s:c r="H87" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I87" s="1" t="n">
+        <s:v>83.7</s:v>
+      </s:c>
+      <s:c r="J87" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K87" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L87" s="1" t="n">
+        <s:v>363.4</s:v>
+      </s:c>
+      <s:c r="M87" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N87" s="1" t="n">
+        <s:v>20407.93</s:v>
+      </s:c>
+      <s:c r="O87" s="1" t="n">
+        <s:v>1117.19</s:v>
+      </s:c>
+      <s:c r="P87" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="88" s="1" customFormat="1" spans="1:16">
       <s:c r="A88" s="6" t="n">
@@ -5582,17 +8242,39 @@
       </s:c>
       <s:c r="D88" s="1"/>
       <s:c r="E88" s="1"/>
-      <s:c r="F88" s="1"/>
-      <s:c r="G88" s="1"/>
-      <s:c r="H88" s="1"/>
-      <s:c r="I88" s="1"/>
-      <s:c r="J88" s="1"/>
-      <s:c r="K88" s="1"/>
-      <s:c r="L88" s="1"/>
-      <s:c r="M88" s="1"/>
-      <s:c r="N88" s="1"/>
-      <s:c r="O88" s="1"/>
-      <s:c r="P88" s="1"/>
+      <s:c r="F88" s="1" t="n">
+        <s:v>410</s:v>
+      </s:c>
+      <s:c r="G88" s="1" t="n">
+        <s:v>2336.99</s:v>
+      </s:c>
+      <s:c r="H88" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I88" s="1" t="n">
+        <s:v>83.7</s:v>
+      </s:c>
+      <s:c r="J88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L88" s="1" t="n">
+        <s:v>363.4</s:v>
+      </s:c>
+      <s:c r="M88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N88" s="1" t="n">
+        <s:v>20466.03</s:v>
+      </s:c>
+      <s:c r="O88" s="1" t="n">
+        <s:v>1124.09</s:v>
+      </s:c>
+      <s:c r="P88" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="89" s="1" customFormat="1" spans="1:16">
       <s:c r="A89" s="6" t="n">
@@ -5606,17 +8288,39 @@
       </s:c>
       <s:c r="D89" s="1"/>
       <s:c r="E89" s="1"/>
-      <s:c r="F89" s="1"/>
-      <s:c r="G89" s="1"/>
-      <s:c r="H89" s="1"/>
-      <s:c r="I89" s="1"/>
-      <s:c r="J89" s="1"/>
-      <s:c r="K89" s="1"/>
-      <s:c r="L89" s="1"/>
-      <s:c r="M89" s="1"/>
-      <s:c r="N89" s="1"/>
-      <s:c r="O89" s="1"/>
-      <s:c r="P89" s="1"/>
+      <s:c r="F89" s="1" t="n">
+        <s:v>480</s:v>
+      </s:c>
+      <s:c r="G89" s="1" t="n">
+        <s:v>2335.16</s:v>
+      </s:c>
+      <s:c r="H89" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I89" s="1" t="n">
+        <s:v>83.7</s:v>
+      </s:c>
+      <s:c r="J89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L89" s="1" t="n">
+        <s:v>362.6</s:v>
+      </s:c>
+      <s:c r="M89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N89" s="1" t="n">
+        <s:v>20359.9</s:v>
+      </s:c>
+      <s:c r="O89" s="1" t="n">
+        <s:v>1142.45</s:v>
+      </s:c>
+      <s:c r="P89" s="1" t="n">
+        <s:v>71</s:v>
+      </s:c>
     </s:row>
     <s:row r="90" s="1" customFormat="1" spans="1:16">
       <s:c r="A90" s="6" t="n">
@@ -5630,17 +8334,39 @@
       </s:c>
       <s:c r="D90" s="1"/>
       <s:c r="E90" s="1"/>
-      <s:c r="F90" s="1"/>
-      <s:c r="G90" s="1"/>
-      <s:c r="H90" s="1"/>
-      <s:c r="I90" s="1"/>
-      <s:c r="J90" s="1"/>
-      <s:c r="K90" s="1"/>
-      <s:c r="L90" s="1"/>
-      <s:c r="M90" s="1"/>
-      <s:c r="N90" s="1"/>
-      <s:c r="O90" s="1"/>
-      <s:c r="P90" s="1"/>
+      <s:c r="F90" s="1" t="n">
+        <s:v>480</s:v>
+      </s:c>
+      <s:c r="G90" s="1" t="n">
+        <s:v>2344.33</s:v>
+      </s:c>
+      <s:c r="H90" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I90" s="1" t="n">
+        <s:v>59.7</s:v>
+      </s:c>
+      <s:c r="J90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L90" s="1" t="n">
+        <s:v>364.35</s:v>
+      </s:c>
+      <s:c r="M90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N90" s="1" t="n">
+        <s:v>20292.85</s:v>
+      </s:c>
+      <s:c r="O90" s="1" t="n">
+        <s:v>1198.08</s:v>
+      </s:c>
+      <s:c r="P90" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="91" s="1" customFormat="1" spans="1:16">
       <s:c r="A91" s="6" t="n">
@@ -5654,17 +8380,39 @@
       </s:c>
       <s:c r="D91" s="1"/>
       <s:c r="E91" s="1"/>
-      <s:c r="F91" s="1"/>
-      <s:c r="G91" s="1"/>
-      <s:c r="H91" s="1"/>
-      <s:c r="I91" s="1"/>
-      <s:c r="J91" s="1"/>
-      <s:c r="K91" s="1"/>
-      <s:c r="L91" s="1"/>
-      <s:c r="M91" s="1"/>
-      <s:c r="N91" s="1"/>
-      <s:c r="O91" s="1"/>
-      <s:c r="P91" s="1"/>
+      <s:c r="F91" s="1" t="n">
+        <s:v>540</s:v>
+      </s:c>
+      <s:c r="G91" s="1" t="n">
+        <s:v>2364.95</s:v>
+      </s:c>
+      <s:c r="H91" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I91" s="1" t="n">
+        <s:v>41.7</s:v>
+      </s:c>
+      <s:c r="J91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L91" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N91" s="1" t="n">
+        <s:v>20284.46</s:v>
+      </s:c>
+      <s:c r="O91" s="1" t="n">
+        <s:v>1182.09</s:v>
+      </s:c>
+      <s:c r="P91" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="92" s="1" customFormat="1" spans="1:16">
       <s:c r="A92" s="6" t="n">
@@ -5678,17 +8426,39 @@
       </s:c>
       <s:c r="D92" s="1"/>
       <s:c r="E92" s="1"/>
-      <s:c r="F92" s="1"/>
-      <s:c r="G92" s="1"/>
-      <s:c r="H92" s="1"/>
-      <s:c r="I92" s="1"/>
-      <s:c r="J92" s="1"/>
-      <s:c r="K92" s="1"/>
-      <s:c r="L92" s="1"/>
-      <s:c r="M92" s="1"/>
-      <s:c r="N92" s="1"/>
-      <s:c r="O92" s="1"/>
-      <s:c r="P92" s="1"/>
+      <s:c r="F92" s="1" t="n">
+        <s:v>540</s:v>
+      </s:c>
+      <s:c r="G92" s="1" t="n">
+        <s:v>2330.33</s:v>
+      </s:c>
+      <s:c r="H92" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I92" s="1" t="n">
+        <s:v>23.7</s:v>
+      </s:c>
+      <s:c r="J92" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K92" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L92" s="1" t="n">
+        <s:v>400</s:v>
+      </s:c>
+      <s:c r="M92" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N92" s="1" t="n">
+        <s:v>20371.25</s:v>
+      </s:c>
+      <s:c r="O92" s="1" t="n">
+        <s:v>1013.02</s:v>
+      </s:c>
+      <s:c r="P92" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="93" s="1" customFormat="1" spans="1:16">
       <s:c r="A93" s="6" t="n">
@@ -5702,17 +8472,39 @@
       </s:c>
       <s:c r="D93" s="1"/>
       <s:c r="E93" s="1"/>
-      <s:c r="F93" s="1"/>
-      <s:c r="G93" s="1"/>
-      <s:c r="H93" s="1"/>
-      <s:c r="I93" s="1"/>
-      <s:c r="J93" s="1"/>
-      <s:c r="K93" s="1"/>
-      <s:c r="L93" s="1"/>
-      <s:c r="M93" s="1"/>
-      <s:c r="N93" s="1"/>
-      <s:c r="O93" s="1"/>
-      <s:c r="P93" s="1"/>
+      <s:c r="F93" s="1" t="n">
+        <s:v>540</s:v>
+      </s:c>
+      <s:c r="G93" s="1" t="n">
+        <s:v>2301.58</s:v>
+      </s:c>
+      <s:c r="H93" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I93" s="1" t="n">
+        <s:v>23.7</s:v>
+      </s:c>
+      <s:c r="J93" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K93" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L93" s="1" t="n">
+        <s:v>369.65</s:v>
+      </s:c>
+      <s:c r="M93" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N93" s="1" t="n">
+        <s:v>20367.13</s:v>
+      </s:c>
+      <s:c r="O93" s="1" t="n">
+        <s:v>943.75</s:v>
+      </s:c>
+      <s:c r="P93" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="94" s="1" customFormat="1" spans="1:16">
       <s:c r="A94" s="6" t="n">
@@ -5726,17 +8518,39 @@
       </s:c>
       <s:c r="D94" s="1"/>
       <s:c r="E94" s="1"/>
-      <s:c r="F94" s="1"/>
-      <s:c r="G94" s="1"/>
-      <s:c r="H94" s="1"/>
-      <s:c r="I94" s="1"/>
-      <s:c r="J94" s="1"/>
-      <s:c r="K94" s="1"/>
-      <s:c r="L94" s="1"/>
-      <s:c r="M94" s="1"/>
-      <s:c r="N94" s="1"/>
-      <s:c r="O94" s="1"/>
-      <s:c r="P94" s="1"/>
+      <s:c r="F94" s="1" t="n">
+        <s:v>710</s:v>
+      </s:c>
+      <s:c r="G94" s="1" t="n">
+        <s:v>2286.78</s:v>
+      </s:c>
+      <s:c r="H94" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I94" s="1" t="n">
+        <s:v>23.7</s:v>
+      </s:c>
+      <s:c r="J94" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K94" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L94" s="1" t="n">
+        <s:v>357.44</s:v>
+      </s:c>
+      <s:c r="M94" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N94" s="1" t="n">
+        <s:v>20124.62</s:v>
+      </s:c>
+      <s:c r="O94" s="1" t="n">
+        <s:v>1113.67</s:v>
+      </s:c>
+      <s:c r="P94" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="95" s="1" customFormat="1" spans="1:16">
       <s:c r="A95" s="6" t="n">
@@ -5750,17 +8564,39 @@
       </s:c>
       <s:c r="D95" s="1"/>
       <s:c r="E95" s="1"/>
-      <s:c r="F95" s="1"/>
-      <s:c r="G95" s="1"/>
-      <s:c r="H95" s="1"/>
-      <s:c r="I95" s="1"/>
-      <s:c r="J95" s="1"/>
-      <s:c r="K95" s="1"/>
-      <s:c r="L95" s="1"/>
-      <s:c r="M95" s="1"/>
-      <s:c r="N95" s="1"/>
-      <s:c r="O95" s="1"/>
-      <s:c r="P95" s="1"/>
+      <s:c r="F95" s="1" t="n">
+        <s:v>710</s:v>
+      </s:c>
+      <s:c r="G95" s="1" t="n">
+        <s:v>2234.91</s:v>
+      </s:c>
+      <s:c r="H95" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I95" s="1" t="n">
+        <s:v>15.7</s:v>
+      </s:c>
+      <s:c r="J95" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K95" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L95" s="1" t="n">
+        <s:v>356.34</s:v>
+      </s:c>
+      <s:c r="M95" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N95" s="1" t="n">
+        <s:v>19490.32</s:v>
+      </s:c>
+      <s:c r="O95" s="1" t="n">
+        <s:v>1215.55</s:v>
+      </s:c>
+      <s:c r="P95" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="96" s="1" customFormat="1" spans="1:16">
       <s:c r="A96" s="6" t="n">
@@ -5774,17 +8610,39 @@
       </s:c>
       <s:c r="D96" s="1"/>
       <s:c r="E96" s="1"/>
-      <s:c r="F96" s="1"/>
-      <s:c r="G96" s="1"/>
-      <s:c r="H96" s="1"/>
-      <s:c r="I96" s="1"/>
-      <s:c r="J96" s="1"/>
-      <s:c r="K96" s="1"/>
-      <s:c r="L96" s="1"/>
-      <s:c r="M96" s="1"/>
-      <s:c r="N96" s="1"/>
-      <s:c r="O96" s="1"/>
-      <s:c r="P96" s="1"/>
+      <s:c r="F96" s="1" t="n">
+        <s:v>520</s:v>
+      </s:c>
+      <s:c r="G96" s="1" t="n">
+        <s:v>2243.11</s:v>
+      </s:c>
+      <s:c r="H96" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I96" s="1" t="n">
+        <s:v>9.7</s:v>
+      </s:c>
+      <s:c r="J96" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K96" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L96" s="1" t="n">
+        <s:v>358.22</s:v>
+      </s:c>
+      <s:c r="M96" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N96" s="1" t="n">
+        <s:v>19630.48</s:v>
+      </s:c>
+      <s:c r="O96" s="1" t="n">
+        <s:v>1172.3</s:v>
+      </s:c>
+      <s:c r="P96" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
     <s:row r="97" s="1" customFormat="1" spans="1:16">
       <s:c r="A97" s="6" t="n">
@@ -5800,17 +8658,39 @@
       </s:c>
       <s:c r="D97" s="1"/>
       <s:c r="E97" s="1"/>
-      <s:c r="F97" s="1"/>
-      <s:c r="G97" s="1"/>
-      <s:c r="H97" s="1"/>
-      <s:c r="I97" s="1"/>
-      <s:c r="J97" s="1"/>
-      <s:c r="K97" s="1"/>
-      <s:c r="L97" s="1"/>
-      <s:c r="M97" s="1"/>
-      <s:c r="N97" s="1"/>
-      <s:c r="O97" s="1"/>
-      <s:c r="P97" s="1"/>
+      <s:c r="F97" s="1" t="n">
+        <s:v>380</s:v>
+      </s:c>
+      <s:c r="G97" s="1" t="n">
+        <s:v>2287.52</s:v>
+      </s:c>
+      <s:c r="H97" s="1" t="n">
+        <s:v>0.69</s:v>
+      </s:c>
+      <s:c r="I97" s="1" t="n">
+        <s:v>3.7</s:v>
+      </s:c>
+      <s:c r="J97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L97" s="1" t="n">
+        <s:v>356.81</s:v>
+      </s:c>
+      <s:c r="M97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N97" s="1" t="n">
+        <s:v>19730.33</s:v>
+      </s:c>
+      <s:c r="O97" s="1" t="n">
+        <s:v>1190.95</s:v>
+      </s:c>
+      <s:c r="P97" s="1" t="n">
+        <s:v>70</s:v>
+      </s:c>
     </s:row>
   </s:sheetData>
   <conditionalFormatting sqref="A1:B1">

--- a/review-results/河北实时运行及市场出清数据-20260906.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260906.xlsx
@@ -4285,7 +4285,9 @@
         <s:v>1</s:v>
       </s:c>
       <s:c r="D2" s="1"/>
-      <s:c r="E2" s="1"/>
+      <s:c r="E2" s="1" t="n">
+        <s:v>414.01</s:v>
+      </s:c>
       <s:c r="F2" s="1" t="n">
         <s:v>630</s:v>
       </s:c>
@@ -4331,7 +4333,9 @@
         <s:v>1</s:v>
       </s:c>
       <s:c r="D3" s="1"/>
-      <s:c r="E3" s="1"/>
+      <s:c r="E3" s="1" t="n">
+        <s:v>419.85</s:v>
+      </s:c>
       <s:c r="F3" s="1" t="n">
         <s:v>970</s:v>
       </s:c>
@@ -4377,7 +4381,9 @@
         <s:v>1</s:v>
       </s:c>
       <s:c r="D4" s="1"/>
-      <s:c r="E4" s="1"/>
+      <s:c r="E4" s="1" t="n">
+        <s:v>413.45</s:v>
+      </s:c>
       <s:c r="F4" s="1" t="n">
         <s:v>1030</s:v>
       </s:c>
@@ -4423,7 +4429,9 @@
         <s:v>1</s:v>
       </s:c>
       <s:c r="D5" s="1"/>
-      <s:c r="E5" s="1"/>
+      <s:c r="E5" s="1" t="n">
+        <s:v>414.1</s:v>
+      </s:c>
       <s:c r="F5" s="1" t="n">
         <s:v>970</s:v>
       </s:c>
@@ -4469,7 +4477,9 @@
         <s:v>2</s:v>
       </s:c>
       <s:c r="D6" s="1"/>
-      <s:c r="E6" s="1"/>
+      <s:c r="E6" s="1" t="n">
+        <s:v>429.1</s:v>
+      </s:c>
       <s:c r="F6" s="1" t="n">
         <s:v>260</s:v>
       </s:c>
@@ -4515,7 +4525,9 @@
         <s:v>2</s:v>
       </s:c>
       <s:c r="D7" s="1"/>
-      <s:c r="E7" s="1"/>
+      <s:c r="E7" s="1" t="n">
+        <s:v>419.55</s:v>
+      </s:c>
       <s:c r="F7" s="1" t="n">
         <s:v>200</s:v>
       </s:c>
@@ -4561,7 +4573,9 @@
         <s:v>2</s:v>
       </s:c>
       <s:c r="D8" s="1"/>
-      <s:c r="E8" s="1"/>
+      <s:c r="E8" s="1" t="n">
+        <s:v>419.64</s:v>
+      </s:c>
       <s:c r="F8" s="1" t="n">
         <s:v>250</s:v>
       </s:c>
@@ -4607,7 +4621,9 @@
         <s:v>2</s:v>
       </s:c>
       <s:c r="D9" s="1"/>
-      <s:c r="E9" s="1"/>
+      <s:c r="E9" s="1" t="n">
+        <s:v>424.72</s:v>
+      </s:c>
       <s:c r="F9" s="1" t="n">
         <s:v>560</s:v>
       </s:c>
@@ -4653,7 +4669,9 @@
         <s:v>3</s:v>
       </s:c>
       <s:c r="D10" s="1"/>
-      <s:c r="E10" s="1"/>
+      <s:c r="E10" s="1" t="n">
+        <s:v>405.39</s:v>
+      </s:c>
       <s:c r="F10" s="1" t="n">
         <s:v>1530</s:v>
       </s:c>
@@ -4699,7 +4717,9 @@
         <s:v>3</s:v>
       </s:c>
       <s:c r="D11" s="1"/>
-      <s:c r="E11" s="1"/>
+      <s:c r="E11" s="1" t="n">
+        <s:v>421.76</s:v>
+      </s:c>
       <s:c r="F11" s="1" t="n">
         <s:v>1850</s:v>
       </s:c>
@@ -4745,7 +4765,9 @@
         <s:v>3</s:v>
       </s:c>
       <s:c r="D12" s="1"/>
-      <s:c r="E12" s="1"/>
+      <s:c r="E12" s="1" t="n">
+        <s:v>413.41</s:v>
+      </s:c>
       <s:c r="F12" s="1" t="n">
         <s:v>1740</s:v>
       </s:c>
@@ -4791,7 +4813,9 @@
         <s:v>3</s:v>
       </s:c>
       <s:c r="D13" s="1"/>
-      <s:c r="E13" s="1"/>
+      <s:c r="E13" s="1" t="n">
+        <s:v>412.82</s:v>
+      </s:c>
       <s:c r="F13" s="1" t="n">
         <s:v>1400</s:v>
       </s:c>
@@ -4837,7 +4861,9 @@
         <s:v>4</s:v>
       </s:c>
       <s:c r="D14" s="1"/>
-      <s:c r="E14" s="1"/>
+      <s:c r="E14" s="1" t="n">
+        <s:v>414.1</s:v>
+      </s:c>
       <s:c r="F14" s="1" t="n">
         <s:v>480</s:v>
       </s:c>
@@ -4883,7 +4909,9 @@
         <s:v>4</s:v>
       </s:c>
       <s:c r="D15" s="1"/>
-      <s:c r="E15" s="1"/>
+      <s:c r="E15" s="1" t="n">
+        <s:v>419.64</s:v>
+      </s:c>
       <s:c r="F15" s="1" t="n">
         <s:v>240</s:v>
       </s:c>
@@ -4929,7 +4957,9 @@
         <s:v>4</s:v>
       </s:c>
       <s:c r="D16" s="1"/>
-      <s:c r="E16" s="1"/>
+      <s:c r="E16" s="1" t="n">
+        <s:v>419.55</s:v>
+      </s:c>
       <s:c r="F16" s="1" t="n">
         <s:v>60</s:v>
       </s:c>
@@ -4975,7 +5005,9 @@
         <s:v>4</s:v>
       </s:c>
       <s:c r="D17" s="1"/>
-      <s:c r="E17" s="1"/>
+      <s:c r="E17" s="1" t="n">
+        <s:v>419.61</s:v>
+      </s:c>
       <s:c r="F17" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5021,7 +5053,9 @@
         <s:v>5</s:v>
       </s:c>
       <s:c r="D18" s="1"/>
-      <s:c r="E18" s="1"/>
+      <s:c r="E18" s="1" t="n">
+        <s:v>426.29</s:v>
+      </s:c>
       <s:c r="F18" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5067,7 +5101,9 @@
         <s:v>5</s:v>
       </s:c>
       <s:c r="D19" s="1"/>
-      <s:c r="E19" s="1"/>
+      <s:c r="E19" s="1" t="n">
+        <s:v>419.76</s:v>
+      </s:c>
       <s:c r="F19" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5113,7 +5149,9 @@
         <s:v>5</s:v>
       </s:c>
       <s:c r="D20" s="1"/>
-      <s:c r="E20" s="1"/>
+      <s:c r="E20" s="1" t="n">
+        <s:v>427.67</s:v>
+      </s:c>
       <s:c r="F20" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5159,7 +5197,9 @@
         <s:v>5</s:v>
       </s:c>
       <s:c r="D21" s="1"/>
-      <s:c r="E21" s="1"/>
+      <s:c r="E21" s="1" t="n">
+        <s:v>428.66</s:v>
+      </s:c>
       <s:c r="F21" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5205,7 +5245,9 @@
         <s:v>6</s:v>
       </s:c>
       <s:c r="D22" s="1"/>
-      <s:c r="E22" s="1"/>
+      <s:c r="E22" s="1" t="n">
+        <s:v>1192</s:v>
+      </s:c>
       <s:c r="F22" s="1" t="n">
         <s:v>260</s:v>
       </s:c>
@@ -5251,7 +5293,9 @@
         <s:v>6</s:v>
       </s:c>
       <s:c r="D23" s="1"/>
-      <s:c r="E23" s="1"/>
+      <s:c r="E23" s="1" t="n">
+        <s:v>1192</s:v>
+      </s:c>
       <s:c r="F23" s="1" t="n">
         <s:v>380</s:v>
       </s:c>
@@ -5297,7 +5341,9 @@
         <s:v>6</s:v>
       </s:c>
       <s:c r="D24" s="1"/>
-      <s:c r="E24" s="1"/>
+      <s:c r="E24" s="1" t="n">
+        <s:v>1192</s:v>
+      </s:c>
       <s:c r="F24" s="1" t="n">
         <s:v>440</s:v>
       </s:c>
@@ -5343,7 +5389,9 @@
         <s:v>6</s:v>
       </s:c>
       <s:c r="D25" s="1"/>
-      <s:c r="E25" s="1"/>
+      <s:c r="E25" s="1" t="n">
+        <s:v>429.69</s:v>
+      </s:c>
       <s:c r="F25" s="1" t="n">
         <s:v>640</s:v>
       </s:c>
@@ -5389,7 +5437,9 @@
         <s:v>7</s:v>
       </s:c>
       <s:c r="D26" s="1"/>
-      <s:c r="E26" s="1"/>
+      <s:c r="E26" s="1" t="n">
+        <s:v>433.14</s:v>
+      </s:c>
       <s:c r="F26" s="1" t="n">
         <s:v>820</s:v>
       </s:c>
@@ -5435,7 +5485,9 @@
         <s:v>7</s:v>
       </s:c>
       <s:c r="D27" s="1"/>
-      <s:c r="E27" s="1"/>
+      <s:c r="E27" s="1" t="n">
+        <s:v>421.83</s:v>
+      </s:c>
       <s:c r="F27" s="1" t="n">
         <s:v>790</s:v>
       </s:c>
@@ -5481,7 +5533,9 @@
         <s:v>7</s:v>
       </s:c>
       <s:c r="D28" s="1"/>
-      <s:c r="E28" s="1"/>
+      <s:c r="E28" s="1" t="n">
+        <s:v>420.32</s:v>
+      </s:c>
       <s:c r="F28" s="1" t="n">
         <s:v>825</s:v>
       </s:c>
@@ -5527,7 +5581,9 @@
         <s:v>7</s:v>
       </s:c>
       <s:c r="D29" s="1"/>
-      <s:c r="E29" s="1"/>
+      <s:c r="E29" s="1" t="n">
+        <s:v>405.27</s:v>
+      </s:c>
       <s:c r="F29" s="1" t="n">
         <s:v>645</s:v>
       </s:c>
@@ -5573,7 +5629,9 @@
         <s:v>8</s:v>
       </s:c>
       <s:c r="D30" s="1"/>
-      <s:c r="E30" s="1"/>
+      <s:c r="E30" s="1" t="n">
+        <s:v>414.01</s:v>
+      </s:c>
       <s:c r="F30" s="1" t="n">
         <s:v>95</s:v>
       </s:c>
@@ -5619,7 +5677,9 @@
         <s:v>8</s:v>
       </s:c>
       <s:c r="D31" s="1"/>
-      <s:c r="E31" s="1"/>
+      <s:c r="E31" s="1" t="n">
+        <s:v>403.14</s:v>
+      </s:c>
       <s:c r="F31" s="1" t="n">
         <s:v>95</s:v>
       </s:c>
@@ -5665,7 +5725,9 @@
         <s:v>8</s:v>
       </s:c>
       <s:c r="D32" s="1"/>
-      <s:c r="E32" s="1"/>
+      <s:c r="E32" s="1" t="n">
+        <s:v>391.33</s:v>
+      </s:c>
       <s:c r="F32" s="1" t="n">
         <s:v>60</s:v>
       </s:c>
@@ -5711,7 +5773,9 @@
         <s:v>8</s:v>
       </s:c>
       <s:c r="D33" s="1"/>
-      <s:c r="E33" s="1"/>
+      <s:c r="E33" s="1" t="n">
+        <s:v>378.8</s:v>
+      </s:c>
       <s:c r="F33" s="1" t="n">
         <s:v>30</s:v>
       </s:c>
@@ -5757,7 +5821,9 @@
         <s:v>9</s:v>
       </s:c>
       <s:c r="D34" s="1"/>
-      <s:c r="E34" s="1"/>
+      <s:c r="E34" s="1" t="n">
+        <s:v>370.67</s:v>
+      </s:c>
       <s:c r="F34" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5803,7 +5869,9 @@
         <s:v>9</s:v>
       </s:c>
       <s:c r="D35" s="1"/>
-      <s:c r="E35" s="1"/>
+      <s:c r="E35" s="1" t="n">
+        <s:v>399.23</s:v>
+      </s:c>
       <s:c r="F35" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5849,7 +5917,9 @@
         <s:v>9</s:v>
       </s:c>
       <s:c r="D36" s="1"/>
-      <s:c r="E36" s="1"/>
+      <s:c r="E36" s="1" t="n">
+        <s:v>360.64</s:v>
+      </s:c>
       <s:c r="F36" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5895,7 +5965,9 @@
         <s:v>9</s:v>
       </s:c>
       <s:c r="D37" s="1"/>
-      <s:c r="E37" s="1"/>
+      <s:c r="E37" s="1" t="n">
+        <s:v>362.04</s:v>
+      </s:c>
       <s:c r="F37" s="1" t="n">
         <s:v>-100</s:v>
       </s:c>
@@ -5941,7 +6013,9 @@
         <s:v>10</s:v>
       </s:c>
       <s:c r="D38" s="1"/>
-      <s:c r="E38" s="1"/>
+      <s:c r="E38" s="1" t="n">
+        <s:v>365.25</s:v>
+      </s:c>
       <s:c r="F38" s="1" t="n">
         <s:v>-890</s:v>
       </s:c>
@@ -5987,7 +6061,9 @@
         <s:v>10</s:v>
       </s:c>
       <s:c r="D39" s="1"/>
-      <s:c r="E39" s="1"/>
+      <s:c r="E39" s="1" t="n">
+        <s:v>366.2</s:v>
+      </s:c>
       <s:c r="F39" s="1" t="n">
         <s:v>-1690</s:v>
       </s:c>
@@ -6033,7 +6109,9 @@
         <s:v>10</s:v>
       </s:c>
       <s:c r="D40" s="1"/>
-      <s:c r="E40" s="1"/>
+      <s:c r="E40" s="1" t="n">
+        <s:v>366.2</s:v>
+      </s:c>
       <s:c r="F40" s="1" t="n">
         <s:v>-2203</s:v>
       </s:c>
@@ -6079,7 +6157,9 @@
         <s:v>10</s:v>
       </s:c>
       <s:c r="D41" s="1"/>
-      <s:c r="E41" s="1"/>
+      <s:c r="E41" s="1" t="n">
+        <s:v>365.25</s:v>
+      </s:c>
       <s:c r="F41" s="1" t="n">
         <s:v>-2463</s:v>
       </s:c>
@@ -6125,7 +6205,9 @@
         <s:v>11</s:v>
       </s:c>
       <s:c r="D42" s="1"/>
-      <s:c r="E42" s="1"/>
+      <s:c r="E42" s="1" t="n">
+        <s:v>366.79</s:v>
+      </s:c>
       <s:c r="F42" s="1" t="n">
         <s:v>-3153</s:v>
       </s:c>
@@ -6171,7 +6253,9 @@
         <s:v>11</s:v>
       </s:c>
       <s:c r="D43" s="1"/>
-      <s:c r="E43" s="1"/>
+      <s:c r="E43" s="1" t="n">
+        <s:v>363.23</s:v>
+      </s:c>
       <s:c r="F43" s="1" t="n">
         <s:v>-3343</s:v>
       </s:c>
@@ -6217,7 +6301,9 @@
         <s:v>11</s:v>
       </s:c>
       <s:c r="D44" s="1"/>
-      <s:c r="E44" s="1"/>
+      <s:c r="E44" s="1" t="n">
+        <s:v>362.77</s:v>
+      </s:c>
       <s:c r="F44" s="1" t="n">
         <s:v>-3503</s:v>
       </s:c>
@@ -6263,7 +6349,9 @@
         <s:v>11</s:v>
       </s:c>
       <s:c r="D45" s="1"/>
-      <s:c r="E45" s="1"/>
+      <s:c r="E45" s="1" t="n">
+        <s:v>365.25</s:v>
+      </s:c>
       <s:c r="F45" s="1" t="n">
         <s:v>-3553</s:v>
       </s:c>
@@ -6309,7 +6397,9 @@
         <s:v>12</s:v>
       </s:c>
       <s:c r="D46" s="1"/>
-      <s:c r="E46" s="1"/>
+      <s:c r="E46" s="1" t="n">
+        <s:v>367.27</s:v>
+      </s:c>
       <s:c r="F46" s="1" t="n">
         <s:v>-3493</s:v>
       </s:c>
@@ -6355,7 +6445,9 @@
         <s:v>12</s:v>
       </s:c>
       <s:c r="D47" s="1"/>
-      <s:c r="E47" s="1"/>
+      <s:c r="E47" s="1" t="n">
+        <s:v>491.2</s:v>
+      </s:c>
       <s:c r="F47" s="1" t="n">
         <s:v>-3273</s:v>
       </s:c>
@@ -6401,7 +6493,9 @@
         <s:v>12</s:v>
       </s:c>
       <s:c r="D48" s="1"/>
-      <s:c r="E48" s="1"/>
+      <s:c r="E48" s="1" t="n">
+        <s:v>397.33</s:v>
+      </s:c>
       <s:c r="F48" s="1" t="n">
         <s:v>-3223</s:v>
       </s:c>
@@ -6447,7 +6541,9 @@
         <s:v>12</s:v>
       </s:c>
       <s:c r="D49" s="1"/>
-      <s:c r="E49" s="1"/>
+      <s:c r="E49" s="1" t="n">
+        <s:v>371.47</s:v>
+      </s:c>
       <s:c r="F49" s="1" t="n">
         <s:v>-3273</s:v>
       </s:c>
@@ -6493,7 +6589,9 @@
         <s:v>13</s:v>
       </s:c>
       <s:c r="D50" s="1"/>
-      <s:c r="E50" s="1"/>
+      <s:c r="E50" s="1" t="n">
+        <s:v>382.55</s:v>
+      </s:c>
       <s:c r="F50" s="1" t="n">
         <s:v>-3743</s:v>
       </s:c>
@@ -6539,7 +6637,9 @@
         <s:v>13</s:v>
       </s:c>
       <s:c r="D51" s="1"/>
-      <s:c r="E51" s="1"/>
+      <s:c r="E51" s="1" t="n">
+        <s:v>375.89</s:v>
+      </s:c>
       <s:c r="F51" s="1" t="n">
         <s:v>-3753</s:v>
       </s:c>
@@ -6585,7 +6685,9 @@
         <s:v>13</s:v>
       </s:c>
       <s:c r="D52" s="1"/>
-      <s:c r="E52" s="1"/>
+      <s:c r="E52" s="1" t="n">
+        <s:v>383.75</s:v>
+      </s:c>
       <s:c r="F52" s="1" t="n">
         <s:v>-3723</s:v>
       </s:c>
@@ -6631,7 +6733,9 @@
         <s:v>13</s:v>
       </s:c>
       <s:c r="D53" s="1"/>
-      <s:c r="E53" s="1"/>
+      <s:c r="E53" s="1" t="n">
+        <s:v>397.33</s:v>
+      </s:c>
       <s:c r="F53" s="1" t="n">
         <s:v>-3253</s:v>
       </s:c>
@@ -6677,7 +6781,9 @@
         <s:v>14</s:v>
       </s:c>
       <s:c r="D54" s="1"/>
-      <s:c r="E54" s="1"/>
+      <s:c r="E54" s="1" t="n">
+        <s:v>378.35</s:v>
+      </s:c>
       <s:c r="F54" s="1" t="n">
         <s:v>-2793</s:v>
       </s:c>
@@ -6723,7 +6829,9 @@
         <s:v>14</s:v>
       </s:c>
       <s:c r="D55" s="1"/>
-      <s:c r="E55" s="1"/>
+      <s:c r="E55" s="1" t="n">
+        <s:v>375.7</s:v>
+      </s:c>
       <s:c r="F55" s="1" t="n">
         <s:v>-2453</s:v>
       </s:c>
@@ -6769,7 +6877,9 @@
         <s:v>14</s:v>
       </s:c>
       <s:c r="D56" s="1"/>
-      <s:c r="E56" s="1"/>
+      <s:c r="E56" s="1" t="n">
+        <s:v>368.63</s:v>
+      </s:c>
       <s:c r="F56" s="1" t="n">
         <s:v>-1900</s:v>
       </s:c>
@@ -6815,7 +6925,9 @@
         <s:v>14</s:v>
       </s:c>
       <s:c r="D57" s="1"/>
-      <s:c r="E57" s="1"/>
+      <s:c r="E57" s="1" t="n">
+        <s:v>363.8</s:v>
+      </s:c>
       <s:c r="F57" s="1" t="n">
         <s:v>-1490</s:v>
       </s:c>
@@ -6861,7 +6973,9 @@
         <s:v>15</s:v>
       </s:c>
       <s:c r="D58" s="1"/>
-      <s:c r="E58" s="1"/>
+      <s:c r="E58" s="1" t="n">
+        <s:v>361.89</s:v>
+      </s:c>
       <s:c r="F58" s="1" t="n">
         <s:v>-730</s:v>
       </s:c>
@@ -6907,7 +7021,9 @@
         <s:v>15</s:v>
       </s:c>
       <s:c r="D59" s="1"/>
-      <s:c r="E59" s="1"/>
+      <s:c r="E59" s="1" t="n">
+        <s:v>213.25</s:v>
+      </s:c>
       <s:c r="F59" s="1" t="n">
         <s:v>-620</s:v>
       </s:c>
@@ -6953,7 +7069,9 @@
         <s:v>15</s:v>
       </s:c>
       <s:c r="D60" s="1"/>
-      <s:c r="E60" s="1"/>
+      <s:c r="E60" s="1" t="n">
+        <s:v>370.39</s:v>
+      </s:c>
       <s:c r="F60" s="1" t="n">
         <s:v>-410</s:v>
       </s:c>
@@ -6999,7 +7117,9 @@
         <s:v>15</s:v>
       </s:c>
       <s:c r="D61" s="1"/>
-      <s:c r="E61" s="1"/>
+      <s:c r="E61" s="1" t="n">
+        <s:v>376.82</s:v>
+      </s:c>
       <s:c r="F61" s="1" t="n">
         <s:v>-160</s:v>
       </s:c>
@@ -7045,7 +7165,9 @@
         <s:v>16</s:v>
       </s:c>
       <s:c r="D62" s="1"/>
-      <s:c r="E62" s="1"/>
+      <s:c r="E62" s="1" t="n">
+        <s:v>378.66</s:v>
+      </s:c>
       <s:c r="F62" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7091,7 +7213,9 @@
         <s:v>16</s:v>
       </s:c>
       <s:c r="D63" s="1"/>
-      <s:c r="E63" s="1"/>
+      <s:c r="E63" s="1" t="n">
+        <s:v>391.02</s:v>
+      </s:c>
       <s:c r="F63" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7137,7 +7261,9 @@
         <s:v>16</s:v>
       </s:c>
       <s:c r="D64" s="1"/>
-      <s:c r="E64" s="1"/>
+      <s:c r="E64" s="1" t="n">
+        <s:v>399.95</s:v>
+      </s:c>
       <s:c r="F64" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7183,7 +7309,9 @@
         <s:v>16</s:v>
       </s:c>
       <s:c r="D65" s="1"/>
-      <s:c r="E65" s="1"/>
+      <s:c r="E65" s="1" t="n">
+        <s:v>405.27</s:v>
+      </s:c>
       <s:c r="F65" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7229,7 +7357,9 @@
         <s:v>17</s:v>
       </s:c>
       <s:c r="D66" s="1"/>
-      <s:c r="E66" s="1"/>
+      <s:c r="E66" s="1" t="n">
+        <s:v>412.32</s:v>
+      </s:c>
       <s:c r="F66" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7275,7 +7405,9 @@
         <s:v>17</s:v>
       </s:c>
       <s:c r="D67" s="1"/>
-      <s:c r="E67" s="1"/>
+      <s:c r="E67" s="1" t="n">
+        <s:v>413.97</s:v>
+      </s:c>
       <s:c r="F67" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7321,7 +7453,9 @@
         <s:v>17</s:v>
       </s:c>
       <s:c r="D68" s="1"/>
-      <s:c r="E68" s="1"/>
+      <s:c r="E68" s="1" t="n">
+        <s:v>412.89</s:v>
+      </s:c>
       <s:c r="F68" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7367,7 +7501,9 @@
         <s:v>17</s:v>
       </s:c>
       <s:c r="D69" s="1"/>
-      <s:c r="E69" s="1"/>
+      <s:c r="E69" s="1" t="n">
+        <s:v>421.86</s:v>
+      </s:c>
       <s:c r="F69" s="1" t="n">
         <s:v>100</s:v>
       </s:c>
@@ -7413,7 +7549,9 @@
         <s:v>18</s:v>
       </s:c>
       <s:c r="D70" s="1"/>
-      <s:c r="E70" s="1"/>
+      <s:c r="E70" s="1" t="n">
+        <s:v>419.39</s:v>
+      </s:c>
       <s:c r="F70" s="1" t="n">
         <s:v>820</s:v>
       </s:c>
@@ -7459,7 +7597,9 @@
         <s:v>18</s:v>
       </s:c>
       <s:c r="D71" s="1"/>
-      <s:c r="E71" s="1"/>
+      <s:c r="E71" s="1" t="n">
+        <s:v>421.22</s:v>
+      </s:c>
       <s:c r="F71" s="1" t="n">
         <s:v>1120</s:v>
       </s:c>
@@ -7505,7 +7645,9 @@
         <s:v>18</s:v>
       </s:c>
       <s:c r="D72" s="1"/>
-      <s:c r="E72" s="1"/>
+      <s:c r="E72" s="1" t="n">
+        <s:v>420.6</s:v>
+      </s:c>
       <s:c r="F72" s="1" t="n">
         <s:v>1260</s:v>
       </s:c>
@@ -7551,7 +7693,9 @@
         <s:v>18</s:v>
       </s:c>
       <s:c r="D73" s="1"/>
-      <s:c r="E73" s="1"/>
+      <s:c r="E73" s="1" t="n">
+        <s:v>420.6</s:v>
+      </s:c>
       <s:c r="F73" s="1" t="n">
         <s:v>1355</s:v>
       </s:c>
@@ -7597,7 +7741,9 @@
         <s:v>19</s:v>
       </s:c>
       <s:c r="D74" s="1"/>
-      <s:c r="E74" s="1"/>
+      <s:c r="E74" s="1" t="n">
+        <s:v>403.89</s:v>
+      </s:c>
       <s:c r="F74" s="1" t="n">
         <s:v>2030</s:v>
       </s:c>
@@ -7643,7 +7789,9 @@
         <s:v>19</s:v>
       </s:c>
       <s:c r="D75" s="1"/>
-      <s:c r="E75" s="1"/>
+      <s:c r="E75" s="1" t="n">
+        <s:v>412.89</s:v>
+      </s:c>
       <s:c r="F75" s="1" t="n">
         <s:v>2030</s:v>
       </s:c>
@@ -7689,7 +7837,9 @@
         <s:v>19</s:v>
       </s:c>
       <s:c r="D76" s="1"/>
-      <s:c r="E76" s="1"/>
+      <s:c r="E76" s="1" t="n">
+        <s:v>410.7</s:v>
+      </s:c>
       <s:c r="F76" s="1" t="n">
         <s:v>2090</s:v>
       </s:c>
@@ -7735,7 +7885,9 @@
         <s:v>19</s:v>
       </s:c>
       <s:c r="D77" s="1"/>
-      <s:c r="E77" s="1"/>
+      <s:c r="E77" s="1" t="n">
+        <s:v>410.04</s:v>
+      </s:c>
       <s:c r="F77" s="1" t="n">
         <s:v>2050</s:v>
       </s:c>
@@ -7781,7 +7933,9 @@
         <s:v>20</s:v>
       </s:c>
       <s:c r="D78" s="1"/>
-      <s:c r="E78" s="1"/>
+      <s:c r="E78" s="1" t="n">
+        <s:v>413.14</s:v>
+      </s:c>
       <s:c r="F78" s="1" t="n">
         <s:v>1495</s:v>
       </s:c>
@@ -7827,7 +7981,9 @@
         <s:v>20</s:v>
       </s:c>
       <s:c r="D79" s="1"/>
-      <s:c r="E79" s="1"/>
+      <s:c r="E79" s="1" t="n">
+        <s:v>413.95</s:v>
+      </s:c>
       <s:c r="F79" s="1" t="n">
         <s:v>1280</s:v>
       </s:c>
@@ -7873,7 +8029,9 @@
         <s:v>20</s:v>
       </s:c>
       <s:c r="D80" s="1"/>
-      <s:c r="E80" s="1"/>
+      <s:c r="E80" s="1" t="n">
+        <s:v>403.26</s:v>
+      </s:c>
       <s:c r="F80" s="1" t="n">
         <s:v>1215</s:v>
       </s:c>
@@ -7919,7 +8077,9 @@
         <s:v>20</s:v>
       </s:c>
       <s:c r="D81" s="1"/>
-      <s:c r="E81" s="1"/>
+      <s:c r="E81" s="1" t="n">
+        <s:v>397.67</s:v>
+      </s:c>
       <s:c r="F81" s="1" t="n">
         <s:v>935</s:v>
       </s:c>
@@ -7965,7 +8125,9 @@
         <s:v>21</s:v>
       </s:c>
       <s:c r="D82" s="1"/>
-      <s:c r="E82" s="1"/>
+      <s:c r="E82" s="1" t="n">
+        <s:v>412.77</s:v>
+      </s:c>
       <s:c r="F82" s="1" t="n">
         <s:v>565</s:v>
       </s:c>
@@ -8011,7 +8173,9 @@
         <s:v>21</s:v>
       </s:c>
       <s:c r="D83" s="1"/>
-      <s:c r="E83" s="1"/>
+      <s:c r="E83" s="1" t="n">
+        <s:v>412.77</s:v>
+      </s:c>
       <s:c r="F83" s="1" t="n">
         <s:v>560</s:v>
       </s:c>
@@ -8057,7 +8221,9 @@
         <s:v>21</s:v>
       </s:c>
       <s:c r="D84" s="1"/>
-      <s:c r="E84" s="1"/>
+      <s:c r="E84" s="1" t="n">
+        <s:v>407.26</s:v>
+      </s:c>
       <s:c r="F84" s="1" t="n">
         <s:v>540</s:v>
       </s:c>
@@ -8103,7 +8269,9 @@
         <s:v>21</s:v>
       </s:c>
       <s:c r="D85" s="1"/>
-      <s:c r="E85" s="1"/>
+      <s:c r="E85" s="1" t="n">
+        <s:v>411.16</s:v>
+      </s:c>
       <s:c r="F85" s="1" t="n">
         <s:v>455</s:v>
       </s:c>
@@ -8149,7 +8317,9 @@
         <s:v>22</s:v>
       </s:c>
       <s:c r="D86" s="1"/>
-      <s:c r="E86" s="1"/>
+      <s:c r="E86" s="1" t="n">
+        <s:v>405.54</s:v>
+      </s:c>
       <s:c r="F86" s="1" t="n">
         <s:v>370</s:v>
       </s:c>
@@ -8195,7 +8365,9 @@
         <s:v>22</s:v>
       </s:c>
       <s:c r="D87" s="1"/>
-      <s:c r="E87" s="1"/>
+      <s:c r="E87" s="1" t="n">
+        <s:v>411</s:v>
+      </s:c>
       <s:c r="F87" s="1" t="n">
         <s:v>370</s:v>
       </s:c>
@@ -8241,7 +8413,9 @@
         <s:v>22</s:v>
       </s:c>
       <s:c r="D88" s="1"/>
-      <s:c r="E88" s="1"/>
+      <s:c r="E88" s="1" t="n">
+        <s:v>411.16</s:v>
+      </s:c>
       <s:c r="F88" s="1" t="n">
         <s:v>410</s:v>
       </s:c>
@@ -8287,7 +8461,9 @@
         <s:v>22</s:v>
       </s:c>
       <s:c r="D89" s="1"/>
-      <s:c r="E89" s="1"/>
+      <s:c r="E89" s="1" t="n">
+        <s:v>404.19</s:v>
+      </s:c>
       <s:c r="F89" s="1" t="n">
         <s:v>480</s:v>
       </s:c>
@@ -8333,7 +8509,9 @@
         <s:v>23</s:v>
       </s:c>
       <s:c r="D90" s="1"/>
-      <s:c r="E90" s="1"/>
+      <s:c r="E90" s="1" t="n">
+        <s:v>412.16</s:v>
+      </s:c>
       <s:c r="F90" s="1" t="n">
         <s:v>480</s:v>
       </s:c>
@@ -8379,7 +8557,9 @@
         <s:v>23</s:v>
       </s:c>
       <s:c r="D91" s="1"/>
-      <s:c r="E91" s="1"/>
+      <s:c r="E91" s="1" t="n">
+        <s:v>412.47</s:v>
+      </s:c>
       <s:c r="F91" s="1" t="n">
         <s:v>540</s:v>
       </s:c>
@@ -8425,7 +8605,9 @@
         <s:v>23</s:v>
       </s:c>
       <s:c r="D92" s="1"/>
-      <s:c r="E92" s="1"/>
+      <s:c r="E92" s="1" t="n">
+        <s:v>413.45</s:v>
+      </s:c>
       <s:c r="F92" s="1" t="n">
         <s:v>540</s:v>
       </s:c>
@@ -8471,7 +8653,9 @@
         <s:v>23</s:v>
       </s:c>
       <s:c r="D93" s="1"/>
-      <s:c r="E93" s="1"/>
+      <s:c r="E93" s="1" t="n">
+        <s:v>413.45</s:v>
+      </s:c>
       <s:c r="F93" s="1" t="n">
         <s:v>540</s:v>
       </s:c>
@@ -8517,7 +8701,9 @@
         <s:v>24</s:v>
       </s:c>
       <s:c r="D94" s="1"/>
-      <s:c r="E94" s="1"/>
+      <s:c r="E94" s="1" t="n">
+        <s:v>412.26</s:v>
+      </s:c>
       <s:c r="F94" s="1" t="n">
         <s:v>710</s:v>
       </s:c>
@@ -8563,7 +8749,9 @@
         <s:v>24</s:v>
       </s:c>
       <s:c r="D95" s="1"/>
-      <s:c r="E95" s="1"/>
+      <s:c r="E95" s="1" t="n">
+        <s:v>404.26</s:v>
+      </s:c>
       <s:c r="F95" s="1" t="n">
         <s:v>710</s:v>
       </s:c>
@@ -8609,7 +8797,9 @@
         <s:v>24</s:v>
       </s:c>
       <s:c r="D96" s="1"/>
-      <s:c r="E96" s="1"/>
+      <s:c r="E96" s="1" t="n">
+        <s:v>405.27</s:v>
+      </s:c>
       <s:c r="F96" s="1" t="n">
         <s:v>520</s:v>
       </s:c>
@@ -8657,7 +8847,9 @@
         <s:v>24</s:v>
       </s:c>
       <s:c r="D97" s="1"/>
-      <s:c r="E97" s="1"/>
+      <s:c r="E97" s="1" t="n">
+        <s:v>406.16</s:v>
+      </s:c>
       <s:c r="F97" s="1" t="n">
         <s:v>380</s:v>
       </s:c>
